--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -573,10 +573,10 @@
         <v>0.2375268817204247</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5543111140221361</v>
+        <v>0.3926489259287328</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1697225105426171</v>
+        <v>0.3282735536805973</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -585,10 +585,10 @@
         <v>8.529999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.017125623057534</v>
+        <v>-0.2716964246545226</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.530130541746341</v>
+        <v>-0.8561508076277378</v>
       </c>
       <c r="K2" t="n">
         <v>1.503869319268053</v>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>2.308886183749409</v>
+        <v>1.628280321699303</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5484225354733688</v>
+        <v>0.3867603473799655</v>
       </c>
     </row>
     <row r="3">
@@ -653,25 +653,25 @@
         <v>0.8333333333333357</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7879489999445289</v>
+        <v>0.7025257120264781</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7667019697157103</v>
+        <v>0.723348266805792</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3400155431219595</v>
+        <v>0.4654048644243423</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8.363137619014847</v>
+        <v>7.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4175953374219</v>
+        <v>-1.120303575345475</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.313199763404282</v>
+        <v>-1.180506354030542</v>
       </c>
       <c r="K3" t="n">
         <v>1.476124700750311</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.9531828027707</v>
+        <v>1.009787346841578</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7510594362074963</v>
+        <v>0.7094015748352079</v>
       </c>
     </row>
     <row r="4">
@@ -736,25 +736,25 @@
         <v>1.616666666666665</v>
       </c>
       <c r="D4" t="n">
-        <v>1.466727442926349</v>
+        <v>1.390900995023915</v>
       </c>
       <c r="E4" t="n">
-        <v>1.095743696655871</v>
+        <v>1.138402588177013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5329106806969117</v>
+        <v>0.6095437283672813</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.356304837751197</v>
+        <v>6.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.781568470528983</v>
+        <v>-2.16445045300336</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9848379260494671</v>
+        <v>-0.7929148872947609</v>
       </c>
       <c r="K4" t="n">
         <v>1.456107007927592</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.7345700653210789</v>
+        <v>0.8059671886090314</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.077414073558628</v>
+        <v>1.121020564592929</v>
       </c>
     </row>
     <row r="5">
@@ -819,25 +819,25 @@
         <v>3.383333333333338</v>
       </c>
       <c r="D5" t="n">
-        <v>4.31583695462491</v>
+        <v>4.436530529066649</v>
       </c>
       <c r="E5" t="n">
-        <v>2.486887985810236</v>
+        <v>2.532768420962769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9553228217759524</v>
+        <v>0.8821521047972887</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5670106430165482</v>
+        <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.507633374437406</v>
+        <v>-1.413538593481983</v>
       </c>
       <c r="J5" t="n">
-        <v>1.334374722323774</v>
+        <v>1.156859975770168</v>
       </c>
       <c r="K5" t="n">
         <v>1.453274757558028</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.5919721885577585</v>
+        <v>0.5866378230597462</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.554855447487759</v>
+        <v>2.602636611509764</v>
       </c>
     </row>
     <row r="6">
@@ -902,13 +902,13 @@
         <v>4.116666666666669</v>
       </c>
       <c r="D6" t="n">
-        <v>6.405658768428653</v>
+        <v>6.540103064712703</v>
       </c>
       <c r="E6" t="n">
-        <v>3.238561958585666</v>
+        <v>3.207955434994732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.917776590256664</v>
+        <v>0.8343859193810066</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>-0.342408123791104</v>
       </c>
       <c r="J6" t="n">
-        <v>1.159196246285139</v>
+        <v>1.070925513667381</v>
       </c>
       <c r="K6" t="n">
         <v>1.477513144171748</v>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>0.5349931956246751</v>
+        <v>0.5199202466166637</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.426983854602866</v>
+        <v>3.400331998303826</v>
       </c>
     </row>
     <row r="7">
@@ -985,13 +985,13 @@
         <v>5.733333333333334</v>
       </c>
       <c r="D7" t="n">
-        <v>13.02704063110584</v>
+        <v>12.93609347484513</v>
       </c>
       <c r="E7" t="n">
-        <v>4.340119414738684</v>
+        <v>4.249220558538559</v>
       </c>
       <c r="F7" t="n">
-        <v>0.13226677584806</v>
+        <v>0.2116656624548665</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>0.3797887969978633</v>
+        <v>0.3751043311349999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.947524089729971</v>
+        <v>4.852384690381618</v>
       </c>
     </row>
     <row r="8">
@@ -1068,13 +1068,13 @@
         <v>6.533333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>16.59589596568245</v>
+        <v>16.4514370628705</v>
       </c>
       <c r="E8" t="n">
-        <v>4.228553614214273</v>
+        <v>4.247369903771546</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4979464305348238</v>
+        <v>-0.3621710175174195</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>0.2987748964420489</v>
+        <v>0.3021559819679683</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.958437098509792</v>
+        <v>4.970900120515864</v>
       </c>
     </row>
     <row r="9">
@@ -1151,13 +1151,13 @@
         <v>7.400000000000004</v>
       </c>
       <c r="D9" t="n">
-        <v>20.04233616118429</v>
+        <v>19.99465309484491</v>
       </c>
       <c r="E9" t="n">
-        <v>3.460418533308513</v>
+        <v>3.595621960029153</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.161270647703097</v>
+        <v>-1.123938611504293</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>0.2046758579461997</v>
+        <v>0.2118495842034962</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.102182349036537</v>
+        <v>4.235858944436043</v>
       </c>
     </row>
     <row r="10">
@@ -1234,13 +1234,13 @@
         <v>8.000000000000002</v>
       </c>
       <c r="D10" t="n">
-        <v>21.90414778532685</v>
+        <v>21.94736451349033</v>
       </c>
       <c r="E10" t="n">
-        <v>2.649441600808605</v>
+        <v>2.766768218662275</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.295412204256244</v>
+        <v>-1.343755282634725</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>0.1412456392075651</v>
+        <v>0.1463532815536431</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001484785124081059</v>
+        <v>0.001481861422009717</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001484785124081059</v>
+        <v>0.001481861422009717</v>
       </c>
       <c r="X10" t="n">
         <v>0.03252295278732637</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.093865355235462</v>
+        <v>3.212068818003286</v>
       </c>
     </row>
     <row r="11">
@@ -1317,13 +1317,13 @@
         <v>9.283333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>24.05923551807384</v>
+        <v>24.15921957614428</v>
       </c>
       <c r="E11" t="n">
-        <v>1.141303698996739</v>
+        <v>1.145676400792977</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8593776337987036</v>
+        <v>-0.9199320657109662</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>0.04656417835443825</v>
+        <v>0.04654885228669232</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004277320963704851</v>
+        <v>0.004259619071213121</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004017468428302058</v>
+        <v>0.004000927121195224</v>
       </c>
       <c r="X11" t="n">
         <v>0.1029090724521696</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.120298533735026</v>
+        <v>1.124583943411706</v>
       </c>
     </row>
     <row r="12">
@@ -1400,13 +1400,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>24.77268809228702</v>
+        <v>24.78520015052234</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3909939650415275</v>
+        <v>0.3549297903157393</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.226662046390678</v>
+        <v>-0.2324157917266303</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>0.003842087191651498</v>
+        <v>0.002379050554110678</v>
       </c>
       <c r="V12" t="n">
-        <v>0.003398407529152446</v>
+        <v>0.003396691945955462</v>
       </c>
       <c r="W12" t="n">
-        <v>0.003350211476126097</v>
+        <v>0.003366863637048577</v>
       </c>
       <c r="X12" t="n">
         <v>0.08418768973017335</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09517882762215352</v>
+        <v>0.05896524415184423</v>
       </c>
     </row>
     <row r="13">
@@ -1483,13 +1483,13 @@
         <v>13.15</v>
       </c>
       <c r="D13" t="n">
-        <v>25.55755469146949</v>
+        <v>25.52936787515874</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4285991589614797</v>
+        <v>0.4247827633206231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01374980761621421</v>
+        <v>0.02421244228691488</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1536,19 +1536,19 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>0.004644306008744943</v>
+        <v>0.00451333120799062</v>
       </c>
       <c r="V13" t="n">
-        <v>0.002802332196263887</v>
+        <v>0.002805426233814838</v>
       </c>
       <c r="W13" t="n">
-        <v>0.002718079287151608</v>
+        <v>0.002723458954427426</v>
       </c>
       <c r="X13" t="n">
         <v>0.07162075836968011</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1186971048224192</v>
+        <v>0.115222492751227</v>
       </c>
     </row>
     <row r="14">
@@ -1566,13 +1566,13 @@
         <v>15.15</v>
       </c>
       <c r="D14" t="n">
-        <v>26.52397387472312</v>
+        <v>26.51727820874701</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4485086783228001</v>
+        <v>0.4565985853136878</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.01280234260742574</v>
+        <v>-0.01156002969159746</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>0.004363500136320473</v>
+        <v>0.00467285042783293</v>
       </c>
       <c r="V14" t="n">
-        <v>0.004286411711977421</v>
+        <v>0.004287494039538852</v>
       </c>
       <c r="W14" t="n">
-        <v>0.004183164297161491</v>
+        <v>0.004176898982023491</v>
       </c>
       <c r="X14" t="n">
         <v>0.1136926722647963</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1157373636181149</v>
+        <v>0.1239112748227083</v>
       </c>
     </row>
     <row r="15">
@@ -1649,13 +1649,13 @@
         <v>17.1</v>
       </c>
       <c r="D15" t="n">
-        <v>27.33259068603333</v>
+        <v>27.336621249569</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3802771695130964</v>
+        <v>0.3818331051817658</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02928478232179146</v>
+        <v>-0.03239071966445572</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1702,19 +1702,19 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>-0.003590733905795075</v>
+        <v>-0.003535867629664758</v>
       </c>
       <c r="V15" t="n">
-        <v>0.008576982722137571</v>
+        <v>0.008575718115458847</v>
       </c>
       <c r="W15" t="n">
-        <v>0.008700461953821473</v>
+        <v>0.008697292661400426</v>
       </c>
       <c r="X15" t="n">
         <v>0.2344311580653662</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.09814406010955845</v>
+        <v>-0.0966586741807568</v>
       </c>
     </row>
     <row r="16">
@@ -1732,13 +1732,13 @@
         <v>18.15</v>
       </c>
       <c r="D16" t="n">
-        <v>27.71243354711543</v>
+        <v>27.71586757332252</v>
       </c>
       <c r="E16" t="n">
-        <v>0.352754082873016</v>
+        <v>0.3511872001999183</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01812639682461964</v>
+        <v>-0.0201447979836277</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1785,19 +1785,19 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>-0.01066597591190639</v>
+        <v>-0.01072408683700126</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01245217194545731</v>
+        <v>0.0124506291077784</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01293505824701726</v>
+        <v>0.0129360861395104</v>
       </c>
       <c r="X16" t="n">
         <v>0.3450799875557407</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.2955801486738396</v>
+        <v>-0.297227370619138</v>
       </c>
     </row>
     <row r="17">
@@ -1815,13 +1815,13 @@
         <v>19.16666666666667</v>
       </c>
       <c r="D17" t="n">
-        <v>28.06220633394021</v>
+        <v>28.06306419986345</v>
       </c>
       <c r="E17" t="n">
-        <v>0.342285434983685</v>
+        <v>0.3396073054888795</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.006786826796083723</v>
+        <v>-0.007464977064400441</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1868,19 +1868,19 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>-0.01986944509974919</v>
+        <v>-0.01996525050408979</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0172187913778917</v>
+        <v>0.01721826501290685</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01842874062079043</v>
+        <v>0.01843401115738567</v>
       </c>
       <c r="X17" t="n">
         <v>0.4831972764674675</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.5575804681300589</v>
+        <v>-0.5602861066626278</v>
       </c>
     </row>
     <row r="18">
@@ -1898,13 +1898,13 @@
         <v>20.13333333333334</v>
       </c>
       <c r="D18" t="n">
-        <v>28.39147068543616</v>
+        <v>28.38960715368643</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3389511543182806</v>
+        <v>0.3359988058690107</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0001116849254426677</v>
+        <v>-8.842180868606775e-07</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>-0.03026604090839843</v>
+        <v>-0.03036925123769535</v>
       </c>
       <c r="V18" t="n">
-        <v>0.02162190239001286</v>
+        <v>0.02162332168057842</v>
       </c>
       <c r="W18" t="n">
-        <v>0.02408736760693919</v>
+        <v>0.02409735677715759</v>
       </c>
       <c r="X18" t="n">
         <v>0.6138776078694121</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.8592974132150057</v>
+        <v>-0.8621711121897764</v>
       </c>
     </row>
     <row r="19">
@@ -1984,10 +1984,10 @@
         <v>0.1675555555555282</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02306373213911789</v>
+        <v>0.1255382041851616</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1122349736084235</v>
+        <v>0.009035322182628869</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1996,10 +1996,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1753890535507434</v>
+        <v>-0.7913765033448836</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9862356951995965</v>
+        <v>-0.2960109003588285</v>
       </c>
       <c r="K19" t="n">
         <v>1.549963747666238</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>0.121734114757783</v>
+        <v>0.7333191601255176</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.02039722722830075</v>
+        <v>0.1228716992743445</v>
       </c>
     </row>
     <row r="20">
@@ -2064,25 +2064,25 @@
         <v>1.216666666666665</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3289694526095552</v>
+        <v>0.3866171026921199</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2422741808264062</v>
+        <v>0.234562969190058</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2481109694391741</v>
+        <v>0.1701834696062422</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8.426287063027756</v>
+        <v>8.10757322031974</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.260851390787195</v>
+        <v>-1.168777107088426</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7980859550521077</v>
+        <v>-0.3243736537401457</v>
       </c>
       <c r="K20" t="n">
         <v>1.521195707693277</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>0.7215918400968782</v>
+        <v>0.5918339114083226</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.2373816726441917</v>
+        <v>0.2288131121036305</v>
       </c>
     </row>
     <row r="21">
@@ -2147,25 +2147,25 @@
         <v>2.050000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5934246628551025</v>
+        <v>0.6132006172582924</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4878107180961385</v>
+        <v>0.4223722952956069</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4334420526090135</v>
+        <v>0.398793439945613</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>7.065799506425278</v>
+        <v>7.025886645992754</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8722273179004</v>
+        <v>-1.44718287829349</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4897432903228169</v>
+        <v>-0.3556079501759632</v>
       </c>
       <c r="K21" t="n">
         <v>1.502925724577933</v>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>0.8094467922734685</v>
+        <v>0.6762199552482044</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.4803456898040273</v>
+        <v>0.4146584939605738</v>
       </c>
     </row>
     <row r="22">
@@ -2230,25 +2230,25 @@
         <v>2.83333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>1.101061727015566</v>
+        <v>1.054856521871844</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9295420730460983</v>
+        <v>0.8624570723194246</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6437955968923486</v>
+        <v>0.6549483233901348</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.422764864003257</v>
+        <v>5.782429322354742</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.076262102230415</v>
+        <v>-1.741589087140767</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0907850254344562</v>
+        <v>-0.2118398972099618</v>
       </c>
       <c r="K22" t="n">
         <v>1.490338016847339</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>0.8374516823386481</v>
+        <v>0.8108343321743422</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.9220859956478831</v>
+        <v>0.8553138834517061</v>
       </c>
     </row>
     <row r="23">
@@ -2313,25 +2313,25 @@
         <v>5.299999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>5.580407762317665</v>
+        <v>5.50190772117922</v>
       </c>
       <c r="E23" t="n">
-        <v>3.138054277718519</v>
+        <v>3.201433890314465</v>
       </c>
       <c r="F23" t="n">
-        <v>1.077524615621536</v>
+        <v>1.031873573097766</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4662114291862001</v>
+        <v>0.295</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9821920044631338</v>
+        <v>-0.99029481717011</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5047875303520509</v>
+        <v>0.450912240958371</v>
       </c>
       <c r="K23" t="n">
         <v>1.5118717459471</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>0.5845114068112641</v>
+        <v>0.6040542413861695</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.261811991732797</v>
+        <v>3.323450694693622</v>
       </c>
     </row>
     <row r="24">
@@ -2396,13 +2396,13 @@
         <v>6.999999999999998</v>
       </c>
       <c r="D24" t="n">
-        <v>12.46410470886678</v>
+        <v>12.58294639097404</v>
       </c>
       <c r="E24" t="n">
-        <v>5.183294295303559</v>
+        <v>5.053613078290592</v>
       </c>
       <c r="F24" t="n">
-        <v>1.062869724844733</v>
+        <v>0.9801587140388435</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>-0.05229653505237738</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2146702420577397</v>
+        <v>0.2161066794433439</v>
       </c>
       <c r="K24" t="n">
         <v>1.597926373230323</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>0.450493388580871</v>
+        <v>0.4362596436659493</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.614996765924186</v>
+        <v>5.489431708794079</v>
       </c>
     </row>
     <row r="25">
@@ -2479,13 +2479,13 @@
         <v>7.733333333333336</v>
       </c>
       <c r="D25" t="n">
-        <v>16.62393583647465</v>
+        <v>16.56993282318025</v>
       </c>
       <c r="E25" t="n">
-        <v>5.918377245807189</v>
+        <v>5.73780169577941</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1998728483672161</v>
+        <v>0.6028099807799618</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>0.3884933643330891</v>
+        <v>0.378755868888033</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.458288761569442</v>
+        <v>6.275959303859973</v>
       </c>
     </row>
     <row r="26">
@@ -2562,13 +2562,13 @@
         <v>8.616666666666669</v>
       </c>
       <c r="D26" t="n">
-        <v>22.11345605224206</v>
+        <v>21.95859502624546</v>
       </c>
       <c r="E26" t="n">
-        <v>5.24104561111519</v>
+        <v>5.918973177363313</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.963660347160828</v>
+        <v>-1.509816023684901</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>0.2602240868702173</v>
+        <v>0.2927685517922844</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.754453908739368</v>
+        <v>6.428786065227143</v>
       </c>
     </row>
     <row r="27">
@@ -2645,13 +2645,13 @@
         <v>9.216666666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>24.86133397639429</v>
+        <v>25.43605023144343</v>
       </c>
       <c r="E27" t="n">
-        <v>3.575068496137004</v>
+        <v>4.314174476627918</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.577600201021315</v>
+        <v>-2.775155341726455</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>0.1594278855253748</v>
+        <v>0.1852361999692742</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.9635899071967</v>
+        <v>4.711677287100157</v>
       </c>
     </row>
     <row r="28">
@@ -2728,13 +2728,13 @@
         <v>10.5</v>
       </c>
       <c r="D28" t="n">
-        <v>26.69145309571078</v>
+        <v>26.90576270140085</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8134625588328568</v>
+        <v>0.4768870689450928</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.43954721797159</v>
+        <v>-1.884045409374397</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>0.03232851343233704</v>
+        <v>0.01957634192483895</v>
       </c>
       <c r="V28" t="n">
-        <v>0.005776488224851725</v>
+        <v>0.005730477378495867</v>
       </c>
       <c r="W28" t="n">
-        <v>0.00552884292313</v>
+        <v>0.005581711678475328</v>
       </c>
       <c r="X28" t="n">
         <v>0.1541828645115554</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.8628949999332802</v>
+        <v>0.5267164103912014</v>
       </c>
     </row>
     <row r="29">
@@ -2811,13 +2811,13 @@
         <v>12.25</v>
       </c>
       <c r="D29" t="n">
-        <v>26.65311597876561</v>
+        <v>26.14540462095952</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.005810554401408652</v>
+        <v>-0.1807580605032388</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1637940475849494</v>
+        <v>-0.03320424263343408</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -2864,19 +2864,19 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>-0.01119116119163786</v>
+        <v>-0.01788672368346078</v>
       </c>
       <c r="V29" t="n">
-        <v>0.003323907882975883</v>
+        <v>0.003388454055007017</v>
       </c>
       <c r="W29" t="n">
-        <v>0.003517243579328763</v>
+        <v>0.003703461135519619</v>
       </c>
       <c r="X29" t="n">
         <v>0.08859250230768947</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.2982793171777847</v>
+        <v>-0.4676556280473815</v>
       </c>
     </row>
     <row r="30">
@@ -2894,13 +2894,13 @@
         <v>14.36666666666667</v>
       </c>
       <c r="D30" t="n">
-        <v>26.68202623302077</v>
+        <v>26.41239494873913</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4267071201364878</v>
+        <v>0.6260520196969441</v>
       </c>
       <c r="F30" t="n">
-        <v>0.224155456203944</v>
+        <v>0.2906134019905942</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2947,19 +2947,19 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>-0.002159116125110338</v>
+        <v>0.005551541158314535</v>
       </c>
       <c r="V30" t="n">
-        <v>0.0006467522300865029</v>
+        <v>0.00065335460880864</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0006891476685905666</v>
+        <v>0.0005432342243975793</v>
       </c>
       <c r="X30" t="n">
         <v>0.01725665996943276</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.0576095930903322</v>
+        <v>0.1466294976475842</v>
       </c>
     </row>
     <row r="31">
@@ -2977,13 +2977,13 @@
         <v>16.36666666666667</v>
       </c>
       <c r="D31" t="n">
-        <v>28.31600500677294</v>
+        <v>28.60921997767586</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9124663425295276</v>
+        <v>1.036148024359556</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06681355908669991</v>
+        <v>-0.08046043146725339</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -3030,19 +3030,19 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>0.01660748072661906</v>
+        <v>0.02060035451617961</v>
       </c>
       <c r="V31" t="n">
-        <v>0.006991070313086991</v>
+        <v>0.006919419059399134</v>
       </c>
       <c r="W31" t="n">
-        <v>0.006655958281680099</v>
+        <v>0.006507997618334095</v>
       </c>
       <c r="X31" t="n">
         <v>0.1979591819880729</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4702575074048302</v>
+        <v>0.589360073971491</v>
       </c>
     </row>
     <row r="32">
@@ -3060,13 +3060,13 @@
         <v>18.3</v>
       </c>
       <c r="D32" t="n">
-        <v>30.25854242389568</v>
+        <v>30.49607407770099</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7125913349319077</v>
+        <v>0.3470076505793394</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2315382207953283</v>
+        <v>-0.5460393706624851</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -3113,19 +3113,19 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>0.01987610556165762</v>
+        <v>0.007704782304053718</v>
       </c>
       <c r="V32" t="n">
-        <v>0.02408237874456443</v>
+        <v>0.02389480288689215</v>
       </c>
       <c r="W32" t="n">
-        <v>0.02321948068965366</v>
+        <v>0.02356291405558334</v>
       </c>
       <c r="X32" t="n">
         <v>0.7286976789107263</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.601421983359246</v>
+        <v>0.2349656118969819</v>
       </c>
     </row>
     <row r="33">
@@ -3143,13 +3143,13 @@
         <v>19.36666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>30.84669647792873</v>
+        <v>30.49607407770099</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3901975163800557</v>
+        <v>-0.3470076505793358</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3729501889893923</v>
+        <v>-0.7552393190100266</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -3196,19 +3196,19 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>0.01802613182238104</v>
+        <v>-0.006002205126870144</v>
       </c>
       <c r="V33" t="n">
-        <v>0.03668647152063631</v>
+        <v>0.03710826675459588</v>
       </c>
       <c r="W33" t="n">
-        <v>0.03534134900753256</v>
+        <v>0.03756130499155563</v>
       </c>
       <c r="X33" t="n">
         <v>1.131656451843245</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.5560466169961201</v>
+        <v>-0.1830436921785885</v>
       </c>
     </row>
     <row r="34">
@@ -3229,10 +3229,10 @@
         <v>0.103563218390794</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.003236254490673496</v>
+        <v>-0.0918118973955262</v>
       </c>
       <c r="F34" t="n">
-        <v>0.216388077821744</v>
+        <v>0.2116110470203466</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3241,10 +3241,10 @@
         <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4438975883783622</v>
+        <v>-0.850049343677429</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5834831425555236</v>
+        <v>0.4719308012271115</v>
       </c>
       <c r="K34" t="n">
         <v>1.655684716242998</v>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>-0.07843201552556303</v>
+        <v>-0.9337129181585238</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.008122671952704028</v>
+        <v>-0.09669831485755673</v>
       </c>
     </row>
     <row r="35">
@@ -3309,25 +3309,25 @@
         <v>0.6833333333333336</v>
       </c>
       <c r="D35" t="n">
-        <v>0.158780670997071</v>
+        <v>0.103563218390794</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1648483108992891</v>
+        <v>0.0918118973955262</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2755667477098538</v>
+        <v>0.3258244499290749</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>9.581342360757406</v>
+        <v>9.453302605195947</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7814418435511805</v>
+        <v>-0.750040592334428</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4044512628283344</v>
+        <v>-0.1792222607110113</v>
       </c>
       <c r="K35" t="n">
         <v>1.607841572062204</v>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>0.9997097811572452</v>
+        <v>0.8480257853527235</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1587345898544824</v>
+        <v>0.08782427960950868</v>
       </c>
     </row>
     <row r="36">
@@ -3392,25 +3392,25 @@
         <v>1.716666666666666</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4604485331862986</v>
+        <v>0.3419009325240578</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4958369597624576</v>
+        <v>0.517732186871251</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4322468041164155</v>
+        <v>0.5486115755314339</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>8.510128854761771</v>
+        <v>8.756397578515919</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.059497061955232</v>
+        <v>-1.44398334508746</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.08577851918667223</v>
+        <v>-0.3511064044088421</v>
       </c>
       <c r="K36" t="n">
         <v>1.556535326712928</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>1.052390522728232</v>
+        <v>1.489809546534737</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.4845716725293765</v>
+        <v>0.5093672732434701</v>
       </c>
     </row>
     <row r="37">
@@ -3475,25 +3475,25 @@
         <v>2.149999999999998</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7123640694058089</v>
+        <v>0.6184203542009686</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7034848224352286</v>
+        <v>0.7802561060416093</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5459432050535495</v>
+        <v>0.6466218851281117</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>8.046863179174109</v>
+        <v>7.990826846992402</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.06335709473045</v>
+        <v>-1.537896942261227</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3368013440350611</v>
+        <v>-1.970175822507692e-05</v>
       </c>
       <c r="K37" t="n">
         <v>1.542135465609338</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>0.9689605552551183</v>
+        <v>1.243117183826354</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.6902526842352482</v>
+        <v>0.7687689691352048</v>
       </c>
     </row>
     <row r="38">
@@ -3558,25 +3558,25 @@
         <v>2.666666666666665</v>
       </c>
       <c r="D38" t="n">
-        <v>1.151073386316615</v>
+        <v>1.109111088172195</v>
       </c>
       <c r="E38" t="n">
-        <v>1.026678781134888</v>
+        <v>1.139476359177527</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6898018177224933</v>
+        <v>0.7360861973581334</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>7.500984165571503</v>
+        <v>7.337196350401693</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.439361972882319</v>
+        <v>-1.404411910829691</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.590151483021186</v>
+        <v>-0.877943943965775</v>
       </c>
       <c r="K38" t="n">
         <v>1.530160174384962</v>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>0.8802054621135156</v>
+        <v>1.015651840150318</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.013181081929385</v>
+        <v>1.126470717633211</v>
       </c>
     </row>
     <row r="39">
@@ -3641,25 +3641,25 @@
         <v>3.166666666666666</v>
       </c>
       <c r="D39" t="n">
-        <v>1.750330828921519</v>
+        <v>1.770664924830103</v>
       </c>
       <c r="E39" t="n">
-        <v>1.402675717479243</v>
+        <v>1.527271647189796</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8162881122844017</v>
+        <v>0.8164302618724539</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>6.596066753378069</v>
+        <v>6.567577188322776</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.651728088241166</v>
+        <v>-2.393207464740226</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.97733384527763</v>
+        <v>-2.944494379525494</v>
       </c>
       <c r="K39" t="n">
         <v>1.523721788805478</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>0.7960973021490124</v>
+        <v>0.8572611291126977</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.393433650772666</v>
+        <v>1.517922212740104</v>
       </c>
     </row>
     <row r="40">
@@ -3724,25 +3724,25 @@
         <v>3.666666666666665</v>
       </c>
       <c r="D40" t="n">
-        <v>2.553749103795857</v>
+        <v>2.63638273536199</v>
       </c>
       <c r="E40" t="n">
-        <v>1.84296689341929</v>
+        <v>1.955906621049981</v>
       </c>
       <c r="F40" t="n">
-        <v>0.944166157889093</v>
+        <v>0.8976583663213509</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>4.849256077330341</v>
+        <v>4.94398888566147</v>
       </c>
       <c r="I40" t="n">
-        <v>-4.416695818159947</v>
+        <v>-4.348906290355183</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.172552940378093</v>
+        <v>-2.575996645276082</v>
       </c>
       <c r="K40" t="n">
         <v>1.522114644830368</v>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>0.7225807478943129</v>
+        <v>0.7427999005020658</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.845289937355242</v>
+        <v>1.95830483351225</v>
       </c>
     </row>
     <row r="41">
@@ -3807,25 +3807,25 @@
         <v>4.166666666666667</v>
       </c>
       <c r="D41" t="n">
-        <v>3.593297722340811</v>
+        <v>3.726571545880087</v>
       </c>
       <c r="E41" t="n">
-        <v>2.346841875368337</v>
+        <v>2.424930013511148</v>
       </c>
       <c r="F41" t="n">
-        <v>1.080719922124493</v>
+        <v>0.9843972852010769</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.179370935218114</v>
+        <v>2.218670897967584</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.824281028619254</v>
+        <v>-4.969204110016304</v>
       </c>
       <c r="J41" t="n">
-        <v>1.677518798451239</v>
+        <v>1.518203753949354</v>
       </c>
       <c r="K41" t="n">
         <v>1.525106395926922</v>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>0.6599045942354963</v>
+        <v>0.6575015304236708</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.371233675428646</v>
+        <v>2.450226494649462</v>
       </c>
     </row>
     <row r="42">
@@ -3890,25 +3890,25 @@
         <v>4.649999999999998</v>
       </c>
       <c r="D42" t="n">
-        <v>4.852700873653368</v>
+        <v>5.012881364672379</v>
       </c>
       <c r="E42" t="n">
-        <v>2.903283023766507</v>
+        <v>2.922378018433013</v>
       </c>
       <c r="F42" t="n">
-        <v>1.214058165585493</v>
+        <v>1.069093706042256</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08848314025434899</v>
+        <v>0.04182457744715143</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.848840479651152</v>
+        <v>-2.946433245751134</v>
       </c>
       <c r="J42" t="n">
-        <v>3.762380701880289</v>
+        <v>3.863750883367386</v>
       </c>
       <c r="K42" t="n">
         <v>1.532151522940201</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>0.6103679068526441</v>
+        <v>0.5950597266298594</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.961932874833804</v>
+        <v>2.982963814489862</v>
       </c>
     </row>
     <row r="43">
@@ -3973,13 +3973,13 @@
         <v>5.549999999999998</v>
       </c>
       <c r="D43" t="n">
-        <v>7.964427895244278</v>
+        <v>8.08050094818379</v>
       </c>
       <c r="E43" t="n">
-        <v>4.101180545025463</v>
+        <v>3.951414062484349</v>
       </c>
       <c r="F43" t="n">
-        <v>1.418758297730828</v>
+        <v>1.218072736818905</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3988,10 +3988,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.006913400350021075</v>
+        <v>-0.00749900265779244</v>
       </c>
       <c r="J43" t="n">
-        <v>1.58378105823286</v>
+        <v>1.668520525197393</v>
       </c>
       <c r="K43" t="n">
         <v>1.555422776715727</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>0.5358612711645822</v>
+        <v>0.5099301040513576</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>4.267828456044256</v>
+        <v>4.120490689294455</v>
       </c>
     </row>
     <row r="44">
@@ -4056,25 +4056,25 @@
         <v>6.499999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>12.50604356204457</v>
+        <v>12.37880035462277</v>
       </c>
       <c r="E44" t="n">
-        <v>5.537005760456983</v>
+        <v>5.183490015209006</v>
       </c>
       <c r="F44" t="n">
-        <v>1.512063095082627</v>
+        <v>1.551496076099506</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08508736182210397</v>
+        <v>0.03195695517542099</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0806090796209398</v>
+        <v>-0.02380247631305794</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.04419967569863407</v>
+        <v>0.01471127293890823</v>
       </c>
       <c r="K44" t="n">
         <v>1.59304854146272</v>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>0.4713981719546028</v>
+        <v>0.4473910577938021</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>5.89532607353244</v>
+        <v>5.538164584872975</v>
       </c>
     </row>
     <row r="45">
@@ -4139,25 +4139,25 @@
         <v>7.000000000000002</v>
       </c>
       <c r="D45" t="n">
-        <v>15.47358793967858</v>
+        <v>15.14395702649587</v>
       </c>
       <c r="E45" t="n">
-        <v>6.293213132069486</v>
+        <v>6.026231216574519</v>
       </c>
       <c r="F45" t="n">
-        <v>1.267095483844998</v>
+        <v>1.736837107563246</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.09392609548764849</v>
+        <v>-0.008059254539662348</v>
       </c>
       <c r="J45" t="n">
-        <v>0.03366712721215642</v>
+        <v>0.01866376470394637</v>
       </c>
       <c r="K45" t="n">
         <v>1.617459214584841</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>0.4376827638584523</v>
+        <v>0.4289057455504909</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>6.772522736245334</v>
+        <v>6.495330179033808</v>
       </c>
     </row>
     <row r="46">
@@ -4222,13 +4222,13 @@
         <v>7.716666666666667</v>
       </c>
       <c r="D46" t="n">
-        <v>20.35159733583168</v>
+        <v>19.97217392440739</v>
       </c>
       <c r="E46" t="n">
-        <v>6.949300834050835</v>
+        <v>7.32371717101417</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.2655219994815425</v>
+        <v>0.5631088264474462</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -4240,7 +4240,7 @@
         <v>-0.007855297157622764</v>
       </c>
       <c r="J46" t="n">
-        <v>0.06292700359626549</v>
+        <v>0.00671787429353536</v>
       </c>
       <c r="K46" t="n">
         <v>1.654681843835648</v>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>0.3720925468024087</v>
+        <v>0.3973264089171852</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>7.572677684186727</v>
+        <v>7.935472143654233</v>
       </c>
     </row>
     <row r="47">
@@ -4305,13 +4305,13 @@
         <v>8.35</v>
       </c>
       <c r="D47" t="n">
-        <v>24.83273153906999</v>
+        <v>24.9388816079963</v>
       </c>
       <c r="E47" t="n">
-        <v>6.120146902024114</v>
+        <v>6.982230984994462</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.122279871244019</v>
+        <v>-2.176264291227698</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>0.2734768576359868</v>
+        <v>0.3069957177739396</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>6.791177387822923</v>
+        <v>7.656129859726126</v>
       </c>
     </row>
     <row r="48">
@@ -4388,13 +4388,13 @@
         <v>8.966666666666667</v>
       </c>
       <c r="D48" t="n">
-        <v>28.03320623164211</v>
+        <v>28.72825012412826</v>
       </c>
       <c r="E48" t="n">
-        <v>4.323197358556811</v>
+        <v>4.657237977257827</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.620885258395538</v>
+        <v>-3.492331854128099</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>0.1744061835371289</v>
+        <v>0.182302697386951</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>4.889164511169961</v>
+        <v>5.237237488835593</v>
       </c>
     </row>
     <row r="49">
@@ -4471,13 +4471,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D49" t="n">
-        <v>30.89887988078042</v>
+        <v>30.97593657564373</v>
       </c>
       <c r="E49" t="n">
-        <v>2.233794122914519</v>
+        <v>1.702464341763148</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.703333547076863</v>
+        <v>-1.99122392921793</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -4524,19 +4524,19 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>0.07719764402011454</v>
+        <v>0.05986481881725748</v>
       </c>
       <c r="V49" t="n">
-        <v>0.002665044063479796</v>
+        <v>0.002658414417699906</v>
       </c>
       <c r="W49" t="n">
-        <v>0.002415380766685625</v>
+        <v>0.002465288474968639</v>
       </c>
       <c r="X49" t="n">
         <v>0.08234687639444917</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.385320729656766</v>
+        <v>1.854368830795771</v>
       </c>
     </row>
     <row r="50">
@@ -4554,13 +4554,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D50" t="n">
-        <v>32.44142377184905</v>
+        <v>32.06916300779451</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9335646748834137</v>
+        <v>0.8457530478826385</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.875063755176267</v>
+        <v>-0.4855263396745825</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -4607,19 +4607,19 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>0.01596779318247201</v>
+        <v>0.01356364238017025</v>
       </c>
       <c r="V50" t="n">
-        <v>0.001312865070175834</v>
+        <v>0.001328104886506724</v>
       </c>
       <c r="W50" t="n">
-        <v>0.001232617739754924</v>
+        <v>0.001259148530008072</v>
       </c>
       <c r="X50" t="n">
         <v>0.04259121209683257</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.5180179453338167</v>
+        <v>0.4349746584691095</v>
       </c>
     </row>
     <row r="51">
@@ -4637,13 +4637,13 @@
         <v>11.96666666666666</v>
       </c>
       <c r="D51" t="n">
-        <v>32.94154030130098</v>
+        <v>32.74125786872719</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3599284067761737</v>
+        <v>0.6248667002441746</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3857770911210205</v>
+        <v>-0.2052850684266847</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -4690,19 +4690,19 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>-0.01304869134972544</v>
+        <v>-0.004889975030627713</v>
       </c>
       <c r="V51" t="n">
-        <v>0.0008976812172023368</v>
+        <v>0.0009031724472148775</v>
       </c>
       <c r="W51" t="n">
-        <v>0.000974800236789819</v>
+        <v>0.0009322494558017368</v>
       </c>
       <c r="X51" t="n">
         <v>0.0295710019941917</v>
       </c>
       <c r="Y51" t="n">
-        <v>-0.4298439919762179</v>
+        <v>-0.1601039334494191</v>
       </c>
     </row>
     <row r="52">
@@ -4720,13 +4720,13 @@
         <v>12.96666666666667</v>
       </c>
       <c r="D52" t="n">
-        <v>33.11299292387466</v>
+        <v>33.26408713703984</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2193297400873746</v>
+        <v>0.4532018555371362</v>
       </c>
       <c r="F52" t="n">
-        <v>0.08441974228211516</v>
+        <v>-0.1408090739834827</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -4773,19 +4773,19 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>-0.02414546328281751</v>
+        <v>-0.01714478067395405</v>
       </c>
       <c r="V52" t="n">
-        <v>0.001199127514792181</v>
+        <v>0.001193680762936769</v>
       </c>
       <c r="W52" t="n">
-        <v>0.001366312353781091</v>
+        <v>0.001311853177397105</v>
       </c>
       <c r="X52" t="n">
         <v>0.03970670091213688</v>
       </c>
       <c r="Y52" t="n">
-        <v>-0.7995285548276116</v>
+        <v>-0.5703054782838444</v>
       </c>
     </row>
     <row r="53">
@@ -4803,13 +4803,13 @@
         <v>14.05</v>
       </c>
       <c r="D53" t="n">
-        <v>33.40678925938469</v>
+        <v>33.67334030860047</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5748685658658061</v>
+        <v>0.336871367418091</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4562261621977117</v>
+        <v>-0.08982491806961665</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -4856,19 +4856,19 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>-0.01490992801453295</v>
+        <v>-0.02211396666571151</v>
       </c>
       <c r="V53" t="n">
-        <v>0.002283368665355401</v>
+        <v>0.002265294001306065</v>
       </c>
       <c r="W53" t="n">
-        <v>0.002414683439122582</v>
+        <v>0.002458514514707374</v>
       </c>
       <c r="X53" t="n">
         <v>0.07628001580501038</v>
       </c>
       <c r="Y53" t="n">
-        <v>-0.4980928230540984</v>
+        <v>-0.7446511251075507</v>
       </c>
     </row>
     <row r="54">
@@ -4886,13 +4886,13 @@
         <v>14.93333333333333</v>
       </c>
       <c r="D54" t="n">
-        <v>34.13331149340144</v>
+        <v>33.94145095962335</v>
       </c>
       <c r="E54" t="n">
-        <v>1.070087435681565</v>
+        <v>0.2701716160299412</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6650241090832518</v>
+        <v>-0.06119338696015625</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -4939,19 +4939,19 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>0.0008903347551768859</v>
+        <v>-0.02249997190019291</v>
       </c>
       <c r="V54" t="n">
-        <v>0.00339667032848518</v>
+        <v>0.003415870656222101</v>
       </c>
       <c r="W54" t="n">
-        <v>0.00338653621268722</v>
+        <v>0.003673421235716655</v>
       </c>
       <c r="X54" t="n">
         <v>0.1159396063625789</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.03039007353185408</v>
+        <v>-0.763681692843301</v>
       </c>
     </row>
     <row r="55">
@@ -4972,10 +4972,10 @@
         <v>0.04347826086957973</v>
       </c>
       <c r="E55" t="n">
-        <v>0.05601730883899672</v>
+        <v>0.05539241075248286</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1159833450672381</v>
+        <v>0.1026405685546561</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -4984,10 +4984,10 @@
         <v>9.5</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2433140031949601</v>
+        <v>-0.716529056171157</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.6589878927144839</v>
+        <v>0.5791229930317843</v>
       </c>
       <c r="K55" t="n">
         <v>1.64693558111481</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>1.255335890111995</v>
+        <v>1.240963234122181</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.05457982130923539</v>
+        <v>0.05395492322272152</v>
       </c>
     </row>
     <row r="56">
@@ -5052,25 +5052,25 @@
         <v>0.6833333333333336</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1193331747856476</v>
+        <v>0.1168352151527269</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1659970733543725</v>
+        <v>0.1593108700762405</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2059086486363007</v>
+        <v>0.2015110197100003</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>9.497693139299184</v>
+        <v>9.105635635996398</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2500657906119801</v>
+        <v>-0.437708106766209</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.7850505281838773</v>
+        <v>0.2369383222997708</v>
       </c>
       <c r="K56" t="n">
         <v>1.61221262164786</v>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>1.361776606349538</v>
+        <v>1.334289649061833</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1625051257845154</v>
+        <v>0.1558920182241958</v>
       </c>
     </row>
     <row r="57">
@@ -5135,25 +5135,25 @@
         <v>1.716666666666666</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3767907633488045</v>
+        <v>0.3626480243210458</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4490280564003943</v>
+        <v>0.4447864876467248</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4102577227227512</v>
+        <v>0.4201441563038889</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>8.853813788310324</v>
+        <v>8.871180293458432</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.159777509317504</v>
+        <v>-0.46022100183162</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.2440436004914153</v>
+        <v>-0.6856675861344117</v>
       </c>
       <c r="K57" t="n">
         <v>1.569146791633991</v>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>1.169047255803026</v>
+        <v>1.203826371130069</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -5200,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.4404862079048471</v>
+        <v>0.4365652551158936</v>
       </c>
     </row>
     <row r="58">
@@ -5218,25 +5218,25 @@
         <v>2.149999999999998</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6076910589463265</v>
+        <v>0.5929873603067661</v>
       </c>
       <c r="E58" t="n">
-        <v>0.651585214058267</v>
+        <v>0.6529944237722252</v>
       </c>
       <c r="F58" t="n">
-        <v>0.535338813842497</v>
+        <v>0.5479059599717013</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>8.253719910901221</v>
+        <v>8.629350594609635</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.149896923472092</v>
+        <v>-0.8779843476295284</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.449765359540223e-06</v>
+        <v>-1.395868688688974</v>
       </c>
       <c r="K58" t="n">
         <v>1.554841242700892</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>1.052791528023522</v>
+        <v>1.081754998238168</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.639771998514335</v>
+        <v>0.6414670409039019</v>
       </c>
     </row>
     <row r="59">
@@ -5301,25 +5301,25 @@
         <v>2.616666666666665</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9714378052518284</v>
+        <v>0.9587505364055194</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9355337040373082</v>
+        <v>0.9425698129010216</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6652203920784994</v>
+        <v>0.6768825422824154</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>7.835171294969007</v>
+        <v>8.058846362850151</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.161357469609764</v>
+        <v>-1.746396628285529</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.152740602302694</v>
+        <v>-2.111964608948109</v>
       </c>
       <c r="K59" t="n">
         <v>1.542136954641748</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>0.9474529859143589</v>
+        <v>0.967535852789203</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.9203916492159363</v>
+        <v>0.92762551785322</v>
       </c>
     </row>
     <row r="60">
@@ -5384,25 +5384,25 @@
         <v>3.166666666666666</v>
       </c>
       <c r="D60" t="n">
-        <v>1.587152288473713</v>
+        <v>1.580094903073477</v>
       </c>
       <c r="E60" t="n">
-        <v>1.338197136092624</v>
+        <v>1.351391064761791</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7990699229985518</v>
+        <v>0.8097994291606467</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>7.02499302430417</v>
+        <v>6.758736816644348</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.526668677593472</v>
+        <v>-3.070731551769549</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.911487253641473</v>
+        <v>-2.043749925516509</v>
       </c>
       <c r="K60" t="n">
         <v>1.530981294268405</v>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>0.8324956677995398</v>
+        <v>0.8446115965716684</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.321297404292491</v>
+        <v>1.334566478819645</v>
       </c>
     </row>
     <row r="61">
@@ -5467,25 +5467,25 @@
         <v>3.666666666666665</v>
       </c>
       <c r="D61" t="n">
-        <v>2.355667337205196</v>
+        <v>2.356551360207286</v>
       </c>
       <c r="E61" t="n">
-        <v>1.768166003041393</v>
+        <v>1.786512625769871</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9231542483692654</v>
+        <v>0.9330191530199066</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>5.282741741696221</v>
+        <v>4.902054671117055</v>
       </c>
       <c r="I61" t="n">
-        <v>-4.177459231289498</v>
+        <v>-3.927092081098102</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.02775024523259</v>
+        <v>-0.734768093055103</v>
       </c>
       <c r="K61" t="n">
         <v>1.524640199129953</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>0.7447948559584689</v>
+        <v>0.7522986492445932</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -5532,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.754488915099814</v>
+        <v>1.77283040515945</v>
       </c>
     </row>
     <row r="62">
@@ -5550,25 +5550,25 @@
         <v>4.166666666666667</v>
       </c>
       <c r="D62" t="n">
-        <v>3.355318291515109</v>
+        <v>3.366607528843351</v>
       </c>
       <c r="E62" t="n">
-        <v>2.261351384461891</v>
+        <v>2.284410217781698</v>
       </c>
       <c r="F62" t="n">
-        <v>1.056663664944954</v>
+        <v>1.065598295420997</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2.847533793014665</v>
+        <v>2.831644735546242</v>
       </c>
       <c r="I62" t="n">
-        <v>-4.554418922826057</v>
+        <v>-3.805499644824648</v>
       </c>
       <c r="J62" t="n">
-        <v>1.214972641854724</v>
+        <v>1.272672679605255</v>
       </c>
       <c r="K62" t="n">
         <v>1.522129179305727</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>0.6733096571198872</v>
+        <v>0.6778989462490556</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.259168208388123</v>
+        <v>2.282219696237044</v>
       </c>
     </row>
     <row r="63">
@@ -5633,25 +5633,25 @@
         <v>4.649999999999998</v>
       </c>
       <c r="D63" t="n">
-        <v>4.570740132440116</v>
+        <v>4.594224977164805</v>
       </c>
       <c r="E63" t="n">
-        <v>2.804914561779411</v>
+        <v>2.832062958726937</v>
       </c>
       <c r="F63" t="n">
-        <v>1.187569477169255</v>
+        <v>1.195591975006719</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7938721223074401</v>
+        <v>1.148988968510205</v>
       </c>
       <c r="I63" t="n">
-        <v>-3.047272038727226</v>
+        <v>-2.709374935384301</v>
       </c>
       <c r="J63" t="n">
-        <v>3.081272601458775</v>
+        <v>2.29513168449791</v>
       </c>
       <c r="K63" t="n">
         <v>1.523534166455679</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="U63" t="n">
-        <v>0.6182915682099216</v>
+        <v>0.6210638555092903</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.826050084366424</v>
+        <v>2.853307077395055</v>
       </c>
     </row>
     <row r="64">
@@ -5716,13 +5716,13 @@
         <v>5.500000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>7.38878924966134</v>
+        <v>7.438214479573144</v>
       </c>
       <c r="E64" t="n">
-        <v>3.908456993140764</v>
+        <v>3.941768779790767</v>
       </c>
       <c r="F64" t="n">
-        <v>1.367027855449776</v>
+        <v>1.354245977252376</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -5731,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4834426397550148</v>
+        <v>-0.7177229584811761</v>
       </c>
       <c r="J64" t="n">
-        <v>1.831133949063606</v>
+        <v>1.588964587857402</v>
       </c>
       <c r="K64" t="n">
         <v>1.535708118407536</v>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="U64" t="n">
-        <v>0.5433871738107342</v>
+        <v>0.5443507466733761</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>4.014973308256611</v>
+        <v>4.048997605872358</v>
       </c>
     </row>
     <row r="65">
@@ -5799,25 +5799,25 @@
         <v>6.499999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>11.99501693754041</v>
+        <v>12.08104064401971</v>
       </c>
       <c r="E65" t="n">
-        <v>5.35635854515934</v>
+        <v>5.353320306663477</v>
       </c>
       <c r="F65" t="n">
-        <v>1.261741561897927</v>
+        <v>0.9344531791093651</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0465862578445318</v>
+        <v>0.012</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.04658625784453122</v>
+        <v>-0.01599999999999988</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1888844893610437</v>
+        <v>0.2363916710919004</v>
       </c>
       <c r="K65" t="n">
         <v>1.567042522912585</v>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>0.4724666221316637</v>
+        <v>0.4690354601005478</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>5.667245134891812</v>
+        <v>5.666436456961203</v>
       </c>
     </row>
     <row r="66">
@@ -5882,13 +5882,13 @@
         <v>7.000000000000002</v>
       </c>
       <c r="D66" t="n">
-        <v>14.86072892444016</v>
+        <v>14.93532433290569</v>
       </c>
       <c r="E66" t="n">
-        <v>5.940689328578143</v>
+        <v>5.701272309277323</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8561081408892193</v>
+        <v>0.4084376969089329</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -5900,7 +5900,7 @@
         <v>-0.01413698630136974</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0463344955428722</v>
+        <v>0.01030136986301366</v>
       </c>
       <c r="K66" t="n">
         <v>1.589669852465964</v>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>0.4297126692261488</v>
+        <v>0.4116858025337201</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>6.385843492767417</v>
+        <v>6.148660984093677</v>
       </c>
     </row>
     <row r="67">
@@ -5965,13 +5965,13 @@
         <v>7.716666666666667</v>
       </c>
       <c r="D67" t="n">
-        <v>19.33318496602436</v>
+        <v>19.01374249808414</v>
       </c>
       <c r="E67" t="n">
-        <v>6.233171671449554</v>
+        <v>5.69869421201685</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1979498739135295</v>
+        <v>0.7311813029352114</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>0.3533671646292537</v>
+        <v>0.3306737531422033</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>6.831712754696941</v>
+        <v>6.287345593120893</v>
       </c>
     </row>
     <row r="68">
@@ -6048,13 +6048,13 @@
         <v>8.35</v>
       </c>
       <c r="D68" t="n">
-        <v>23.27668245980639</v>
+        <v>22.62732483003128</v>
       </c>
       <c r="E68" t="n">
-        <v>5.768595073303436</v>
+        <v>6.57302390838727</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.518381183979009</v>
+        <v>-0.3643376804520155</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>0.2750826662581736</v>
+        <v>0.3177460092061178</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>6.403011872688403</v>
+        <v>7.189742163752938</v>
       </c>
     </row>
     <row r="69">
@@ -6131,13 +6131,13 @@
         <v>9.066666666666665</v>
       </c>
       <c r="D69" t="n">
-        <v>27.03943661922263</v>
+        <v>28.04139664979665</v>
       </c>
       <c r="E69" t="n">
-        <v>4.043944849087982</v>
+        <v>4.896896416768156</v>
       </c>
       <c r="F69" t="n">
-        <v>-2.400988013905154</v>
+        <v>-3.234733537074055</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>0.1673255930795769</v>
+        <v>0.1923992778945267</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>4.524389768849058</v>
+        <v>5.395144466574874</v>
       </c>
     </row>
     <row r="70">
@@ -6214,13 +6214,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D70" t="n">
-        <v>29.27979654368249</v>
+        <v>29.50002045375516</v>
       </c>
       <c r="E70" t="n">
-        <v>1.968853614753954</v>
+        <v>1.154448483606217</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.792138006022656</v>
+        <v>-2.599403986552142</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -6267,19 +6267,19 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>0.0679577701438254</v>
+        <v>0.03984885440305574</v>
       </c>
       <c r="V70" t="n">
-        <v>0.002171392694003044</v>
+        <v>0.002155182786958192</v>
       </c>
       <c r="W70" t="n">
-        <v>0.002036109500216239</v>
+        <v>0.002076448063670487</v>
       </c>
       <c r="X70" t="n">
         <v>0.06357793629684773</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.989789683373548</v>
+        <v>1.175542019948856</v>
       </c>
     </row>
     <row r="71">
@@ -6297,13 +6297,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D71" t="n">
-        <v>30.58525753746805</v>
+        <v>30.03193620630886</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8382629088769171</v>
+        <v>0.6948205432293904</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.736254002251828</v>
+        <v>-0.145240400931089</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -6350,19 +6350,19 @@
         </is>
       </c>
       <c r="U71" t="n">
-        <v>0.005384674261734224</v>
+        <v>0.001113312725761866</v>
       </c>
       <c r="V71" t="n">
-        <v>0.001637513087263281</v>
+        <v>0.00166768333386379</v>
       </c>
       <c r="W71" t="n">
-        <v>0.001615860851638156</v>
+        <v>0.001663124127076932</v>
       </c>
       <c r="X71" t="n">
         <v>0.05008375949492182</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.1646916490505168</v>
+        <v>0.03343493675775222</v>
       </c>
     </row>
     <row r="72">
@@ -6380,13 +6380,13 @@
         <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>31.09951252865547</v>
+        <v>30.88306102035976</v>
       </c>
       <c r="E72" t="n">
-        <v>0.3742258271403891</v>
+        <v>0.7859965146668575</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.330239523885744</v>
+        <v>-0.1340465429635165</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -6433,19 +6433,19 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>-0.02574787930166702</v>
+        <v>-0.01233032053743415</v>
       </c>
       <c r="V72" t="n">
-        <v>0.001117690791236708</v>
+        <v>0.001125524401299257</v>
       </c>
       <c r="W72" t="n">
-        <v>0.001257526630730451</v>
+        <v>0.001192959288930269</v>
       </c>
       <c r="X72" t="n">
         <v>0.03475963876522885</v>
       </c>
       <c r="Y72" t="n">
-        <v>-0.8007464949285026</v>
+        <v>-0.3807980415581744</v>
       </c>
     </row>
     <row r="73">
@@ -6463,13 +6463,13 @@
         <v>13</v>
       </c>
       <c r="D73" t="n">
-        <v>31.3105361887845</v>
+        <v>31.57132226167865</v>
       </c>
       <c r="E73" t="n">
-        <v>0.198950616907771</v>
+        <v>0.415708750928097</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.03027597005130039</v>
+        <v>-0.3471285004430657</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -6516,19 +6516,19 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>-0.04218450406868358</v>
+        <v>-0.03537132505043111</v>
       </c>
       <c r="V73" t="n">
-        <v>0.0005439678299067449</v>
+        <v>0.0005394745358670995</v>
       </c>
       <c r="W73" t="n">
-        <v>0.0008180953476856608</v>
+        <v>0.0007674293396487528</v>
       </c>
       <c r="X73" t="n">
         <v>0.01703192442382971</v>
       </c>
       <c r="Y73" t="n">
-        <v>-1.320819441248444</v>
+        <v>-1.116719501989747</v>
       </c>
     </row>
     <row r="74">
@@ -6546,13 +6546,13 @@
         <v>14.05</v>
       </c>
       <c r="D74" t="n">
-        <v>31.50612380638622</v>
+        <v>31.7073273294973</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3270225106538085</v>
+        <v>0.07675691324638123</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2020212066664041</v>
+        <v>-0.2010329824318151</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -6599,19 +6599,19 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>-0.04305609581154686</v>
+        <v>-0.05101495077145059</v>
       </c>
       <c r="V74" t="n">
-        <v>-6.983484559359728e-05</v>
+        <v>-6.939169827867749e-05</v>
       </c>
       <c r="W74" t="n">
-        <v>0.0002352937468371053</v>
+        <v>0.0002898453091343708</v>
       </c>
       <c r="X74" t="n">
         <v>-0.002200225291271741</v>
       </c>
       <c r="Y74" t="n">
-        <v>-1.356530685258223</v>
+        <v>-1.617547742808574</v>
       </c>
     </row>
     <row r="75">
@@ -6629,13 +6629,13 @@
         <v>14.91666666666667</v>
       </c>
       <c r="D75" t="n">
-        <v>31.89022696244574</v>
+        <v>31.73610005685744</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5593693879450825</v>
+        <v>-0.01035831164603707</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3341638947749972</v>
+        <v>-2.151935303947722e-06</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="U75" t="n">
-        <v>-0.03694101358039363</v>
+        <v>-0.05480786681970858</v>
       </c>
       <c r="V75" t="n">
-        <v>-0.0005525454326814507</v>
+        <v>-0.0005552288789014829</v>
       </c>
       <c r="W75" t="n">
-        <v>-0.0002917087220623052</v>
+        <v>-0.0001663567120984929</v>
       </c>
       <c r="X75" t="n">
         <v>-0.01762079925527425</v>
       </c>
       <c r="Y75" t="n">
-        <v>-1.178057307301543</v>
+        <v>-1.739387945293189</v>
       </c>
     </row>
     <row r="76">
@@ -6715,10 +6715,10 @@
         <v>0.1343209876543128</v>
       </c>
       <c r="E76" t="n">
-        <v>0.450504276982719</v>
+        <v>0.3207997556994401</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.4951889718096523</v>
+        <v>-0.3066531612091995</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6727,10 +6727,10 @@
         <v>12.332</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3482412914777129</v>
+        <v>-0.3116853316994579</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.4025783870181464</v>
+        <v>-0.5061904718760818</v>
       </c>
       <c r="K76" t="n">
         <v>1.778200175321474</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>3.34209098337321</v>
+        <v>2.376459896613446</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.448912961717263</v>
+        <v>0.3192084404339841</v>
       </c>
     </row>
     <row r="77">
@@ -6795,25 +6795,25 @@
         <v>0.75</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3776507545668253</v>
+        <v>0.326149841973539</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1983751014506477</v>
+        <v>0.1907438558184966</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.1771554962758713</v>
+        <v>-0.04016257180665003</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>11.92577490386271</v>
+        <v>11.93233052024019</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.7350256315550787</v>
+        <v>-0.7540999476600305</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.6288465198548291</v>
+        <v>-0.6735818373521119</v>
       </c>
       <c r="K77" t="n">
         <v>1.762459288572748</v>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>0.5134235522310283</v>
+        <v>0.5729714079237874</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.1938947919124277</v>
+        <v>0.1868745341496994</v>
       </c>
     </row>
     <row r="78">
@@ -6878,25 +6878,25 @@
         <v>1.416666666666666</v>
       </c>
       <c r="D78" t="n">
-        <v>0.435195881302199</v>
+        <v>0.4147773310729978</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1745035781656314</v>
+        <v>0.2429289825851887</v>
       </c>
       <c r="F78" t="n">
-        <v>0.284696234276858</v>
+        <v>0.3405170093750408</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>11.32115504872899</v>
+        <v>11.29851140966371</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.221299054521018</v>
+        <v>-1.252751947517298</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.949494138201125</v>
+        <v>-0.9171055936733736</v>
       </c>
       <c r="K78" t="n">
         <v>1.748566468720244</v>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>0.3892490967492305</v>
+        <v>0.5739572992901764</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.1693996037058663</v>
+        <v>0.2380644767494451</v>
       </c>
     </row>
     <row r="79">
@@ -6961,25 +6961,25 @@
         <v>2.083333333333334</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6103221921210011</v>
+        <v>0.6500551520871247</v>
       </c>
       <c r="E79" t="n">
-        <v>0.5779700804864603</v>
+        <v>0.6447665349852193</v>
       </c>
       <c r="F79" t="n">
-        <v>0.903122070130195</v>
+        <v>0.8450116625035167</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>10.29737616450135</v>
+        <v>10.26199459021713</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.001017815823247</v>
+        <v>-1.976907405891197</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.370708445272331</v>
+        <v>-1.273903336105778</v>
       </c>
       <c r="K79" t="n">
         <v>1.735116387039626</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>0.9357006116599159</v>
+        <v>0.9805732184429676</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.5710788484772414</v>
+        <v>0.6374266726475046</v>
       </c>
     </row>
     <row r="80">
@@ -7044,25 +7044,25 @@
         <v>2.75</v>
       </c>
       <c r="D80" t="n">
-        <v>1.205822655284145</v>
+        <v>1.274466044386622</v>
       </c>
       <c r="E80" t="n">
-        <v>1.378666338339224</v>
+        <v>1.369611199256544</v>
       </c>
       <c r="F80" t="n">
-        <v>1.264586055855156</v>
+        <v>1.156606160916698</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>8.653131294297996</v>
+        <v>8.662634868475449</v>
       </c>
       <c r="I80" t="n">
-        <v>-3.048910314884125</v>
+        <v>-2.951289728991668</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.62946446322546</v>
+        <v>-1.646407728728741</v>
       </c>
       <c r="K80" t="n">
         <v>1.722444550951895</v>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>1.133397134076784</v>
+        <v>1.064711167499284</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.366675941703907</v>
+        <v>1.356938230057074</v>
       </c>
     </row>
     <row r="81">
@@ -7127,25 +7127,25 @@
         <v>3.583333333333333</v>
       </c>
       <c r="D81" t="n">
-        <v>2.860352565977776</v>
+        <v>2.866845023774675</v>
       </c>
       <c r="E81" t="n">
-        <v>2.498677290172695</v>
+        <v>2.405677963051405</v>
       </c>
       <c r="F81" t="n">
-        <v>1.192724896179069</v>
+        <v>1.158856535692838</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>5.505557063582999</v>
+        <v>5.62796619183745</v>
       </c>
       <c r="I81" t="n">
-        <v>-4.466824153649238</v>
+        <v>-4.515831840513568</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.1653860952156205</v>
+        <v>-0.3065132117171383</v>
       </c>
       <c r="K81" t="n">
         <v>1.710130129992031</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="U81" t="n">
-        <v>0.8699959264087201</v>
+        <v>0.8355780036318021</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.488495080493395</v>
+        <v>2.395472641687409</v>
       </c>
     </row>
     <row r="82">
@@ -7210,25 +7210,25 @@
         <v>4.533333333333332</v>
       </c>
       <c r="D82" t="n">
-        <v>5.789936424961421</v>
+        <v>5.688132601045467</v>
       </c>
       <c r="E82" t="n">
-        <v>3.467920771101963</v>
+        <v>3.415160933887142</v>
       </c>
       <c r="F82" t="n">
-        <v>0.862035600728823</v>
+        <v>0.97158591235512</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.5150910294513114</v>
+        <v>0.352</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.960333260363453</v>
+        <v>-3.105694271800648</v>
       </c>
       <c r="J82" t="n">
-        <v>2.159236984418583</v>
+        <v>2.175871313460834</v>
       </c>
       <c r="K82" t="n">
         <v>1.713757703395073</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>0.6124072943974128</v>
+        <v>0.6138517469073569</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.545799300743653</v>
+        <v>3.491670133792448</v>
       </c>
     </row>
     <row r="83">
@@ -7293,13 +7293,13 @@
         <v>5.55</v>
       </c>
       <c r="D83" t="n">
-        <v>9.733613705846061</v>
+        <v>9.64479646900147</v>
       </c>
       <c r="E83" t="n">
-        <v>4.172177665163508</v>
+        <v>4.303900697751645</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9103926758786844</v>
+        <v>1.030596710109098</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>-0.1411809645074009</v>
       </c>
       <c r="J83" t="n">
-        <v>1.250157799691256</v>
+        <v>1.308459526385786</v>
       </c>
       <c r="K83" t="n">
         <v>1.758118475380813</v>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="U83" t="n">
-        <v>0.4690256517571912</v>
+        <v>0.4866303054277152</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.565314512337178</v>
+        <v>4.693450251498335</v>
       </c>
     </row>
     <row r="84">
@@ -7376,13 +7376,13 @@
         <v>6.250000000000001</v>
       </c>
       <c r="D84" t="n">
-        <v>12.79542716074397</v>
+        <v>12.85614572879914</v>
       </c>
       <c r="E84" t="n">
-        <v>4.914367632015827</v>
+        <v>5.100710815266788</v>
       </c>
       <c r="F84" t="n">
-        <v>1.285203684034701</v>
+        <v>1.252926991670684</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="U84" t="n">
-        <v>0.4392727070930371</v>
+        <v>0.4519532471052569</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.620681927311779</v>
+        <v>5.810376807389153</v>
       </c>
     </row>
     <row r="85">
@@ -7459,13 +7459,13 @@
         <v>7.499999999999999</v>
       </c>
       <c r="D85" t="n">
-        <v>20.14452154615013</v>
+        <v>20.37727758617688</v>
       </c>
       <c r="E85" t="n">
-        <v>7.02295327013309</v>
+        <v>6.922733000819225</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5727788366421391</v>
+        <v>0.3144761537110412</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>0.4075229093676315</v>
+        <v>0.3986225228757163</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>8.209354028306038</v>
+        <v>8.122841800740616</v>
       </c>
     </row>
     <row r="86">
@@ -7542,13 +7542,13 @@
         <v>8.333333333333332</v>
       </c>
       <c r="D86" t="n">
-        <v>26.63235913893223</v>
+        <v>26.64945926181347</v>
       </c>
       <c r="E86" t="n">
-        <v>6.881330259639498</v>
+        <v>6.549717798505696</v>
       </c>
       <c r="F86" t="n">
-        <v>-2.381739434911003</v>
+        <v>-2.446093726057599</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="U86" t="n">
-        <v>0.3024762830406257</v>
+        <v>0.2898669904112506</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>8.05565700094726</v>
+        <v>7.724798552309098</v>
       </c>
     </row>
     <row r="87">
@@ -7625,13 +7625,13 @@
         <v>8.783333333333335</v>
       </c>
       <c r="D87" t="n">
-        <v>29.50926756680715</v>
+        <v>29.3594455195623</v>
       </c>
       <c r="E87" t="n">
-        <v>5.27208210110609</v>
+        <v>4.963346079342391</v>
       </c>
       <c r="F87" t="n">
-        <v>-3.571139213634964</v>
+        <v>-3.43967671874627</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="U87" t="n">
-        <v>0.2080857642341618</v>
+        <v>0.1984817328435625</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>6.14045849362943</v>
+        <v>5.827313622048893</v>
       </c>
     </row>
     <row r="88">
@@ -7708,13 +7708,13 @@
         <v>10.06666666666667</v>
       </c>
       <c r="D88" t="n">
-        <v>32.1722099408478</v>
+        <v>31.85382879710079</v>
       </c>
       <c r="E88" t="n">
-        <v>0.707301664466268</v>
+        <v>0.8623569150695829</v>
       </c>
       <c r="F88" t="n">
-        <v>-1.942919424195476</v>
+        <v>-1.752467504723467</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -7761,19 +7761,19 @@
         </is>
       </c>
       <c r="U88" t="n">
-        <v>0.01725440175726392</v>
+        <v>0.02234185349890289</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001188027837066629</v>
+        <v>0.001199902254549623</v>
       </c>
       <c r="W88" t="n">
-        <v>0.001165302101415717</v>
+        <v>0.001170181728185258</v>
       </c>
       <c r="X88" t="n">
         <v>0.03822148098967892</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.5551122357384279</v>
+        <v>0.7116735763639597</v>
       </c>
     </row>
     <row r="89">
@@ -7791,13 +7791,13 @@
         <v>11.11666666666667</v>
       </c>
       <c r="D89" t="n">
-        <v>31.73988227303304</v>
+        <v>31.83035277974918</v>
       </c>
       <c r="E89" t="n">
-        <v>0.05385396511644558</v>
+        <v>0.2620274003173293</v>
       </c>
       <c r="F89" t="n">
-        <v>0.02705240706237722</v>
+        <v>-0.0744549171525824</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -7844,19 +7844,19 @@
         </is>
       </c>
       <c r="U89" t="n">
-        <v>-0.01067550311139266</v>
+        <v>-0.004140233686431001</v>
       </c>
       <c r="V89" t="n">
-        <v>0.001360364769149424</v>
+        <v>0.001356498243043499</v>
       </c>
       <c r="W89" t="n">
-        <v>0.001389747358315305</v>
+        <v>0.001367861175509034</v>
       </c>
       <c r="X89" t="n">
         <v>0.0431778176211845</v>
       </c>
       <c r="Y89" t="n">
-        <v>-0.3388392119610011</v>
+        <v>-0.1317850988297001</v>
       </c>
     </row>
     <row r="90">
@@ -7874,13 +7874,13 @@
         <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>32.13344672385298</v>
+        <v>32.27314335993289</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5603212606629562</v>
+        <v>0.5658040026736622</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3437661981741477</v>
+        <v>0.200859545251626</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -7927,19 +7927,19 @@
         </is>
       </c>
       <c r="U90" t="n">
-        <v>0.00785090253290148</v>
+        <v>0.007945309412866825</v>
       </c>
       <c r="V90" t="n">
-        <v>0.001410039768395712</v>
+        <v>0.001403936309238141</v>
       </c>
       <c r="W90" t="n">
-        <v>0.001378887229783353</v>
+        <v>0.001372545629770688</v>
       </c>
       <c r="X90" t="n">
         <v>0.04530943777625759</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.2522765582751521</v>
+        <v>0.2564201097204752</v>
       </c>
     </row>
     <row r="91">
@@ -7957,13 +7957,13 @@
         <v>12.91666666666667</v>
       </c>
       <c r="D91" t="n">
-        <v>32.75625668859781</v>
+        <v>32.85318326629564</v>
       </c>
       <c r="E91" t="n">
-        <v>0.6570381253092883</v>
+        <v>0.6138587594580578</v>
       </c>
       <c r="F91" t="n">
-        <v>0.04067714968584588</v>
+        <v>0.01312591605095265</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -8010,19 +8010,19 @@
         </is>
       </c>
       <c r="U91" t="n">
-        <v>0.01320014848713912</v>
+        <v>0.01182665729059543</v>
       </c>
       <c r="V91" t="n">
-        <v>0.001449561274254363</v>
+        <v>0.001445284641078882</v>
       </c>
       <c r="W91" t="n">
-        <v>0.001380575143152895</v>
+        <v>0.001383658951160251</v>
       </c>
       <c r="X91" t="n">
         <v>0.04748220118532685</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.432387452172335</v>
+        <v>0.3885433393956031</v>
       </c>
     </row>
     <row r="92">
@@ -8040,13 +8040,13 @@
         <v>14.16666666666667</v>
       </c>
       <c r="D92" t="n">
-        <v>33.53938799215553</v>
+        <v>33.5882702710447</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5973752035511506</v>
+        <v>0.563281856249187</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.04659673704326886</v>
+        <v>-0.03965254189883066</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -8093,19 +8093,19 @@
         </is>
       </c>
       <c r="U92" t="n">
-        <v>0.01386777576349243</v>
+        <v>0.01282681721411007</v>
       </c>
       <c r="V92" t="n">
-        <v>0.001498633967497358</v>
+        <v>0.001496452948857194</v>
       </c>
       <c r="W92" t="n">
-        <v>0.001401997188973545</v>
+        <v>0.001407200111008052</v>
       </c>
       <c r="X92" t="n">
         <v>0.05026326609411727</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.4651167119199837</v>
+        <v>0.4308306033048176</v>
       </c>
     </row>
     <row r="93">
@@ -8123,13 +8123,13 @@
         <v>15.75</v>
       </c>
       <c r="D93" t="n">
-        <v>34.42681055341428</v>
+        <v>34.4304200052972</v>
       </c>
       <c r="E93" t="n">
-        <v>0.5258705350722535</v>
+        <v>0.5021211205829497</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.04347434076316148</v>
+        <v>-0.03742428023697117</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -8176,19 +8176,19 @@
         </is>
       </c>
       <c r="U93" t="n">
-        <v>0.01453966378119044</v>
+        <v>0.01384828246872307</v>
       </c>
       <c r="V93" t="n">
-        <v>0.001555928175116516</v>
+        <v>0.001555765062151862</v>
       </c>
       <c r="W93" t="n">
-        <v>0.001422008993618066</v>
+        <v>0.001428227296302813</v>
       </c>
       <c r="X93" t="n">
         <v>0.0535656445194559</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.5005542505053826</v>
+        <v>0.4768021817501293</v>
       </c>
     </row>
     <row r="94">
@@ -8206,13 +8206,13 @@
         <v>17.75</v>
       </c>
       <c r="D94" t="n">
-        <v>35.39112373630353</v>
+        <v>35.35947170641381</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4431824914069873</v>
+        <v>0.4303131145899908</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.03983935126362285</v>
+        <v>-0.03483021240685444</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -8259,19 +8259,19 @@
         </is>
       </c>
       <c r="U94" t="n">
-        <v>0.01483565883992953</v>
+        <v>0.01448290988117382</v>
       </c>
       <c r="V94" t="n">
-        <v>0.001610135080234354</v>
+        <v>0.001611576392596405</v>
       </c>
       <c r="W94" t="n">
-        <v>0.001430900348563791</v>
+        <v>0.001436446716125748</v>
       </c>
       <c r="X94" t="n">
         <v>0.05698448985673704</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.5250506377135312</v>
+        <v>0.5121080421699066</v>
       </c>
     </row>
     <row r="95">
@@ -8289,13 +8289,13 @@
         <v>22.08333333333333</v>
       </c>
       <c r="D95" t="n">
-        <v>36.94565770426932</v>
+        <v>36.90294229304569</v>
       </c>
       <c r="E95" t="n">
-        <v>0.284672487384773</v>
+        <v>0.2894638946962118</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.0330118757323387</v>
+        <v>-0.02995786418167946</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -8342,19 +8342,19 @@
         </is>
       </c>
       <c r="U95" t="n">
-        <v>0.01374954112533501</v>
+        <v>0.01388829799400032</v>
       </c>
       <c r="V95" t="n">
-        <v>0.001674330666669242</v>
+        <v>0.001676268716009134</v>
       </c>
       <c r="W95" t="n">
-        <v>0.00142226601502559</v>
+        <v>0.001421365581058319</v>
       </c>
       <c r="X95" t="n">
         <v>0.06185924769452287</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.5079858400074013</v>
+        <v>0.5125190594212161</v>
       </c>
     </row>
     <row r="96">
@@ -8372,13 +8372,13 @@
         <v>23.75</v>
       </c>
       <c r="D96" t="n">
-        <v>37.37263356747</v>
+        <v>37.34261184491389</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2319394611418337</v>
+        <v>0.2411660453854987</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.02992349343528483</v>
+        <v>-0.02775387620182451</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -8425,19 +8425,19 @@
         </is>
       </c>
       <c r="U96" t="n">
-        <v>0.0125649815468165</v>
+        <v>0.01281705022982444</v>
       </c>
       <c r="V96" t="n">
-        <v>0.001663619557944517</v>
+        <v>0.001664957030669107</v>
       </c>
       <c r="W96" t="n">
-        <v>0.001403505201260744</v>
+        <v>0.001399411151259112</v>
       </c>
       <c r="X96" t="n">
         <v>0.06217384413473686</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.4695864511311953</v>
+        <v>0.4786221317290983</v>
       </c>
     </row>
     <row r="97">
@@ -8455,13 +8455,13 @@
         <v>26.25</v>
       </c>
       <c r="D97" t="n">
-        <v>37.86155950740491</v>
+        <v>37.8606431368698</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1635669362179168</v>
+        <v>0.1763744800731999</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.02503796202126905</v>
+        <v>-0.02426737373029872</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -8508,19 +8508,19 @@
         </is>
       </c>
       <c r="U97" t="n">
-        <v>0.009856556106216902</v>
+        <v>0.0101949418713682</v>
       </c>
       <c r="V97" t="n">
-        <v>0.001584682353749132</v>
+        <v>0.001584720709046247</v>
       </c>
       <c r="W97" t="n">
-        <v>0.001346558041265088</v>
+        <v>0.001338415381262659</v>
       </c>
       <c r="X97" t="n">
         <v>0.05999854523680726</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.3731845855536065</v>
+        <v>0.3859870559930031</v>
       </c>
     </row>
     <row r="98">
@@ -8538,13 +8538,13 @@
         <v>27.91666666666667</v>
       </c>
       <c r="D98" t="n">
-        <v>38.09861169026139</v>
+        <v>38.12033611842607</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1244048305694658</v>
+        <v>0.1377613598500584</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.02190141821751917</v>
+        <v>-0.02202901585331096</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -8591,19 +8591,19 @@
         </is>
       </c>
       <c r="U98" t="n">
-        <v>0.007919468046409125</v>
+        <v>0.008267985217046022</v>
       </c>
       <c r="V98" t="n">
-        <v>0.001499635808012634</v>
+        <v>0.001498781179389131</v>
       </c>
       <c r="W98" t="n">
-        <v>0.001290809087633514</v>
+        <v>0.00128088873168627</v>
       </c>
       <c r="X98" t="n">
         <v>0.05713404232628472</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.3017207378935743</v>
+        <v>0.3151783754959723</v>
       </c>
     </row>
     <row r="99">
@@ -8621,13 +8621,13 @@
         <v>30.78333333333333</v>
       </c>
       <c r="D99" t="n">
-        <v>38.36734244472576</v>
+        <v>38.42623164499421</v>
       </c>
       <c r="E99" t="n">
-        <v>0.06948934560510711</v>
+        <v>0.08022683510465001</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.01674483575858813</v>
+        <v>-0.01834908096718654</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -8674,19 +8674,19 @@
         </is>
       </c>
       <c r="U99" t="n">
-        <v>0.005052211606982032</v>
+        <v>0.005328867197648854</v>
       </c>
       <c r="V99" t="n">
-        <v>0.001306261603118239</v>
+        <v>0.00130425972320819</v>
       </c>
       <c r="W99" t="n">
-        <v>0.001155140604225533</v>
+        <v>0.001145107722561769</v>
       </c>
       <c r="X99" t="n">
         <v>0.05011778624923392</v>
       </c>
       <c r="Y99" t="n">
-        <v>0.1938399328282979</v>
+        <v>0.204768285342266</v>
       </c>
     </row>
     <row r="100">
@@ -8704,13 +8704,13 @@
         <v>33.71666666666666</v>
       </c>
       <c r="D100" t="n">
-        <v>38.49837843298384</v>
+        <v>38.58207991880084</v>
       </c>
       <c r="E100" t="n">
-        <v>0.02761008611919902</v>
+        <v>0.03156883889350492</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.0117309675131365</v>
+        <v>-0.01477099241380605</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -8757,19 +8757,19 @@
         </is>
       </c>
       <c r="U100" t="n">
-        <v>0.00282988831759466</v>
+        <v>0.002930938446158824</v>
       </c>
       <c r="V100" t="n">
-        <v>0.001060169505293938</v>
+        <v>0.00105786953175706</v>
       </c>
       <c r="W100" t="n">
-        <v>0.0009665769365223807</v>
+        <v>0.0009611452374981006</v>
       </c>
       <c r="X100" t="n">
         <v>0.04081480681791529</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.1089461113738392</v>
+        <v>0.1130817013667857</v>
       </c>
     </row>
     <row r="101">
@@ -8787,13 +8787,13 @@
         <v>36.74999999999999</v>
       </c>
       <c r="D101" t="n">
-        <v>38.52861220710172</v>
+        <v>38.610206628559</v>
       </c>
       <c r="E101" t="n">
-        <v>1.246305529534197e-05</v>
+        <v>-0.007537166611712109</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.005293057087266991</v>
+        <v>-0.007252583323883788</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -8840,19 +8840,19 @@
         </is>
       </c>
       <c r="U101" t="n">
-        <v>0.001271592252182027</v>
+        <v>0.001076057011114318</v>
       </c>
       <c r="V101" t="n">
-        <v>0.0007537726782938218</v>
+        <v>0.0007521797408048471</v>
       </c>
       <c r="W101" t="n">
-        <v>0.0007084201026021043</v>
+        <v>0.0007138822248728211</v>
       </c>
       <c r="X101" t="n">
         <v>0.0290418152142911</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.04899268476987639</v>
+        <v>0.04154678354323343</v>
       </c>
     </row>
     <row r="102">
@@ -8870,13 +8870,13 @@
         <v>39.24999999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>38.50813227567679</v>
+        <v>38.55672832406908</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.005380082671812447</v>
+        <v>-0.01404876282709977</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.001030988424734784</v>
+        <v>-0.0004380237515939963</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -8923,19 +8923,19 @@
         </is>
       </c>
       <c r="U102" t="n">
-        <v>0.0007532701297637439</v>
+        <v>0.0005286169748632762</v>
       </c>
       <c r="V102" t="n">
-        <v>0.0004502963104570966</v>
+        <v>0.0004497287669375862</v>
       </c>
       <c r="W102" t="n">
-        <v>0.0004223217800877304</v>
+        <v>0.0004301220245453036</v>
       </c>
       <c r="X102" t="n">
         <v>0.01734006988633109</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.02900702579625847</v>
+        <v>0.0203817410872946</v>
       </c>
     </row>
     <row r="103">
@@ -8953,13 +8953,13 @@
         <v>46.53333333333333</v>
       </c>
       <c r="D103" t="n">
-        <v>38.52861220710172</v>
+        <v>38.610206628559</v>
       </c>
       <c r="E103" t="n">
-        <v>0.01100386246812946</v>
+        <v>0.0287338807648343</v>
       </c>
       <c r="F103" t="n">
-        <v>0.005530012261789766</v>
+        <v>0.01218611810178183</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
@@ -9006,19 +9006,19 @@
         </is>
       </c>
       <c r="U103" t="n">
-        <v>0.000624739936952795</v>
+        <v>0.001083341852967938</v>
       </c>
       <c r="V103" t="n">
-        <v>-0.0005249533532954774</v>
+        <v>-0.0005238439765556357</v>
       </c>
       <c r="W103" t="n">
-        <v>-0.0005478681617593275</v>
+        <v>-0.0005634958511517288</v>
       </c>
       <c r="X103" t="n">
         <v>-0.02022572417593911</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.02407036276114341</v>
+        <v>0.04182805279245808</v>
       </c>
     </row>
     <row r="104">
@@ -9039,10 +9039,10 @@
         <v>0.2107142857143181</v>
       </c>
       <c r="E104" t="n">
-        <v>0.3702556956811134</v>
+        <v>0.2996120690308404</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.05240263736533157</v>
+        <v>0.1858926673667783</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -9051,10 +9051,10 @@
         <v>8.1</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5070848910718366</v>
+        <v>-1.277705487038766</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.6333355438555968</v>
+        <v>0.4697829032810299</v>
       </c>
       <c r="K104" t="n">
         <v>1.7519190460133</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="U104" t="n">
-        <v>1.740606630296247</v>
+        <v>1.405348741108562</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.3667706828124798</v>
+        <v>0.2961270561622067</v>
       </c>
     </row>
     <row r="105">
@@ -9119,25 +9119,25 @@
         <v>0.6500000000000004</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4540178047524702</v>
+        <v>0.4460534679810709</v>
       </c>
       <c r="E105" t="n">
-        <v>0.37837051674397</v>
+        <v>0.4245084917899373</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0773713175587368</v>
+        <v>0.1984040180458277</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>7.627711440197221</v>
+        <v>7.331733615904859</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.946110677552098</v>
+        <v>-1.086191079407817</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.7175130299298224</v>
+        <v>0.1194921971218895</v>
       </c>
       <c r="K105" t="n">
         <v>1.733334821152476</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="U105" t="n">
-        <v>0.8171092020816048</v>
+        <v>0.9354253191780092</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -9184,7 +9184,7 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0.3709821261721327</v>
+        <v>0.4172497076566511</v>
       </c>
     </row>
     <row r="106">
@@ -9202,25 +9202,25 @@
         <v>1.383333333333332</v>
       </c>
       <c r="D106" t="n">
-        <v>0.7348464173684945</v>
+        <v>0.8090262496658301</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4887937514864016</v>
+        <v>0.5751804073557321</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2660921907094168</v>
+        <v>0.2529529051282783</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>6.752282857294532</v>
+        <v>6.614418254504409</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.507109039039031</v>
+        <v>-1.143470050903921</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.7327862516885699</v>
+        <v>-0.4114184687505051</v>
       </c>
       <c r="K106" t="n">
         <v>1.712967229810738</v>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="U106" t="n">
-        <v>0.6502752848147708</v>
+        <v>0.6960647318850139</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -9267,7 +9267,7 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0.4778524633494117</v>
+        <v>0.5631346395615845</v>
       </c>
     </row>
     <row r="107">
@@ -9285,25 +9285,25 @@
         <v>2.15</v>
       </c>
       <c r="D107" t="n">
-        <v>1.194425180393912</v>
+        <v>1.314293455599225</v>
       </c>
       <c r="E107" t="n">
-        <v>0.7853848291097514</v>
+        <v>0.8071758859880831</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4963367346116541</v>
+        <v>0.4016230163507482</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>5.345683600527791</v>
+        <v>5.605257216373751</v>
       </c>
       <c r="I107" t="n">
-        <v>-2.043093815495719</v>
+        <v>-1.726044517557217</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.5154750648292854</v>
+        <v>-1.124912891978527</v>
       </c>
       <c r="K107" t="n">
         <v>1.695232430025936</v>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="U107" t="n">
-        <v>0.6463932083978727</v>
+        <v>0.6030030666861583</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0.7720683245460289</v>
+        <v>0.7925229842518809</v>
       </c>
     </row>
     <row r="108">
@@ -9368,25 +9368,25 @@
         <v>2.733333333333332</v>
       </c>
       <c r="D108" t="n">
-        <v>1.735091504289897</v>
+        <v>1.850892917284805</v>
       </c>
       <c r="E108" t="n">
-        <v>1.123505728254281</v>
+        <v>1.085405169879255</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6437560594110712</v>
+        <v>0.5510719718023769</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>4.061382882928227</v>
+        <v>4.416535341515271</v>
       </c>
       <c r="I108" t="n">
-        <v>-2.262282710697519</v>
+        <v>-2.544260230725948</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.2024251838844795</v>
+        <v>-0.7666611442762989</v>
       </c>
       <c r="K108" t="n">
         <v>1.686085973958131</v>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="U108" t="n">
-        <v>0.6410365860052412</v>
+        <v>0.5799394582166518</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.112257134316694</v>
+        <v>1.073405835667188</v>
       </c>
     </row>
     <row r="109">
@@ -9451,25 +9451,25 @@
         <v>3.633333333333332</v>
       </c>
       <c r="D109" t="n">
-        <v>3.019308082804331</v>
+        <v>3.05759443849406</v>
       </c>
       <c r="E109" t="n">
-        <v>1.791921704297944</v>
+        <v>1.684273480998688</v>
       </c>
       <c r="F109" t="n">
-        <v>0.8118299962485882</v>
+        <v>0.7681775062545757</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>1.941147220136266</v>
+        <v>1.457</v>
       </c>
       <c r="I109" t="n">
-        <v>-2.203788167523385</v>
+        <v>-2.351131657973761</v>
       </c>
       <c r="J109" t="n">
-        <v>0.7658077445534994</v>
+        <v>0.9180792406552831</v>
       </c>
       <c r="K109" t="n">
         <v>1.682842147345238</v>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="U109" t="n">
-        <v>0.5972149776538415</v>
+        <v>0.5545766550465557</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -9516,7 +9516,7 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.803176009202052</v>
+        <v>1.695670496188987</v>
       </c>
     </row>
     <row r="110">
@@ -9534,13 +9534,13 @@
         <v>4.583333333333335</v>
       </c>
       <c r="D110" t="n">
-        <v>5.087662025599396</v>
+        <v>5.002102408467303</v>
       </c>
       <c r="E110" t="n">
-        <v>2.632497850207574</v>
+        <v>2.517095851039292</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9321685902405407</v>
+        <v>0.958819077232937</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
         <v>-0.7735102974828335</v>
       </c>
       <c r="J110" t="n">
-        <v>1.1559361968497</v>
+        <v>1.234159743267291</v>
       </c>
       <c r="K110" t="n">
         <v>1.698705603232393</v>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="U110" t="n">
-        <v>0.5352296808290546</v>
+        <v>0.5210094455092956</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -9599,7 +9599,7 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.723067722127666</v>
+        <v>2.606142602216261</v>
       </c>
     </row>
     <row r="111">
@@ -9617,13 +9617,13 @@
         <v>5.55</v>
       </c>
       <c r="D111" t="n">
-        <v>8.080238191889853</v>
+        <v>7.897840496839257</v>
       </c>
       <c r="E111" t="n">
-        <v>3.580170400906002</v>
+        <v>3.52477286860467</v>
       </c>
       <c r="F111" t="n">
-        <v>0.7921967357370696</v>
+        <v>0.8677975346506814</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="U111" t="n">
-        <v>0.4774365199404186</v>
+        <v>0.4806549632942718</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -9682,7 +9682,7 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>3.857800802625552</v>
+        <v>3.796136234112287</v>
       </c>
     </row>
     <row r="112">
@@ -9700,13 +9700,13 @@
         <v>6.183333333333334</v>
       </c>
       <c r="D112" t="n">
-        <v>10.54867841710731</v>
+        <v>10.34977665743332</v>
       </c>
       <c r="E112" t="n">
-        <v>4.003821829471601</v>
+        <v>4.001917818910186</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4153054928614337</v>
+        <v>0.4903318506362861</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="U112" t="n">
-        <v>0.4230349843181493</v>
+        <v>0.4301453300101384</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>4.46246000875819</v>
+        <v>4.451908095842881</v>
       </c>
     </row>
     <row r="113">
@@ -9783,13 +9783,13 @@
         <v>7.449999999999998</v>
       </c>
       <c r="D113" t="n">
-        <v>15.88944046822959</v>
+        <v>15.7493197269158</v>
       </c>
       <c r="E113" t="n">
-        <v>3.887376988082663</v>
+        <v>3.956599050106016</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.5570617493262473</v>
+        <v>-0.5239705523481573</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="U113" t="n">
-        <v>0.2968208971301379</v>
+        <v>0.3033927889306563</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>4.716317974675825</v>
+        <v>4.778230035709586</v>
       </c>
     </row>
     <row r="114">
@@ -9866,13 +9866,13 @@
         <v>8.350000000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>19.17768389568085</v>
+        <v>19.11445323850371</v>
       </c>
       <c r="E114" t="n">
-        <v>3.088581988512221</v>
+        <v>3.172839247189312</v>
       </c>
       <c r="F114" t="n">
-        <v>-1.009767747743275</v>
+        <v>-1.004468107488447</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
         </is>
       </c>
       <c r="U114" t="n">
-        <v>0.2124432939955549</v>
+        <v>0.2173840897160017</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>4.074170338003945</v>
+        <v>4.15517801767121</v>
       </c>
     </row>
     <row r="115">
@@ -9949,13 +9949,13 @@
         <v>9.350000000000001</v>
       </c>
       <c r="D115" t="n">
-        <v>21.63846386222979</v>
+        <v>21.65818361023929</v>
       </c>
       <c r="E115" t="n">
-        <v>1.943016742746096</v>
+        <v>2.019900159672592</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.9836473090306255</v>
+        <v>-0.9943073314490398</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="U115" t="n">
-        <v>0.1347453744089194</v>
+        <v>0.1382134718180471</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -10014,7 +10014,7 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.915682914750025</v>
+        <v>2.993452750043898</v>
       </c>
     </row>
     <row r="116">
@@ -10032,13 +10032,13 @@
         <v>10.5</v>
       </c>
       <c r="D116" t="n">
-        <v>23.18819125290853</v>
+        <v>23.28830333840948</v>
       </c>
       <c r="E116" t="n">
-        <v>1.025958808693576</v>
+        <v>1.086237225905704</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.5975109207230677</v>
+        <v>-0.6138141076207885</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="U116" t="n">
-        <v>0.07719412451654387</v>
+        <v>0.07959227988629636</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -10097,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.789992122890455</v>
+        <v>1.853569157387657</v>
       </c>
     </row>
     <row r="117">
@@ -10115,13 +10115,13 @@
         <v>11.91666666666667</v>
       </c>
       <c r="D117" t="n">
-        <v>24.08033377108011</v>
+        <v>24.24903785723786</v>
       </c>
       <c r="E117" t="n">
-        <v>0.5283979871066755</v>
+        <v>0.5623271287404528</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.1882381318596124</v>
+        <v>-0.2075108301967473</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="U117" t="n">
-        <v>0.0359476784681711</v>
+        <v>0.03719421226749242</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -10180,7 +10180,7 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0.8656320958090298</v>
+        <v>0.9019238613445647</v>
       </c>
     </row>
     <row r="118">
@@ -10198,13 +10198,13 @@
         <v>12.81666666666666</v>
       </c>
       <c r="D118" t="n">
-        <v>24.49794379362827</v>
+        <v>24.68889995641544</v>
       </c>
       <c r="E118" t="n">
-        <v>0.4521706072614453</v>
+        <v>0.4683694028493468</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.06189192941126924</v>
+        <v>-0.08062752562744983</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -10251,19 +10251,19 @@
         </is>
       </c>
       <c r="U118" t="n">
-        <v>0.02206378333645542</v>
+        <v>0.02257714050178286</v>
       </c>
       <c r="V118" t="n">
-        <v>0.003118352624790683</v>
+        <v>0.003094233743329843</v>
       </c>
       <c r="W118" t="n">
-        <v>0.003053248186169309</v>
+        <v>0.00302812978833972</v>
       </c>
       <c r="X118" t="n">
         <v>0.07639322733083535</v>
       </c>
       <c r="Y118" t="n">
-        <v>0.5405173240512769</v>
+        <v>0.5574047631504522</v>
       </c>
     </row>
     <row r="119">
@@ -10281,13 +10281,13 @@
         <v>14.25</v>
       </c>
       <c r="D119" t="n">
-        <v>25.1190264320092</v>
+        <v>25.31373903863702</v>
       </c>
       <c r="E119" t="n">
-        <v>0.415516544927705</v>
+        <v>0.4070633236283516</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.02474601114727429</v>
+        <v>-0.03999284415639892</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -10334,19 +10334,19 @@
         </is>
       </c>
       <c r="U119" t="n">
-        <v>0.01291890048475715</v>
+        <v>0.01245772251766014</v>
       </c>
       <c r="V119" t="n">
-        <v>0.002425044925870336</v>
+        <v>0.002406391544874938</v>
       </c>
       <c r="W119" t="n">
-        <v>0.002336659122449342</v>
+        <v>0.002321816523026087</v>
       </c>
       <c r="X119" t="n">
         <v>0.06091476759174676</v>
       </c>
       <c r="Y119" t="n">
-        <v>0.3245102027491114</v>
+        <v>0.315351536827801</v>
       </c>
     </row>
     <row r="120">
@@ -10364,13 +10364,13 @@
         <v>15.75</v>
       </c>
       <c r="D120" t="n">
-        <v>25.7143642179953</v>
+        <v>25.87901339418912</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3796950830314882</v>
+        <v>0.3514361884151525</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.02282520085588392</v>
+        <v>-0.03353544752169235</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -10417,19 +10417,19 @@
         </is>
       </c>
       <c r="U120" t="n">
-        <v>0.01071301830702301</v>
+        <v>0.00952711205653349</v>
       </c>
       <c r="V120" t="n">
-        <v>0.00175467991656586</v>
+        <v>0.001743516175570568</v>
       </c>
       <c r="W120" t="n">
-        <v>0.001649811370585271</v>
+        <v>0.001650849678072112</v>
       </c>
       <c r="X120" t="n">
         <v>0.04512047846057613</v>
       </c>
       <c r="Y120" t="n">
-        <v>0.275478454620841</v>
+        <v>0.2465522605189709</v>
       </c>
     </row>
     <row r="121">
@@ -10447,13 +10447,13 @@
         <v>17.75</v>
       </c>
       <c r="D121" t="n">
-        <v>26.42789631927808</v>
+        <v>26.51411675247832</v>
       </c>
       <c r="E121" t="n">
-        <v>0.3368600779639706</v>
+        <v>0.2938301181373864</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.02045269624248116</v>
+        <v>-0.02555954101228416</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -10500,19 +10500,19 @@
         </is>
       </c>
       <c r="U121" t="n">
-        <v>0.0109061566477308</v>
+        <v>0.009241799548130016</v>
       </c>
       <c r="V121" t="n">
-        <v>0.001102720811710549</v>
+        <v>0.001099134908134269</v>
       </c>
       <c r="W121" t="n">
-        <v>0.0009685751640328625</v>
+        <v>0.000985830493883179</v>
       </c>
       <c r="X121" t="n">
         <v>0.02914259128099655</v>
       </c>
       <c r="Y121" t="n">
-        <v>0.2882267771280351</v>
+        <v>0.2450381522221206</v>
       </c>
     </row>
     <row r="122">
@@ -10530,13 +10530,13 @@
         <v>22.08333333333333</v>
       </c>
       <c r="D122" t="n">
-        <v>27.70072835809506</v>
+        <v>27.56466149717262</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2572901866479924</v>
+        <v>0.2135249130505557</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.01606282761716979</v>
+        <v>-0.01080164273625846</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="U122" t="n">
-        <v>0.01224676059052313</v>
+        <v>0.01070487856881287</v>
       </c>
       <c r="V122" t="n">
-        <v>0.0002329777313350133</v>
+        <v>0.0002341277744280816</v>
       </c>
       <c r="W122" t="n">
-        <v>6.10655905385959e-05</v>
+        <v>8.311781506497117e-05</v>
       </c>
       <c r="X122" t="n">
         <v>0.006453652849196456</v>
       </c>
       <c r="Y122" t="n">
-        <v>0.339244188384705</v>
+        <v>0.2950763541176645</v>
       </c>
     </row>
     <row r="123">
@@ -10613,13 +10613,13 @@
         <v>23.75</v>
       </c>
       <c r="D123" t="n">
-        <v>28.10618617952874</v>
+        <v>27.90200526919842</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2319928168977157</v>
+        <v>0.2004775134057626</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.01407211063616783</v>
+        <v>-0.004341779320751256</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -10666,19 +10666,19 @@
         </is>
       </c>
       <c r="U123" t="n">
-        <v>0.01204437474977316</v>
+        <v>0.0109752773023198</v>
       </c>
       <c r="V123" t="n">
-        <v>6.531630339965662e-05</v>
+        <v>6.579427414616336e-05</v>
       </c>
       <c r="W123" t="n">
-        <v>-0.0001025170476882296</v>
+        <v>-8.826080120155897e-05</v>
       </c>
       <c r="X123" t="n">
         <v>0.001835792183909335</v>
       </c>
       <c r="Y123" t="n">
-        <v>0.3385214391331394</v>
+        <v>0.3062322451202408</v>
       </c>
     </row>
     <row r="124">
@@ -10696,13 +10696,13 @@
         <v>26.25</v>
       </c>
       <c r="D124" t="n">
-        <v>28.64386118691368</v>
+        <v>28.39596624092639</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2009612073597893</v>
+        <v>0.2026980418518516</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.0109326309643531</v>
+        <v>0.002663315221819396</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -10749,19 +10749,19 @@
         </is>
       </c>
       <c r="U124" t="n">
-        <v>0.01068191935259054</v>
+        <v>0.01080433215319584</v>
       </c>
       <c r="V124" t="n">
-        <v>-5.017271922451634e-06</v>
+        <v>-5.061072381350162e-06</v>
       </c>
       <c r="W124" t="n">
-        <v>-0.0001495383361958823</v>
+        <v>-0.000152514438970206</v>
       </c>
       <c r="X124" t="n">
         <v>-0.0001437140404837041</v>
       </c>
       <c r="Y124" t="n">
-        <v>0.3059714151454102</v>
+        <v>0.3067994510779046</v>
       </c>
     </row>
     <row r="125">
@@ -10779,13 +10779,13 @@
         <v>27.91666666666666</v>
       </c>
       <c r="D125" t="n">
-        <v>28.96312009296423</v>
+        <v>28.73947814752466</v>
       </c>
       <c r="E125" t="n">
-        <v>0.1843846144756647</v>
+        <v>0.2091092381586437</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.008901652291602401</v>
+        <v>0.00312787002091983</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
@@ -10832,19 +10832,19 @@
         </is>
       </c>
       <c r="U125" t="n">
-        <v>0.009552581993302903</v>
+        <v>0.01046242349453234</v>
       </c>
       <c r="V125" t="n">
-        <v>3.478942026938983e-06</v>
+        <v>3.506014103856397e-06</v>
       </c>
       <c r="W125" t="n">
-        <v>-0.000123507417960572</v>
+        <v>-0.000136657527570694</v>
       </c>
       <c r="X125" t="n">
         <v>0.0001007610157226942</v>
       </c>
       <c r="Y125" t="n">
-        <v>0.2766725794699196</v>
+        <v>0.3006845913912608</v>
       </c>
     </row>
     <row r="126">
@@ -10862,13 +10862,13 @@
         <v>30.7</v>
       </c>
       <c r="D126" t="n">
-        <v>29.44299319235574</v>
+        <v>29.3354530945887</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1644624453651566</v>
+        <v>0.2144738188390969</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.005653854142682241</v>
+        <v>0.0001867597164298407</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -10915,19 +10915,19 @@
         </is>
       </c>
       <c r="U126" t="n">
-        <v>0.0079536835586646</v>
+        <v>0.009678970363111127</v>
       </c>
       <c r="V126" t="n">
-        <v>3.065108018757976e-05</v>
+        <v>3.076344320953171e-05</v>
       </c>
       <c r="W126" t="n">
-        <v>-7.299415716891363e-05</v>
+        <v>-9.582654525136444e-05</v>
       </c>
       <c r="X126" t="n">
         <v>0.0009024595453012609</v>
       </c>
       <c r="Y126" t="n">
-        <v>0.2341802508719136</v>
+        <v>0.2839369810909607</v>
       </c>
     </row>
     <row r="127">
@@ -10945,13 +10945,13 @@
         <v>33.75</v>
       </c>
       <c r="D127" t="n">
-        <v>29.9180428917296</v>
+        <v>29.99077163834306</v>
       </c>
       <c r="E127" t="n">
-        <v>0.1522442521237526</v>
+        <v>0.2092258601148522</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.002306842777105907</v>
+        <v>-0.003687345484199168</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -10998,19 +10998,19 @@
         </is>
       </c>
       <c r="U127" t="n">
-        <v>0.006754510432644329</v>
+        <v>0.008642141506427718</v>
       </c>
       <c r="V127" t="n">
-        <v>4.900134090875597e-05</v>
+        <v>4.888251081829854e-05</v>
       </c>
       <c r="W127" t="n">
-        <v>-3.797539753177769e-05</v>
+        <v>-6.213108111183558e-05</v>
       </c>
       <c r="X127" t="n">
         <v>0.001466024219060425</v>
       </c>
       <c r="Y127" t="n">
-        <v>0.2020817328364881</v>
+        <v>0.2591844923855197</v>
       </c>
     </row>
     <row r="128">
@@ -11028,13 +11028,13 @@
         <v>36.75</v>
       </c>
       <c r="D128" t="n">
-        <v>30.36441901562919</v>
+        <v>30.6018281992158</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1503375270647895</v>
+        <v>0.1923604369357763</v>
       </c>
       <c r="F128" t="n">
-        <v>0.001626391730103559</v>
+        <v>-0.008239993382676031</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -11081,19 +11081,19 @@
         </is>
       </c>
       <c r="U128" t="n">
-        <v>0.006121912736337415</v>
+        <v>0.007456717671039857</v>
       </c>
       <c r="V128" t="n">
-        <v>5.527485268731127e-05</v>
+        <v>5.484603001815776e-05</v>
       </c>
       <c r="W128" t="n">
-        <v>-2.307884195777648e-05</v>
+        <v>-3.985128123262358e-05</v>
       </c>
       <c r="X128" t="n">
         <v>0.001678388788024696</v>
       </c>
       <c r="Y128" t="n">
-        <v>0.1858883235032663</v>
+        <v>0.2281891930992183</v>
       </c>
     </row>
     <row r="129">
@@ -11111,13 +11111,13 @@
         <v>39.33333333333334</v>
       </c>
       <c r="D129" t="n">
-        <v>30.75622895087086</v>
+        <v>31.07356626059552</v>
       </c>
       <c r="E129" t="n">
-        <v>0.1595708678456065</v>
+        <v>0.165249536401546</v>
       </c>
       <c r="F129" t="n">
-        <v>0.004219532357862998</v>
+        <v>-0.01124150682098886</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -11164,19 +11164,19 @@
         </is>
       </c>
       <c r="U129" t="n">
-        <v>0.006135991785462943</v>
+        <v>0.006265756249527881</v>
       </c>
       <c r="V129" t="n">
-        <v>4.842643580783609e-05</v>
+        <v>4.79318831475481e-05</v>
       </c>
       <c r="W129" t="n">
-        <v>-2.978026594894044e-05</v>
+        <v>-3.111316763550425e-05</v>
       </c>
       <c r="X129" t="n">
         <v>0.001489414546980458</v>
       </c>
       <c r="Y129" t="n">
-        <v>0.1887199681943611</v>
+        <v>0.1946993919924451</v>
       </c>
     </row>
     <row r="130">
@@ -11194,13 +11194,13 @@
         <v>46.93333333333334</v>
       </c>
       <c r="D130" t="n">
-        <v>32.14565737977434</v>
+        <v>31.94134358797329</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2060681923921539</v>
+        <v>0.0631129181715524</v>
       </c>
       <c r="F130" t="n">
-        <v>0.008016605680702123</v>
+        <v>-0.01563655060795684</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -11247,19 +11247,19 @@
         </is>
       </c>
       <c r="U130" t="n">
-        <v>0.007061072516470514</v>
+        <v>0.002626521099334869</v>
       </c>
       <c r="V130" t="n">
-        <v>8.303042474814183e-06</v>
+        <v>8.35615314271211e-06</v>
       </c>
       <c r="W130" t="n">
-        <v>-7.874507341036715e-05</v>
+        <v>-2.423042277860768e-05</v>
       </c>
       <c r="X130" t="n">
         <v>0.0002669067586050903</v>
       </c>
       <c r="Y130" t="n">
-        <v>0.2269828178482022</v>
+        <v>0.08389461287491637</v>
       </c>
     </row>
     <row r="131">
@@ -11280,10 +11280,10 @@
         <v>0.1803571428572935</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.1015176409694535</v>
+        <v>0.1201581623370555</v>
       </c>
       <c r="F131" t="n">
-        <v>0.6682904508303718</v>
+        <v>0.5272743961133084</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -11292,10 +11292,10 @@
         <v>8.209</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.08359532886518606</v>
+        <v>-0.4529858429858447</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.124072605397242</v>
+        <v>-0.4200795102373955</v>
       </c>
       <c r="K131" t="n">
         <v>1.751659471177489</v>
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="U131" t="n">
-        <v>-0.5679203431903158</v>
+        <v>0.6611732196962319</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>-0.1024284904683389</v>
+        <v>0.11924731283817</v>
       </c>
     </row>
     <row r="132">
@@ -11360,25 +11360,25 @@
         <v>0.7999999999999998</v>
       </c>
       <c r="D132" t="n">
-        <v>0.308706836168724</v>
+        <v>0.4393936031639649</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4223918742480296</v>
+        <v>0.5274329884296229</v>
       </c>
       <c r="F132" t="n">
-        <v>0.6414833372133362</v>
+        <v>0.4909126691181103</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>7.793677064967609</v>
+        <v>7.657</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.9547120087157928</v>
+        <v>-0.9270141570141566</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.053719094229275</v>
+        <v>-0.764991274833384</v>
       </c>
       <c r="K132" t="n">
         <v>1.744614188526386</v>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="U132" t="n">
-        <v>1.363237022220925</v>
+        <v>1.195340539655349</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -11425,7 +11425,7 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0.4208405880778943</v>
+        <v>0.5252249867271221</v>
       </c>
     </row>
     <row r="133">
@@ -11443,25 +11443,25 @@
         <v>1.85</v>
       </c>
       <c r="D133" t="n">
-        <v>1.113224704458702</v>
+        <v>1.273836050869479</v>
       </c>
       <c r="E133" t="n">
-        <v>1.077477601595294</v>
+        <v>1.01783578849601</v>
       </c>
       <c r="F133" t="n">
-        <v>0.6129455794253742</v>
+        <v>0.4872356754159723</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>6.190975618606466</v>
+        <v>6.357</v>
       </c>
       <c r="I133" t="n">
-        <v>-2.012639091367355</v>
+        <v>-1.967920758381133</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.9066690965561124</v>
+        <v>-0.932941997857871</v>
       </c>
       <c r="K133" t="n">
         <v>1.73546370762832</v>
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="U133" t="n">
-        <v>0.9627753485796412</v>
+        <v>0.7939186744941727</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.071785302882695</v>
+        <v>1.011322229029188</v>
       </c>
     </row>
     <row r="134">
@@ -11526,25 +11526,25 @@
         <v>3.033333333333333</v>
       </c>
       <c r="D134" t="n">
-        <v>2.803349023583602</v>
+        <v>2.775839023269351</v>
       </c>
       <c r="E134" t="n">
-        <v>1.788199522287685</v>
+        <v>1.621317197306361</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6089915733320981</v>
+        <v>0.6023071583833031</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>3.160881705800736</v>
+        <v>3.055</v>
       </c>
       <c r="I134" t="n">
-        <v>-2.950996826368633</v>
+        <v>-2.994023176750961</v>
       </c>
       <c r="J134" t="n">
-        <v>0.4239685604040058</v>
+        <v>0.4151273660361725</v>
       </c>
       <c r="K134" t="n">
         <v>1.72475037448885</v>
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="U134" t="n">
-        <v>0.6334595451338554</v>
+        <v>0.5796616656036678</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.775808197330706</v>
+        <v>1.60904747167597</v>
       </c>
     </row>
     <row r="135">
@@ -11609,13 +11609,13 @@
         <v>4.000000000000001</v>
       </c>
       <c r="D135" t="n">
-        <v>4.816164715101619</v>
+        <v>4.621091566542147</v>
       </c>
       <c r="E135" t="n">
-        <v>2.383510006636266</v>
+        <v>2.276452176266931</v>
       </c>
       <c r="F135" t="n">
-        <v>0.6229704468371973</v>
+        <v>0.7562855377510397</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
         <v>-1.5801724137931</v>
       </c>
       <c r="J135" t="n">
-        <v>1.526377668811363</v>
+        <v>1.548632677629808</v>
       </c>
       <c r="K135" t="n">
         <v>1.718509854906813</v>
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="U135" t="n">
-        <v>0.4967217436006408</v>
+        <v>0.4944459759764817</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -11674,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>2.39229373475316</v>
+        <v>2.284880129695621</v>
       </c>
     </row>
     <row r="136">
@@ -11692,13 +11692,13 @@
         <v>4.966666666666666</v>
       </c>
       <c r="D136" t="n">
-        <v>7.411468369747046</v>
+        <v>7.176979897385414</v>
       </c>
       <c r="E136" t="n">
-        <v>2.9926090528396</v>
+        <v>3.08346923695837</v>
       </c>
       <c r="F136" t="n">
-        <v>0.6706891140834572</v>
+        <v>0.894031883704556</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="U136" t="n">
-        <v>0.4222268895661837</v>
+        <v>0.448079287537107</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>3.12932123687645</v>
+        <v>3.215856039088596</v>
       </c>
     </row>
     <row r="137">
@@ -11775,13 +11775,13 @@
         <v>5.833333333333333</v>
       </c>
       <c r="D137" t="n">
-        <v>10.24423647537721</v>
+        <v>10.19077513746318</v>
       </c>
       <c r="E137" t="n">
-        <v>3.605409247212861</v>
+        <v>3.904285575698185</v>
       </c>
       <c r="F137" t="n">
-        <v>0.8476116553187656</v>
+        <v>0.9287648508347501</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="U137" t="n">
-        <v>0.3914880734329325</v>
+        <v>0.4226625211360417</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -11840,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>4.010496401536797</v>
+        <v>4.307258711930682</v>
       </c>
     </row>
     <row r="138">
@@ -11858,13 +11858,13 @@
         <v>6.916666666666667</v>
       </c>
       <c r="D138" t="n">
-        <v>14.60622135041143</v>
+        <v>14.998416165606</v>
       </c>
       <c r="E138" t="n">
-        <v>4.713962353344133</v>
+        <v>4.885624370326928</v>
       </c>
       <c r="F138" t="n">
-        <v>1.084484893801659</v>
+        <v>0.6592139303105498</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="U138" t="n">
-        <v>0.3803331057369282</v>
+        <v>0.3833391826215346</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -11923,7 +11923,7 @@
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>5.555229529283011</v>
+        <v>5.749480593541015</v>
       </c>
     </row>
     <row r="139">
@@ -11941,13 +11941,13 @@
         <v>7.633333333333334</v>
       </c>
       <c r="D139" t="n">
-        <v>18.31051355531937</v>
+        <v>18.71208431852404</v>
       </c>
       <c r="E139" t="n">
-        <v>5.520194023753465</v>
+        <v>5.241129660770438</v>
       </c>
       <c r="F139" t="n">
-        <v>0.194758639694907</v>
+        <v>-0.2626738113066089</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="U139" t="n">
-        <v>0.3589080306976107</v>
+        <v>0.3375245972595111</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -12006,7 +12006,7 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>6.571790361201584</v>
+        <v>6.315788723495839</v>
       </c>
     </row>
     <row r="140">
@@ -12024,13 +12024,13 @@
         <v>8.25</v>
       </c>
       <c r="D140" t="n">
-        <v>21.90110066215372</v>
+        <v>21.97556260536534</v>
       </c>
       <c r="E140" t="n">
-        <v>5.146703941302999</v>
+        <v>4.676551264699274</v>
       </c>
       <c r="F140" t="n">
-        <v>-1.301429478420019</v>
+        <v>-1.363458844903703</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
         </is>
       </c>
       <c r="U140" t="n">
-        <v>0.2834808281370577</v>
+        <v>0.2612902223267993</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>6.208542152820399</v>
+        <v>5.741999638912405</v>
       </c>
     </row>
     <row r="141">
@@ -12107,13 +12107,13 @@
         <v>9.050000000000001</v>
       </c>
       <c r="D141" t="n">
-        <v>25.31702061991268</v>
+        <v>25.07793587717033</v>
       </c>
       <c r="E141" t="n">
-        <v>3.383464045219073</v>
+        <v>3.120909314933201</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.995001879609939</v>
+        <v>-1.742867704636333</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="U141" t="n">
-        <v>0.1625643226379999</v>
+        <v>0.1533688877946125</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>4.11564430828838</v>
+        <v>3.846175133666223</v>
       </c>
     </row>
     <row r="142">
@@ -12190,13 +12190,13 @@
         <v>10.13333333333333</v>
       </c>
       <c r="D142" t="n">
-        <v>27.6820262224195</v>
+        <v>27.3483074314982</v>
       </c>
       <c r="E142" t="n">
-        <v>1.528888314475401</v>
+        <v>1.528676938769382</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.289454724126297</v>
+        <v>-1.115294966596787</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
@@ -12243,19 +12243,19 @@
         </is>
       </c>
       <c r="U142" t="n">
-        <v>0.05945800591186536</v>
+        <v>0.06012422753422365</v>
       </c>
       <c r="V142" t="n">
-        <v>0.001090215218210349</v>
+        <v>0.001103518612044737</v>
       </c>
       <c r="W142" t="n">
-        <v>0.0009575974672742633</v>
+        <v>0.0009677784852073051</v>
       </c>
       <c r="X142" t="n">
         <v>0.03017936625857966</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.645918078785031</v>
+        <v>1.644295858687297</v>
       </c>
     </row>
     <row r="143">
@@ -12273,13 +12273,13 @@
         <v>11.56666666666667</v>
       </c>
       <c r="D143" t="n">
-        <v>28.6328130121517</v>
+        <v>28.46405037547181</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4818298852329832</v>
+        <v>0.6022852657586331</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.390496584403931</v>
+        <v>-0.360053881150505</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -12326,19 +12326,19 @@
         </is>
       </c>
       <c r="U143" t="n">
-        <v>0.007180981049318367</v>
+        <v>0.01151259578173216</v>
       </c>
       <c r="V143" t="n">
-        <v>0.0008969775900507867</v>
+        <v>0.000902295747556234</v>
       </c>
       <c r="W143" t="n">
-        <v>0.0008713384920761881</v>
+        <v>0.0008609472688623766</v>
       </c>
       <c r="X143" t="n">
         <v>0.02568299161201464</v>
       </c>
       <c r="Y143" t="n">
-        <v>0.2056116876289377</v>
+        <v>0.3276951062836685</v>
       </c>
     </row>
     <row r="144">
@@ -12356,13 +12356,13 @@
         <v>12.66666666666667</v>
       </c>
       <c r="D144" t="n">
-        <v>29.00959789988407</v>
+        <v>28.97786920043766</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3393147461468509</v>
+        <v>0.4478876670289793</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.07623267057361967</v>
+        <v>-0.09375374226497546</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -12409,19 +12409,19 @@
         </is>
       </c>
       <c r="U144" t="n">
-        <v>0.002743599749419692</v>
+        <v>0.006503159819879348</v>
       </c>
       <c r="V144" t="n">
-        <v>0.0007983468461517041</v>
+        <v>0.0007992209789928847</v>
       </c>
       <c r="W144" t="n">
-        <v>0.0007860297983548474</v>
+        <v>0.0007699938900783005</v>
       </c>
       <c r="X144" t="n">
         <v>0.02315972099150155</v>
       </c>
       <c r="Y144" t="n">
-        <v>0.07959072552888796</v>
+        <v>0.1884477146500055</v>
       </c>
     </row>
     <row r="145">
@@ -12439,13 +12439,13 @@
         <v>14.13333333333333</v>
       </c>
       <c r="D145" t="n">
-        <v>29.5009685640624</v>
+        <v>29.59718463877531</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3317898541146982</v>
+        <v>0.4015261467971136</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.004414699244993117</v>
+        <v>-0.02828585116984849</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -12492,19 +12492,19 @@
         </is>
       </c>
       <c r="U145" t="n">
-        <v>0.006161129062847553</v>
+        <v>0.008480747496735483</v>
       </c>
       <c r="V145" t="n">
-        <v>0.0006987019005542094</v>
+        <v>0.0006964305238984141</v>
       </c>
       <c r="W145" t="n">
-        <v>0.0006645143300337535</v>
+        <v>0.0006495245736151253</v>
       </c>
       <c r="X145" t="n">
         <v>0.02061238280390039</v>
       </c>
       <c r="Y145" t="n">
-        <v>0.1817592748021969</v>
+        <v>0.2510062495357116</v>
       </c>
     </row>
     <row r="146">
@@ -12522,13 +12522,13 @@
         <v>16.85</v>
       </c>
       <c r="D146" t="n">
-        <v>30.38604944373159</v>
+        <v>30.58366178364559</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3233990471364363</v>
+        <v>0.3414107011147993</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.002210540986952472</v>
+        <v>-0.01805098696945927</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -12575,19 +12575,19 @@
         </is>
       </c>
       <c r="U146" t="n">
-        <v>0.01101921643202252</v>
+        <v>0.01153937859759997</v>
       </c>
       <c r="V146" t="n">
-        <v>0.0005568426274757067</v>
+        <v>0.0005532446614977355</v>
       </c>
       <c r="W146" t="n">
-        <v>0.0004788539010684022</v>
+        <v>0.0004721021781200712</v>
       </c>
       <c r="X146" t="n">
         <v>0.01692024761085423</v>
       </c>
       <c r="Y146" t="n">
-        <v>0.334830455334616</v>
+        <v>0.3529164522224361</v>
       </c>
     </row>
     <row r="147">
@@ -12605,13 +12605,13 @@
         <v>22.4</v>
       </c>
       <c r="D147" t="n">
-        <v>32.15372939173055</v>
+        <v>32.23233890740552</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3210867398122836</v>
+        <v>0.2874586621503354</v>
       </c>
       <c r="F147" t="n">
-        <v>0.001534729473765345</v>
+        <v>-0.0006600694074655467</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -12658,19 +12658,19 @@
         </is>
       </c>
       <c r="U147" t="n">
-        <v>0.01637646662611292</v>
+        <v>0.01530880996608005</v>
       </c>
       <c r="V147" t="n">
-        <v>0.000348490198391928</v>
+        <v>0.0003476402865753588</v>
       </c>
       <c r="W147" t="n">
-        <v>0.0002032882832466225</v>
+        <v>0.0002122357847532248</v>
       </c>
       <c r="X147" t="n">
         <v>0.01120525953476454</v>
       </c>
       <c r="Y147" t="n">
-        <v>0.5265644762887414</v>
+        <v>0.4934387510957593</v>
       </c>
     </row>
     <row r="148">
@@ -12688,13 +12688,13 @@
         <v>24.05</v>
       </c>
       <c r="D148" t="n">
-        <v>32.6847909758343</v>
+        <v>32.70193637387037</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3245762653317463</v>
+        <v>0.2908143446361375</v>
       </c>
       <c r="F148" t="n">
-        <v>0.00283005915963172</v>
+        <v>0.005958378862213135</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -12741,19 +12741,19 @@
         </is>
       </c>
       <c r="U148" t="n">
-        <v>0.01665582251877981</v>
+        <v>0.01561820252417522</v>
       </c>
       <c r="V148" t="n">
-        <v>0.0002976187991140823</v>
+        <v>0.0002974627596454867</v>
       </c>
       <c r="W148" t="n">
-        <v>0.0001452584038340783</v>
+        <v>0.0001546689767463408</v>
       </c>
       <c r="X148" t="n">
         <v>0.009727608239522602</v>
       </c>
       <c r="Y148" t="n">
-        <v>0.544392077556912</v>
+        <v>0.5107454652197997</v>
       </c>
     </row>
     <row r="149">
@@ -12771,13 +12771,13 @@
         <v>25.55</v>
       </c>
       <c r="D149" t="n">
-        <v>33.17536550085145</v>
+        <v>33.14662582651447</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3297966202645242</v>
+        <v>0.3051036837037131</v>
       </c>
       <c r="F149" t="n">
-        <v>0.002356905619938968</v>
+        <v>0.009105086945152135</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -12824,19 +12824,19 @@
         </is>
       </c>
       <c r="U149" t="n">
-        <v>0.01614011034749322</v>
+        <v>0.01540376887744909</v>
       </c>
       <c r="V149" t="n">
-        <v>0.0002555725631114712</v>
+        <v>0.0002557941564727905</v>
       </c>
       <c r="W149" t="n">
-        <v>0.0001049490161522152</v>
+        <v>0.0001119176927437326</v>
       </c>
       <c r="X149" t="n">
         <v>0.008478713193212481</v>
       </c>
       <c r="Y149" t="n">
-        <v>0.5354540600021621</v>
+        <v>0.5105829632989139</v>
       </c>
     </row>
     <row r="150">
@@ -12854,13 +12854,13 @@
         <v>27.01666666666667</v>
       </c>
       <c r="D150" t="n">
-        <v>33.6630065215925</v>
+        <v>33.60650743528318</v>
       </c>
       <c r="E150" t="n">
-        <v>0.331642475307321</v>
+        <v>0.3178538665585267</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.0006942422289595851</v>
+        <v>0.006226158618857267</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -12907,19 +12907,19 @@
         </is>
       </c>
       <c r="U150" t="n">
-        <v>0.0152854783221557</v>
+        <v>0.01489174538373089</v>
       </c>
       <c r="V150" t="n">
-        <v>0.0002209300877437384</v>
+        <v>0.0002213015142634324</v>
       </c>
       <c r="W150" t="n">
-        <v>7.631658212372236e-05</v>
+        <v>8.017619307994671e-05</v>
       </c>
       <c r="X150" t="n">
         <v>0.007437170984533468</v>
       </c>
       <c r="Y150" t="n">
-        <v>0.5145551564443881</v>
+        <v>0.5004595519626962</v>
       </c>
     </row>
     <row r="151">
@@ -12937,13 +12937,13 @@
         <v>30.05</v>
       </c>
       <c r="D151" t="n">
-        <v>34.66371872579222</v>
+        <v>34.5976290083399</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3172858729876955</v>
+        <v>0.3212622662351068</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.008628784912759153</v>
+        <v>-0.00402119203103507</v>
       </c>
       <c r="G151" t="n">
         <v>1</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="U151" t="n">
-        <v>0.01309174983064569</v>
+        <v>0.01322416726636053</v>
       </c>
       <c r="V151" t="n">
-        <v>0.0001728070869525385</v>
+        <v>0.0001731371896756962</v>
       </c>
       <c r="W151" t="n">
-        <v>4.680971952456418e-05</v>
+        <v>4.562229347686444e-05</v>
       </c>
       <c r="X151" t="n">
         <v>0.005990136255946315</v>
       </c>
       <c r="Y151" t="n">
-        <v>0.4538087337579402</v>
+        <v>0.4575248330257741</v>
       </c>
     </row>
     <row r="152">
@@ -13020,13 +13020,13 @@
         <v>33.05</v>
       </c>
       <c r="D152" t="n">
-        <v>35.57813461613436</v>
+        <v>35.54515317446911</v>
       </c>
       <c r="E152" t="n">
-        <v>0.2798404352259274</v>
+        <v>0.2939337794328081</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.01680362063193006</v>
+        <v>-0.01481686994613171</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -13073,19 +13073,19 @@
         </is>
       </c>
       <c r="U152" t="n">
-        <v>0.01054151037633381</v>
+        <v>0.01094529989548966</v>
       </c>
       <c r="V152" t="n">
-        <v>0.0001533299475232635</v>
+        <v>0.0001534722184735378</v>
       </c>
       <c r="W152" t="n">
-        <v>5.060135605658079e-05</v>
+        <v>4.670966747733546e-05</v>
       </c>
       <c r="X152" t="n">
         <v>0.005455193513667488</v>
       </c>
       <c r="Y152" t="n">
-        <v>0.3750472752265814</v>
+        <v>0.3890523613256806</v>
       </c>
     </row>
     <row r="153">
@@ -13103,13 +13103,13 @@
         <v>35.71666666666666</v>
       </c>
       <c r="D153" t="n">
-        <v>36.26519980860697</v>
+        <v>36.27704743837425</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2247864944719238</v>
+        <v>0.2408935352022574</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.02540387016099038</v>
+        <v>-0.02587000667387462</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -13156,19 +13156,19 @@
         </is>
       </c>
       <c r="U153" t="n">
-        <v>0.007931425284625664</v>
+        <v>0.008373401835163687</v>
       </c>
       <c r="V153" t="n">
-        <v>0.000160829667548178</v>
+        <v>0.0001607771425911803</v>
       </c>
       <c r="W153" t="n">
-        <v>8.22780838157204e-05</v>
+        <v>7.787537641016748e-05</v>
       </c>
       <c r="X153" t="n">
         <v>0.005832520028786509</v>
       </c>
       <c r="Y153" t="n">
-        <v>0.2876347227139872</v>
+        <v>0.3037622955948031</v>
       </c>
     </row>
     <row r="154">
@@ -13186,13 +13186,13 @@
         <v>38.41666666666666</v>
       </c>
       <c r="D154" t="n">
-        <v>36.78228424672304</v>
+        <v>36.835696706298</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1431871064357388</v>
+        <v>0.1546969243125667</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.0316287160182974</v>
+        <v>-0.03362783079533318</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
@@ -13239,19 +13239,19 @@
         </is>
       </c>
       <c r="U154" t="n">
-        <v>0.004882182380189196</v>
+        <v>0.005189001400015388</v>
       </c>
       <c r="V154" t="n">
-        <v>0.0001990858490734699</v>
+        <v>0.0001987971708125328</v>
       </c>
       <c r="W154" t="n">
-        <v>0.0001493497074342836</v>
+        <v>0.0001460120295966885</v>
       </c>
       <c r="X154" t="n">
         <v>0.007322832290120574</v>
       </c>
       <c r="Y154" t="n">
-        <v>0.1795778200524618</v>
+        <v>0.1911404817795225</v>
       </c>
     </row>
     <row r="155">
@@ -13269,13 +13269,13 @@
         <v>46.41666666666666</v>
       </c>
       <c r="D155" t="n">
-        <v>36.78228424672304</v>
+        <v>36.835696706298</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.1431871064357377</v>
+        <v>-0.1546969243125638</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.03996483719957174</v>
+        <v>-0.04372063136094942</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -13322,19 +13322,19 @@
         </is>
       </c>
       <c r="U155" t="n">
-        <v>-0.004727090289107653</v>
+        <v>-0.005033909308933797</v>
       </c>
       <c r="V155" t="n">
-        <v>0.00037099240092809</v>
+        <v>0.0003704544549032005</v>
       </c>
       <c r="W155" t="n">
-        <v>0.0004299339387122765</v>
+        <v>0.0004331306696072843</v>
       </c>
       <c r="X155" t="n">
         <v>0.01364594794431124</v>
       </c>
       <c r="Y155" t="n">
-        <v>-0.1738731786738819</v>
+        <v>-0.1854275565508955</v>
       </c>
     </row>
     <row r="156">
@@ -13355,10 +13355,10 @@
         <v>0.2740000000001075</v>
       </c>
       <c r="E156" t="n">
-        <v>0.03724215287300014</v>
+        <v>0.01038084257582339</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4977558858054834</v>
+        <v>0.4910265447573807</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -13367,10 +13367,10 @@
         <v>8.204000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1999919344492307</v>
+        <v>-0.8866327300150854</v>
       </c>
       <c r="J156" t="n">
-        <v>0.07600203075427747</v>
+        <v>2.43320213893422</v>
       </c>
       <c r="K156" t="n">
         <v>1.762613424079101</v>
@@ -13405,7 +13405,7 @@
         </is>
       </c>
       <c r="U156" t="n">
-        <v>0.117788326872146</v>
+        <v>0.01975434768540793</v>
       </c>
       <c r="V156" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>0.03227400156298065</v>
+        <v>0.005412691265803897</v>
       </c>
     </row>
     <row r="157">
@@ -13435,25 +13435,25 @@
         <v>1.133333333333333</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6664903672608402</v>
+        <v>0.6379831804880149</v>
       </c>
       <c r="E157" t="n">
-        <v>0.6553879069988811</v>
+        <v>0.6319424171087191</v>
       </c>
       <c r="F157" t="n">
-        <v>0.5930895626519536</v>
+        <v>0.6058468220653765</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>7.915101127049066</v>
+        <v>7.5685</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.7098134749508782</v>
+        <v>-0.2348378582202102</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.681540988519176</v>
+        <v>-1.282975894590323</v>
       </c>
       <c r="K157" t="n">
         <v>1.734633611048246</v>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="U157" t="n">
-        <v>0.9733014316966139</v>
+        <v>0.9804909965316597</v>
       </c>
       <c r="V157" t="n">
         <v>0</v>
@@ -13500,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>0.6486960286669777</v>
+        <v>0.6255367644071316</v>
       </c>
     </row>
     <row r="158">
@@ -13518,25 +13518,25 @@
         <v>1.95</v>
       </c>
       <c r="D158" t="n">
-        <v>1.383607152542308</v>
+        <v>1.336957887358846</v>
       </c>
       <c r="E158" t="n">
-        <v>1.167795382932826</v>
+        <v>1.160502062704328</v>
       </c>
       <c r="F158" t="n">
-        <v>0.680747480571569</v>
+        <v>0.7064506561652611</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>7.067718800450744</v>
+        <v>7.568500000000002</v>
       </c>
       <c r="I158" t="n">
-        <v>-2.600211751515503</v>
+        <v>-2.376050458715594</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.644707874738133</v>
+        <v>-2.133700690464042</v>
       </c>
       <c r="K158" t="n">
         <v>1.724689254426368</v>
@@ -13571,7 +13571,7 @@
         </is>
       </c>
       <c r="U158" t="n">
-        <v>0.8406892851103515</v>
+        <v>0.8646838351718078</v>
       </c>
       <c r="V158" t="n">
         <v>0</v>
@@ -13583,7 +13583,7 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.163183707944362</v>
+        <v>1.156045873504645</v>
       </c>
     </row>
     <row r="159">
@@ -13601,25 +13601,25 @@
         <v>2.95</v>
       </c>
       <c r="D159" t="n">
-        <v>2.906128898994179</v>
+        <v>2.870457500923537</v>
       </c>
       <c r="E159" t="n">
-        <v>1.91382011444909</v>
+        <v>1.939485082460458</v>
       </c>
       <c r="F159" t="n">
-        <v>0.7313403339631428</v>
+        <v>0.7566233597628431</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>2.55411838850141</v>
+        <v>2.283</v>
       </c>
       <c r="I159" t="n">
-        <v>-3.424431228126796</v>
+        <v>-3.911964671953855</v>
       </c>
       <c r="J159" t="n">
-        <v>0.5093052452431466</v>
+        <v>0.2994483234481423</v>
       </c>
       <c r="K159" t="n">
         <v>1.726812031888895</v>
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="U159" t="n">
-        <v>0.6652003277606507</v>
+        <v>0.6823252046457675</v>
       </c>
       <c r="V159" t="n">
         <v>0</v>
@@ -13666,7 +13666,7 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1.933157896125627</v>
+        <v>1.958585501744631</v>
       </c>
     </row>
     <row r="160">
@@ -13684,13 +13684,13 @@
         <v>4.166666666666666</v>
       </c>
       <c r="D160" t="n">
-        <v>5.813840316867564</v>
+        <v>5.831135618957523</v>
       </c>
       <c r="E160" t="n">
-        <v>2.781880533392974</v>
+        <v>2.82694499569852</v>
       </c>
       <c r="F160" t="n">
-        <v>0.6231332302561798</v>
+        <v>0.622914427083624</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -13702,7 +13702,7 @@
         <v>-0.8307895012025531</v>
       </c>
       <c r="J160" t="n">
-        <v>1.422755954661634</v>
+        <v>1.600170613714041</v>
       </c>
       <c r="K160" t="n">
         <v>1.754658823198128</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="U160" t="n">
-        <v>0.499121108172741</v>
+        <v>0.5054301340257518</v>
       </c>
       <c r="V160" t="n">
         <v>0</v>
@@ -13749,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>2.901810421694299</v>
+        <v>2.947231657412036</v>
       </c>
     </row>
     <row r="161">
@@ -13767,13 +13767,13 @@
         <v>5.133333333333335</v>
       </c>
       <c r="D161" t="n">
-        <v>8.804047024770812</v>
+        <v>8.866079880858408</v>
       </c>
       <c r="E161" t="n">
-        <v>3.314857401269617</v>
+        <v>3.347296123964205</v>
       </c>
       <c r="F161" t="n">
-        <v>0.4479068236592805</v>
+        <v>0.4225167340162068</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="U161" t="n">
-        <v>0.4092178776503607</v>
+        <v>0.4102422774393871</v>
       </c>
       <c r="V161" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>3.602773438210685</v>
+        <v>3.637240802282883</v>
       </c>
     </row>
     <row r="162">
@@ -13850,13 +13850,13 @@
         <v>6.133333333333333</v>
       </c>
       <c r="D162" t="n">
-        <v>12.34808385765951</v>
+        <v>12.42823663756704</v>
       </c>
       <c r="E162" t="n">
-        <v>3.655748476408798</v>
+        <v>3.65004299252855</v>
       </c>
       <c r="F162" t="n">
-        <v>0.1233632708184742</v>
+        <v>0.08623988932032933</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="U162" t="n">
-        <v>0.3404978820149582</v>
+        <v>0.338129456550899</v>
       </c>
       <c r="V162" t="n">
         <v>0</v>
@@ -13915,7 +13915,7 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>4.204496400476157</v>
+        <v>4.202352900146515</v>
       </c>
     </row>
     <row r="163">
@@ -13933,13 +13933,13 @@
         <v>7</v>
       </c>
       <c r="D163" t="n">
-        <v>15.60030706056889</v>
+        <v>15.65761955932985</v>
       </c>
       <c r="E163" t="n">
-        <v>3.599275760317255</v>
+        <v>3.562163432196218</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.3293158150152997</v>
+        <v>-0.3535351397863871</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="U163" t="n">
-        <v>0.2788951591809948</v>
+        <v>0.2756804068911901</v>
       </c>
       <c r="V163" t="n">
         <v>0</v>
@@ -13998,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>4.350850120929759</v>
+        <v>4.31649893106351</v>
       </c>
     </row>
     <row r="164">
@@ -14016,13 +14016,13 @@
         <v>8.033333333333335</v>
       </c>
       <c r="D164" t="n">
-        <v>19.1306981868321</v>
+        <v>19.13640667804469</v>
       </c>
       <c r="E164" t="n">
-        <v>2.933530258911251</v>
+        <v>2.886199740495769</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.9469810641927268</v>
+        <v>-0.9406145323268453</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="U164" t="n">
-        <v>0.1939508287302287</v>
+        <v>0.191431762955647</v>
       </c>
       <c r="V164" t="n">
         <v>0</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>3.710414767523968</v>
+        <v>3.663316067014311</v>
       </c>
     </row>
     <row r="165">
@@ -14099,13 +14099,13 @@
         <v>8.649999999999999</v>
       </c>
       <c r="D165" t="n">
-        <v>20.76196767984735</v>
+        <v>20.73944910058109</v>
       </c>
       <c r="E165" t="n">
-        <v>2.238157617222631</v>
+        <v>2.200735179524798</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.154907638002425</v>
+        <v>-1.134477508960474</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="U165" t="n">
-        <v>0.1384439713399621</v>
+        <v>0.1367566113864195</v>
       </c>
       <c r="V165" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>2.874369258430006</v>
+        <v>2.836256781016594</v>
       </c>
     </row>
     <row r="166">
@@ -14182,13 +14182,13 @@
         <v>9.35</v>
       </c>
       <c r="D166" t="n">
-        <v>22.00516338103091</v>
+        <v>21.9630849058926</v>
       </c>
       <c r="E166" t="n">
-        <v>1.408048648502373</v>
+        <v>1.388394094403374</v>
       </c>
       <c r="F166" t="n">
-        <v>-1.001384581443047</v>
+        <v>-0.979249108064111</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -14235,7 +14235,7 @@
         </is>
       </c>
       <c r="U166" t="n">
-        <v>0.08250442181437796</v>
+        <v>0.08173212272076501</v>
       </c>
       <c r="V166" t="n">
         <v>0</v>
@@ -14247,7 +14247,7 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.815523281682878</v>
+        <v>1.795089550854996</v>
       </c>
     </row>
     <row r="167">
@@ -14265,13 +14265,13 @@
         <v>10.08333333333333</v>
       </c>
       <c r="D167" t="n">
-        <v>22.7550570219956</v>
+        <v>22.70493261460721</v>
       </c>
       <c r="E167" t="n">
-        <v>0.8154315760058175</v>
+        <v>0.8095150146725683</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.6178923513600627</v>
+        <v>-0.6030494348381827</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
         </is>
       </c>
       <c r="U167" t="n">
-        <v>0.04592680060041407</v>
+        <v>0.04574532707586186</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.045066966500244</v>
+        <v>1.03864456869061</v>
       </c>
     </row>
     <row r="168">
@@ -14348,13 +14348,13 @@
         <v>11.2</v>
       </c>
       <c r="D168" t="n">
-        <v>23.31338769086442</v>
+        <v>23.26525215107486</v>
       </c>
       <c r="E168" t="n">
-        <v>0.4489009626739628</v>
+        <v>0.4529433107423557</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.2062592192850646</v>
+        <v>-0.1999345879755507</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -14401,7 +14401,7 @@
         </is>
       </c>
       <c r="U168" t="n">
-        <v>0.02435038000474394</v>
+        <v>0.02456396897979753</v>
       </c>
       <c r="V168" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>0.5676898494704686</v>
+        <v>0.5714869321461707</v>
       </c>
     </row>
     <row r="169">
@@ -14431,13 +14431,13 @@
         <v>12.66666666666667</v>
       </c>
       <c r="D169" t="n">
-        <v>23.87334480746527</v>
+        <v>23.83549408839162</v>
       </c>
       <c r="E169" t="n">
-        <v>0.3813603406285093</v>
+        <v>0.3896822104788864</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.02127626603525196</v>
+        <v>-0.01912087657541039</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="U169" t="n">
-        <v>0.02039997424611603</v>
+        <v>0.02077447913967906</v>
       </c>
       <c r="V169" t="n">
         <v>0</v>
@@ -14496,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0.4870156192409393</v>
+        <v>0.4951699747232352</v>
       </c>
     </row>
     <row r="170">
@@ -14514,13 +14514,13 @@
         <v>13.85</v>
       </c>
       <c r="D170" t="n">
-        <v>24.32421200879139</v>
+        <v>24.29745905343904</v>
       </c>
       <c r="E170" t="n">
-        <v>0.3798361778873236</v>
+        <v>0.3899806387838662</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.002007947925256201</v>
+        <v>-0.0007188895655968197</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="U170" t="n">
-        <v>0.02025147405166017</v>
+        <v>0.02068617890031077</v>
       </c>
       <c r="V170" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>0.4926011483231197</v>
+        <v>0.5026215848024155</v>
       </c>
     </row>
     <row r="171">
@@ -14597,13 +14597,13 @@
         <v>15.31666666666667</v>
       </c>
       <c r="D171" t="n">
-        <v>24.87916300213528</v>
+        <v>24.86868118062512</v>
       </c>
       <c r="E171" t="n">
-        <v>0.3755824823665321</v>
+        <v>0.3871609944455874</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.003811934374442154</v>
+        <v>-0.003152232424426527</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -14650,7 +14650,7 @@
         </is>
       </c>
       <c r="U171" t="n">
-        <v>0.01996791396703792</v>
+        <v>0.02043986293642015</v>
       </c>
       <c r="V171" t="n">
         <v>0</v>
@@ -14662,7 +14662,7 @@
         <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>0.4967849863985501</v>
+        <v>0.5083124347415087</v>
       </c>
     </row>
     <row r="172">
@@ -14680,13 +14680,13 @@
         <v>17.98333333333333</v>
       </c>
       <c r="D172" t="n">
-        <v>25.86717352522962</v>
+        <v>25.88991710410795</v>
       </c>
       <c r="E172" t="n">
-        <v>0.3609970213513023</v>
+        <v>0.3727926284734087</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.006548620897526818</v>
+        <v>-0.006843666254660399</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="U172" t="n">
-        <v>0.01918567558594298</v>
+        <v>0.01962902201719036</v>
       </c>
       <c r="V172" t="n">
         <v>0</v>
@@ -14745,7 +14745,7 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>0.4962791995803485</v>
+        <v>0.5081937528597683</v>
       </c>
     </row>
     <row r="173">
@@ -14763,13 +14763,13 @@
         <v>23.56666666666667</v>
       </c>
       <c r="D173" t="n">
-        <v>27.77160328645161</v>
+        <v>27.85244440090797</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3118194120367637</v>
+        <v>0.3175668727475074</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.01127914206599798</v>
+        <v>-0.0132245234440517</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="U173" t="n">
-        <v>0.01700789928688593</v>
+        <v>0.01718166418319534</v>
       </c>
       <c r="V173" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>0.4723366317313193</v>
+        <v>0.47855134637752</v>
       </c>
     </row>
     <row r="174">
@@ -14846,13 +14846,13 @@
         <v>25.13333333333333</v>
       </c>
       <c r="D174" t="n">
-        <v>28.24725212243168</v>
+        <v>28.33504989601718</v>
       </c>
       <c r="E174" t="n">
-        <v>0.2930624064029619</v>
+        <v>0.295383108330789</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.01311373377644165</v>
+        <v>-0.01569914881581858</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="U174" t="n">
-        <v>0.01625977611303667</v>
+        <v>0.01630953105759465</v>
       </c>
       <c r="V174" t="n">
         <v>0</v>
@@ -14911,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>0.4592939953192389</v>
+        <v>0.4621313762975864</v>
       </c>
     </row>
     <row r="175">
@@ -14929,13 +14929,13 @@
         <v>26.68333333333333</v>
       </c>
       <c r="D175" t="n">
-        <v>28.68533069149266</v>
+        <v>28.77347494174718</v>
       </c>
       <c r="E175" t="n">
-        <v>0.2709861119968053</v>
+        <v>0.2686888959857558</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.01517652676585166</v>
+        <v>-0.01848158800336817</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -14982,7 +14982,7 @@
         </is>
       </c>
       <c r="U175" t="n">
-        <v>0.01540456339472086</v>
+        <v>0.01529578606344143</v>
       </c>
       <c r="V175" t="n">
         <v>0</v>
@@ -14994,7 +14994,7 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>0.4418849951356306</v>
+        <v>0.4401129170107577</v>
       </c>
     </row>
     <row r="176">
@@ -15012,13 +15012,13 @@
         <v>28.15</v>
       </c>
       <c r="D176" t="n">
-        <v>29.0666155901646</v>
+        <v>29.14789225999456</v>
       </c>
       <c r="E176" t="n">
-        <v>0.2474313265274128</v>
+        <v>0.2398345941170521</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.01681485666939997</v>
+        <v>-0.02069148174897057</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="U176" t="n">
-        <v>0.01451603799878851</v>
+        <v>0.01423167421311976</v>
       </c>
       <c r="V176" t="n">
         <v>0</v>
@@ -15077,7 +15077,7 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>0.4219320964030077</v>
+        <v>0.4148233066433576</v>
       </c>
     </row>
     <row r="177">
@@ -15095,13 +15095,13 @@
         <v>31.18333333333333</v>
       </c>
       <c r="D177" t="n">
-        <v>29.73851507129508</v>
+        <v>29.77846555771898</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1916911875825731</v>
+        <v>0.1706834348307833</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.01966905005867627</v>
+        <v>-0.02454141704346991</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="U177" t="n">
-        <v>0.0124849574353011</v>
+        <v>0.01177084175533188</v>
       </c>
       <c r="V177" t="n">
         <v>0</v>
@@ -15160,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>0.3712840948541792</v>
+        <v>0.3505176057965108</v>
       </c>
     </row>
     <row r="178">
@@ -15178,13 +15178,13 @@
         <v>34.18333333333334</v>
       </c>
       <c r="D178" t="n">
-        <v>30.22512911004171</v>
+        <v>30.18014854935354</v>
       </c>
       <c r="E178" t="n">
-        <v>0.1288471294861875</v>
+        <v>0.0918836944431245</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.02243699086140478</v>
+        <v>-0.02827500882794872</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -15231,7 +15231,7 @@
         </is>
       </c>
       <c r="U178" t="n">
-        <v>0.01027545007842259</v>
+        <v>0.009057043657529436</v>
       </c>
       <c r="V178" t="n">
         <v>0</v>
@@ -15243,7 +15243,7 @@
         <v>0</v>
       </c>
       <c r="Y178" t="n">
-        <v>0.3105768052841109</v>
+        <v>0.2733429230022186</v>
       </c>
     </row>
     <row r="179">
@@ -15261,13 +15261,13 @@
         <v>35.7</v>
       </c>
       <c r="D179" t="n">
-        <v>30.39497004602677</v>
+        <v>30.28729344170724</v>
       </c>
       <c r="E179" t="n">
-        <v>0.09367601066510289</v>
+        <v>0.04745994975275636</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.02375192891203302</v>
+        <v>-0.03004868906636723</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="U179" t="n">
-        <v>0.009055564318615449</v>
+        <v>0.007540598768276501</v>
       </c>
       <c r="V179" t="n">
         <v>0</v>
@@ -15326,7 +15326,7 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>0.2752436062141854</v>
+        <v>0.2283843276209666</v>
       </c>
     </row>
     <row r="180">
@@ -15344,13 +15344,13 @@
         <v>36.75</v>
       </c>
       <c r="D180" t="n">
-        <v>30.48002205897316</v>
+        <v>30.32027265253625</v>
       </c>
       <c r="E180" t="n">
-        <v>0.06832782351850142</v>
+        <v>0.01535759468346498</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.02453033231958895</v>
+        <v>-0.03109865392275937</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -15397,7 +15397,7 @@
         </is>
       </c>
       <c r="U180" t="n">
-        <v>0.008181315441372846</v>
+        <v>0.006446102990600344</v>
       </c>
       <c r="V180" t="n">
         <v>0</v>
@@ -15409,7 +15409,7 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>0.2493666751244621</v>
+        <v>0.1954476002213318</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -3241,10 +3241,10 @@
         <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.850049343677429</v>
+        <v>-0.4472222847442788</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4719308012271115</v>
+        <v>-0.5768563078528495</v>
       </c>
       <c r="K34" t="n">
         <v>1.655684716242998</v>
@@ -3321,13 +3321,13 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>9.453302605195947</v>
+        <v>9.580200376194631</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.750040592334428</v>
+        <v>-0.781459541027532</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1792222607110113</v>
+        <v>-0.4013990763908181</v>
       </c>
       <c r="K35" t="n">
         <v>1.607841572062204</v>
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>8.756397578515919</v>
+        <v>8.511552343727802</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.44398334508746</v>
+        <v>-1.059153709041937</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3511064044088421</v>
+        <v>-0.09026975965347983</v>
       </c>
       <c r="K36" t="n">
         <v>1.556535326712928</v>
@@ -3487,13 +3487,13 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>7.990826846992402</v>
+        <v>8.048046688364472</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.537896942261227</v>
+        <v>-1.065839589941779</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.970175822507692e-05</v>
+        <v>-0.3417396219993769</v>
       </c>
       <c r="K37" t="n">
         <v>1.542135465609338</v>
@@ -3570,13 +3570,13 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>7.337196350401693</v>
+        <v>7.4996969262132</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.404411910829691</v>
+        <v>-1.443420798551506</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.877943943965775</v>
+        <v>-1.586357267637079</v>
       </c>
       <c r="K38" t="n">
         <v>1.530160174384962</v>
@@ -3653,13 +3653,13 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>6.567577188322776</v>
+        <v>6.593100069715484</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.393207464740226</v>
+        <v>-2.650577623527684</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.944494379525494</v>
+        <v>-2.957633013275597</v>
       </c>
       <c r="K39" t="n">
         <v>1.523721788805478</v>
@@ -3736,13 +3736,13 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>4.94398888566147</v>
+        <v>4.849119302685519</v>
       </c>
       <c r="I40" t="n">
-        <v>-4.348906290355183</v>
+        <v>-4.401053811827101</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.575996645276082</v>
+        <v>-2.125958612544011</v>
       </c>
       <c r="K40" t="n">
         <v>1.522114644830368</v>
@@ -3769,7 +3769,7 @@
         <v>-0.01499999999999346</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.02053185271771731</v>
+        <v>-0.07065467200879998</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3819,13 +3819,13 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.218670897967584</v>
+        <v>2.192046257888375</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.969204110016304</v>
+        <v>-4.776536236071689</v>
       </c>
       <c r="J41" t="n">
-        <v>1.518203753949354</v>
+        <v>1.716024924205575</v>
       </c>
       <c r="K41" t="n">
         <v>1.525106395926922</v>
@@ -3849,10 +3849,10 @@
         <v>37.02</v>
       </c>
       <c r="R41" t="n">
-        <v>0.009468147282291284</v>
+        <v>-0.04065467200879169</v>
       </c>
       <c r="S41" t="n">
-        <v>0.02928809334355157</v>
+        <v>-0.01526552380407617</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3902,13 +3902,13 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04182457744715143</v>
+        <v>0.1345703475717841</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.946433245751134</v>
+        <v>-2.794491745574413</v>
       </c>
       <c r="J42" t="n">
-        <v>3.863750883367386</v>
+        <v>3.741568427766722</v>
       </c>
       <c r="K42" t="n">
         <v>1.532151522940201</v>
@@ -3929,13 +3929,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>37.029</v>
+        <v>36.98135547566276</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01444398282785464</v>
+        <v>-0.03119253473655625</v>
       </c>
       <c r="S42" t="n">
-        <v>0.03224000853379445</v>
+        <v>0.06654946934533441</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3985,13 +3985,13 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.07023299447472457</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.00749900265779244</v>
+        <v>-0.02907206569218013</v>
       </c>
       <c r="J43" t="n">
-        <v>1.668520525197393</v>
+        <v>1.592786328842051</v>
       </c>
       <c r="K43" t="n">
         <v>1.555422776715727</v>
@@ -4015,10 +4015,10 @@
         <v>37.035</v>
       </c>
       <c r="R43" t="n">
-        <v>0.08023707918444956</v>
+        <v>0.107421642620114</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.09645039174700543</v>
+        <v>-0.06882179732963238</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4068,13 +4068,13 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.03195695517542099</v>
+        <v>0.0851462306000212</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.02380247631305794</v>
+        <v>6.190289078129851e-05</v>
       </c>
       <c r="J44" t="n">
-        <v>0.01471127293890823</v>
+        <v>-0.1532415638569897</v>
       </c>
       <c r="K44" t="n">
         <v>1.59304854146272</v>
@@ -4101,7 +4101,7 @@
         <v>-0.1814156079854925</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.2252887376842256</v>
+        <v>-0.2351560928332871</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.012</v>
+        <v>0.1300299759548794</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.008059254539662348</v>
+        <v>-0.1249559577765238</v>
       </c>
       <c r="J45" t="n">
-        <v>0.01866376470394637</v>
+        <v>-0.1244373812770198</v>
       </c>
       <c r="K45" t="n">
         <v>1.617459214584841</v>
@@ -4237,10 +4237,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.007855297157622764</v>
+        <v>-0.08511867504367673</v>
       </c>
       <c r="J46" t="n">
-        <v>0.00671787429353536</v>
+        <v>0.09742484537920557</v>
       </c>
       <c r="K46" t="n">
         <v>1.654681843835648</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.006118863049095637</v>
+        <v>0.06630296792875882</v>
       </c>
       <c r="K47" t="n">
         <v>1.686078963726573</v>
@@ -4972,10 +4972,10 @@
         <v>0.04347826086957973</v>
       </c>
       <c r="E55" t="n">
-        <v>0.05539241075248286</v>
+        <v>0.03206480856453983</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1026405685546561</v>
+        <v>0.1173116762619779</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -4984,10 +4984,10 @@
         <v>9.5</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.716529056171157</v>
+        <v>0.5216257740155958</v>
       </c>
       <c r="J55" t="n">
-        <v>0.5791229930317843</v>
+        <v>-1.406106090828408</v>
       </c>
       <c r="K55" t="n">
         <v>1.64693558111481</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>1.240963234122181</v>
+        <v>0.7044283837996703</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.05395492322272152</v>
+        <v>0.0306273210347785</v>
       </c>
     </row>
     <row r="56">
@@ -5052,25 +5052,25 @@
         <v>0.6833333333333336</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1168352151527269</v>
+        <v>0.1047164888879415</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1593108700762405</v>
+        <v>0.1471690295379824</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2015110197100003</v>
+        <v>0.219578726587122</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>9.105635635996398</v>
+        <v>9.583212157325173</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.437708106766209</v>
+        <v>-0.2780779964784994</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2369383222997708</v>
+        <v>-0.9344903106177233</v>
       </c>
       <c r="K56" t="n">
         <v>1.61221262164786</v>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>1.334289649061833</v>
+        <v>1.376142376779205</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1558920182241958</v>
+        <v>0.144104797906225</v>
       </c>
     </row>
     <row r="57">
@@ -5135,25 +5135,25 @@
         <v>1.716666666666666</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3626480243210458</v>
+        <v>0.3467221741710743</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4447864876467248</v>
+        <v>0.4539683765743199</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4201441563038889</v>
+        <v>0.4390613414466106</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>8.871180293458432</v>
+        <v>8.671055688244687</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.46022100183162</v>
+        <v>-0.8752441916107419</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.6856675861344117</v>
+        <v>0.004948124998967129</v>
       </c>
       <c r="K57" t="n">
         <v>1.569146791633991</v>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>1.203826371130069</v>
+        <v>1.286644513616195</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
@@ -5200,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.4365652551158936</v>
+        <v>0.4461081831462915</v>
       </c>
     </row>
     <row r="58">
@@ -5218,25 +5218,25 @@
         <v>2.149999999999998</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5929873603067661</v>
+        <v>0.5833783805196808</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6529944237722252</v>
+        <v>0.6700614399477864</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5479059599717013</v>
+        <v>0.5604520829365596</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>8.629350594609635</v>
+        <v>8.293143905122815</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.8779843476295284</v>
+        <v>-0.7671840888774035</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.395868688688974</v>
+        <v>-0.2385815774577296</v>
       </c>
       <c r="K58" t="n">
         <v>1.554841242700892</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>1.081754998238168</v>
+        <v>1.129148547358778</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.6414670409039019</v>
+        <v>0.6587208509243141</v>
       </c>
     </row>
     <row r="59">
@@ -5301,25 +5301,25 @@
         <v>2.616666666666665</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9587505364055194</v>
+        <v>0.958357359331045</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9425698129010216</v>
+        <v>0.9626520361833426</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6768825422824154</v>
+        <v>0.6786203956427848</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>8.058846362850151</v>
+        <v>7.987853702364046</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.746396628285529</v>
+        <v>-1.123748837536048</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.111964608948109</v>
+        <v>-1.825756538356935</v>
       </c>
       <c r="K59" t="n">
         <v>1.542136954641748</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>0.967535852789203</v>
+        <v>0.9888940283724944</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.92762551785322</v>
+        <v>0.9477138696893034</v>
       </c>
     </row>
     <row r="60">
@@ -5384,25 +5384,25 @@
         <v>3.166666666666666</v>
       </c>
       <c r="D60" t="n">
-        <v>1.580094903073477</v>
+        <v>1.590963500740558</v>
       </c>
       <c r="E60" t="n">
-        <v>1.351391064761791</v>
+        <v>1.369367393793435</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8097994291606467</v>
+        <v>0.8003988144159402</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>6.758736816644348</v>
+        <v>7.06541922892391</v>
       </c>
       <c r="I60" t="n">
-        <v>-3.070731551769549</v>
+        <v>-2.816117052897328</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.043749925516509</v>
+        <v>-3.007204652897132</v>
       </c>
       <c r="K60" t="n">
         <v>1.530981294268405</v>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>0.8446115965716684</v>
+        <v>0.8500679495247661</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.334566478819645</v>
+        <v>1.35242708084327</v>
       </c>
     </row>
     <row r="61">
@@ -5467,25 +5467,25 @@
         <v>3.666666666666665</v>
       </c>
       <c r="D61" t="n">
-        <v>2.356551360207286</v>
+        <v>2.375271929188412</v>
       </c>
       <c r="E61" t="n">
-        <v>1.786512625769871</v>
+        <v>1.797256049198657</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9330191530199066</v>
+        <v>0.9132926948375664</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>4.902054671117055</v>
+        <v>5.139650036645999</v>
       </c>
       <c r="I61" t="n">
-        <v>-3.927092081098102</v>
+        <v>-4.287979167554274</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.734768093055103</v>
+        <v>-1.46214164687568</v>
       </c>
       <c r="K61" t="n">
         <v>1.524640199129953</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>0.7522986492445932</v>
+        <v>0.7508467196475784</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -5532,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.77283040515945</v>
+        <v>1.783465136302094</v>
       </c>
     </row>
     <row r="62">
@@ -5550,25 +5550,25 @@
         <v>4.166666666666667</v>
       </c>
       <c r="D62" t="n">
-        <v>3.366607528843351</v>
+        <v>3.388219549939217</v>
       </c>
       <c r="E62" t="n">
-        <v>2.284410217781698</v>
+        <v>2.282660088631002</v>
       </c>
       <c r="F62" t="n">
-        <v>1.065598295420997</v>
+        <v>1.034761672204584</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2.831644735546242</v>
+        <v>2.77744006136963</v>
       </c>
       <c r="I62" t="n">
-        <v>-3.805499644824648</v>
+        <v>-4.278258699773001</v>
       </c>
       <c r="J62" t="n">
-        <v>1.272672679605255</v>
+        <v>1.518447182276055</v>
       </c>
       <c r="K62" t="n">
         <v>1.522129179305727</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>0.6778989462490556</v>
+        <v>0.6730542313940386</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.282219696237044</v>
+        <v>2.280455504978595</v>
       </c>
     </row>
     <row r="63">
@@ -5633,25 +5633,25 @@
         <v>4.649999999999998</v>
       </c>
       <c r="D63" t="n">
-        <v>4.594224977164805</v>
+        <v>4.61147150190854</v>
       </c>
       <c r="E63" t="n">
-        <v>2.832062958726937</v>
+        <v>2.812675436862577</v>
       </c>
       <c r="F63" t="n">
-        <v>1.195591975006719</v>
+        <v>1.153861849181766</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.148988968510205</v>
+        <v>0.9180714742047679</v>
       </c>
       <c r="I63" t="n">
-        <v>-2.709374935384301</v>
+        <v>-2.843973531958443</v>
       </c>
       <c r="J63" t="n">
-        <v>2.29513168449791</v>
+        <v>2.866403054024888</v>
       </c>
       <c r="K63" t="n">
         <v>1.523534166455679</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="U63" t="n">
-        <v>0.6210638555092903</v>
+        <v>0.6145542271862207</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.853307077395055</v>
+        <v>2.833999305046683</v>
       </c>
     </row>
     <row r="64">
@@ -5716,13 +5716,13 @@
         <v>5.500000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>7.438214479573144</v>
+        <v>7.42350198278938</v>
       </c>
       <c r="E64" t="n">
-        <v>3.941768779790767</v>
+        <v>3.879079296358552</v>
       </c>
       <c r="F64" t="n">
-        <v>1.354245977252376</v>
+        <v>1.319011485462432</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -5731,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7177229584811761</v>
+        <v>-0.5586333404585631</v>
       </c>
       <c r="J64" t="n">
-        <v>1.588964587857402</v>
+        <v>1.673111580654899</v>
       </c>
       <c r="K64" t="n">
         <v>1.535708118407536</v>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="U64" t="n">
-        <v>0.5443507466733761</v>
+        <v>0.5369562825288021</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>4.048997605872358</v>
+        <v>3.986096028023777</v>
       </c>
     </row>
     <row r="65">
@@ -5799,25 +5799,25 @@
         <v>6.499999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>12.08104064401971</v>
+        <v>11.97412027018452</v>
       </c>
       <c r="E65" t="n">
-        <v>5.353320306663477</v>
+        <v>5.273877498979592</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9344531791093651</v>
+        <v>1.2534574386676</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.012</v>
+        <v>0.07625580539979478</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.01599999999999988</v>
+        <v>-0.08025580539979386</v>
       </c>
       <c r="J65" t="n">
-        <v>0.2363916710919004</v>
+        <v>0.1466861104041142</v>
       </c>
       <c r="K65" t="n">
         <v>1.567042522912585</v>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>0.4690354601005478</v>
+        <v>0.4663576415917471</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>5.666436456961203</v>
+        <v>5.584222489339185</v>
       </c>
     </row>
     <row r="66">
@@ -5882,13 +5882,13 @@
         <v>7.000000000000002</v>
       </c>
       <c r="D66" t="n">
-        <v>14.93532433290569</v>
+        <v>14.79187382257044</v>
       </c>
       <c r="E66" t="n">
-        <v>5.701272309277323</v>
+        <v>5.865271027325035</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4084376969089329</v>
+        <v>0.932643690043542</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -5897,10 +5897,10 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.01413698630136974</v>
+        <v>-0.08983560636140131</v>
       </c>
       <c r="J66" t="n">
-        <v>0.01030136986301366</v>
+        <v>0.04022873128209602</v>
       </c>
       <c r="K66" t="n">
         <v>1.589669852465964</v>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>0.4116858025337201</v>
+        <v>0.4264748812650871</v>
       </c>
       <c r="V66" t="n">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>6.148660984093677</v>
+        <v>6.30836263216888</v>
       </c>
     </row>
     <row r="67">
@@ -5965,13 +5965,13 @@
         <v>7.716666666666667</v>
       </c>
       <c r="D67" t="n">
-        <v>19.01374249808414</v>
+        <v>19.23133666593164</v>
       </c>
       <c r="E67" t="n">
-        <v>5.69869421201685</v>
+        <v>6.276712846894617</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7311813029352114</v>
+        <v>7.40552010825013e-08</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.009254185692541808</v>
+        <v>0.0588071152753361</v>
       </c>
       <c r="K67" t="n">
         <v>1.626224931416015</v>
@@ -6010,7 +6010,7 @@
         <v>-0.03771929824561937</v>
       </c>
       <c r="S67" t="n">
-        <v>0.02825412931957202</v>
+        <v>-0.0885920884859628</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>0.3306737531422033</v>
+        <v>0.3573386968156522</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>6.287345593120893</v>
+        <v>6.872100782227083</v>
       </c>
     </row>
     <row r="68">
@@ -6048,13 +6048,13 @@
         <v>8.35</v>
       </c>
       <c r="D68" t="n">
-        <v>22.62732483003128</v>
+        <v>23.25254625119462</v>
       </c>
       <c r="E68" t="n">
-        <v>6.57302390838727</v>
+        <v>5.955392228127655</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3643376804520155</v>
+        <v>-1.446266843554018</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -6090,10 +6090,10 @@
         <v>36.98999999999999</v>
       </c>
       <c r="R68" t="n">
-        <v>-0.05735754113967673</v>
+        <v>-0.1967577963355822</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0009585017336984289</v>
+        <v>-0.05830071606213131</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>0.3177460092061178</v>
+        <v>0.2833733180335009</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>7.189742163752938</v>
+        <v>6.58915118392846</v>
       </c>
     </row>
     <row r="69">
@@ -6131,13 +6131,13 @@
         <v>9.066666666666665</v>
       </c>
       <c r="D69" t="n">
-        <v>28.04139664979665</v>
+        <v>27.2011495703605</v>
       </c>
       <c r="E69" t="n">
-        <v>4.896896416768156</v>
+        <v>4.157471032770529</v>
       </c>
       <c r="F69" t="n">
-        <v>-3.234733537074055</v>
+        <v>-2.571047539240066</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -6170,13 +6170,13 @@
         <v>0.04051199681788326</v>
       </c>
       <c r="Q69" t="n">
-        <v>36.96</v>
+        <v>36.74704776804941</v>
       </c>
       <c r="R69" t="n">
-        <v>-0.03074710479239329</v>
+        <v>-0.08217564023663115</v>
       </c>
       <c r="S69" t="n">
-        <v>0.03446503999555002</v>
+        <v>0.2002915432463269</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>0.1923992778945267</v>
+        <v>0.1706100437168539</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>5.395144466574874</v>
+        <v>4.640789317347886</v>
       </c>
     </row>
     <row r="70">
@@ -6214,13 +6214,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D70" t="n">
-        <v>29.50002045375516</v>
+        <v>29.38709327217807</v>
       </c>
       <c r="E70" t="n">
-        <v>1.154448483606217</v>
+        <v>1.863914303451672</v>
       </c>
       <c r="F70" t="n">
-        <v>-2.599403986552142</v>
+        <v>-1.937930766168051</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -6256,10 +6256,10 @@
         <v>36.945</v>
       </c>
       <c r="R70" t="n">
-        <v>-0.003671328671323693</v>
+        <v>0.1337619892107362</v>
       </c>
       <c r="S70" t="n">
-        <v>0.02811750367545162</v>
+        <v>0.09494554408321854</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6267,19 +6267,19 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>0.03984885440305574</v>
+        <v>0.06414132474724349</v>
       </c>
       <c r="V70" t="n">
-        <v>0.002155182786958192</v>
+        <v>0.002163464610398861</v>
       </c>
       <c r="W70" t="n">
-        <v>0.002076448063670487</v>
+        <v>0.002036244995661479</v>
       </c>
       <c r="X70" t="n">
         <v>0.06357793629684773</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.175542019948856</v>
+        <v>1.884927092948308</v>
       </c>
     </row>
     <row r="71">
@@ -6297,13 +6297,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D71" t="n">
-        <v>30.03193620630886</v>
+        <v>30.51827123721507</v>
       </c>
       <c r="E71" t="n">
-        <v>0.6948205432293904</v>
+        <v>0.7213387167597531</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.145240400931089</v>
+        <v>-0.6783927277655555</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -6342,7 +6342,7 @@
         <v>0.02289665284659392</v>
       </c>
       <c r="S71" t="n">
-        <v>-0.008859523896477145</v>
+        <v>-0.06729891126568134</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -6350,19 +6350,19 @@
         </is>
       </c>
       <c r="U71" t="n">
-        <v>0.001113312725761866</v>
+        <v>0.001613547458548002</v>
       </c>
       <c r="V71" t="n">
-        <v>0.00166768333386379</v>
+        <v>0.001641107358461638</v>
       </c>
       <c r="W71" t="n">
-        <v>0.001663124127076932</v>
+        <v>0.001634604904815281</v>
       </c>
       <c r="X71" t="n">
         <v>0.05008375949492182</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.03343493675775222</v>
+        <v>0.04924267899408696</v>
       </c>
     </row>
     <row r="72">
@@ -6380,13 +6380,13 @@
         <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>30.88306102035976</v>
+        <v>30.95476622841004</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7859965146668575</v>
+        <v>0.3716426023733312</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1340465429635165</v>
+        <v>-0.1702221617721579</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -6433,19 +6433,19 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>-0.01233032053743415</v>
+        <v>-0.02577506307782374</v>
       </c>
       <c r="V72" t="n">
-        <v>0.001125524401299257</v>
+        <v>0.001122917178851983</v>
       </c>
       <c r="W72" t="n">
-        <v>0.001192959288930269</v>
+        <v>0.00126355522341435</v>
       </c>
       <c r="X72" t="n">
         <v>0.03475963876522885</v>
       </c>
       <c r="Y72" t="n">
-        <v>-0.3807980415581744</v>
+        <v>-0.797861052096557</v>
       </c>
     </row>
     <row r="73">
@@ -6463,13 +6463,13 @@
         <v>13</v>
       </c>
       <c r="D73" t="n">
-        <v>31.57132226167865</v>
+        <v>31.243749582257</v>
       </c>
       <c r="E73" t="n">
-        <v>0.415708750928097</v>
+        <v>0.3995574467914267</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.3471285004430657</v>
+        <v>0.2133105311547059</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -6516,19 +6516,19 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>-0.03537132505043111</v>
+        <v>-0.03575021874534758</v>
       </c>
       <c r="V73" t="n">
-        <v>0.0005394745358670995</v>
+        <v>0.0005451306149727292</v>
       </c>
       <c r="W73" t="n">
-        <v>0.0007674293396487528</v>
+        <v>0.0007779428209024674</v>
       </c>
       <c r="X73" t="n">
         <v>0.01703192442382971</v>
       </c>
       <c r="Y73" t="n">
-        <v>-1.116719501989747</v>
+        <v>-1.11697088199055</v>
       </c>
     </row>
     <row r="74">
@@ -6546,13 +6546,13 @@
         <v>14.05</v>
       </c>
       <c r="D74" t="n">
-        <v>31.7073273294973</v>
+        <v>31.78519283885927</v>
       </c>
       <c r="E74" t="n">
-        <v>0.07675691324638123</v>
+        <v>0.8279322491309813</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.2010329824318151</v>
+        <v>0.510325153787894</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -6599,19 +6599,19 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>-0.05101495077145059</v>
+        <v>-0.02738801091550864</v>
       </c>
       <c r="V74" t="n">
-        <v>-6.939169827867749e-05</v>
+        <v>-6.922170654827162e-05</v>
       </c>
       <c r="W74" t="n">
-        <v>0.0002898453091343708</v>
+        <v>0.0001231666903000812</v>
       </c>
       <c r="X74" t="n">
         <v>-0.002200225291271741</v>
       </c>
       <c r="Y74" t="n">
-        <v>-1.617547742808574</v>
+        <v>-0.8705332084222246</v>
       </c>
     </row>
     <row r="75">
@@ -6629,13 +6629,13 @@
         <v>14.91666666666667</v>
       </c>
       <c r="D75" t="n">
-        <v>31.73610005685744</v>
+        <v>32.72611599996809</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.01035831164603707</v>
+        <v>1.343428891889367</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.151935303947722e-06</v>
+        <v>0.679282483346842</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="U75" t="n">
-        <v>-0.05480786681970858</v>
+        <v>-0.01343081083854204</v>
       </c>
       <c r="V75" t="n">
-        <v>-0.0005552288789014829</v>
+        <v>-0.0005384323411703187</v>
       </c>
       <c r="W75" t="n">
-        <v>-0.0001663567120984929</v>
+        <v>-0.0004460209975923221</v>
       </c>
       <c r="X75" t="n">
         <v>-0.01762079925527425</v>
       </c>
       <c r="Y75" t="n">
-        <v>-1.739387945293189</v>
+        <v>-0.4395382734757554</v>
       </c>
     </row>
     <row r="76">
@@ -6733,13 +6733,13 @@
         <v>-0.5061904718760818</v>
       </c>
       <c r="K76" t="n">
-        <v>1.778200175321474</v>
+        <v>1.77821215131981</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.02106652976158929</v>
+        <v>-0.0210921243459441</v>
       </c>
       <c r="M76" t="n">
-        <v>1.665084600355887e-06</v>
+        <v>1.381190167744351e-06</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>2.376459896613446</v>
+        <v>2.376445582965106</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.3192084404339841</v>
+        <v>0.3192065178106021</v>
       </c>
     </row>
     <row r="77">
@@ -6816,13 +6816,13 @@
         <v>-0.6735818373521119</v>
       </c>
       <c r="K77" t="n">
-        <v>1.762459288572748</v>
+        <v>1.762453489098573</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.02090916823501221</v>
+        <v>-0.02093097491068874</v>
       </c>
       <c r="M77" t="n">
-        <v>0.0004179656529385324</v>
+        <v>0.0004283506371798862</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>0.5729714079237874</v>
+        <v>0.5729589959772375</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.1868745341496994</v>
+        <v>0.1868704859952936</v>
       </c>
     </row>
     <row r="78">
@@ -6899,13 +6899,13 @@
         <v>-0.9171055936733736</v>
       </c>
       <c r="K78" t="n">
-        <v>1.748566468720244</v>
+        <v>1.748547253805597</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.02050717614984188</v>
+        <v>-0.02051889835345411</v>
       </c>
       <c r="M78" t="n">
-        <v>0.0009882974315627568</v>
+        <v>0.001013298779587612</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>0.5739572992901764</v>
+        <v>0.5739504664430914</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.2380644767494451</v>
+        <v>0.2380616426393676</v>
       </c>
     </row>
     <row r="79">
@@ -6982,13 +6982,13 @@
         <v>-1.273903336105778</v>
       </c>
       <c r="K79" t="n">
-        <v>1.735116387039626</v>
+        <v>1.735094957960635</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.01959143832626187</v>
+        <v>-0.01957990987123859</v>
       </c>
       <c r="M79" t="n">
-        <v>0.00253471617360424</v>
+        <v>0.002574758609407706</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>0.9805732184429676</v>
+        <v>0.9805797232721624</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.6374266726475046</v>
+        <v>0.6374309011452362</v>
       </c>
     </row>
     <row r="80">
@@ -7065,13 +7065,13 @@
         <v>-1.646407728728741</v>
       </c>
       <c r="K80" t="n">
-        <v>1.722444550951895</v>
+        <v>1.722440707310612</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.01712755458503623</v>
+        <v>-0.01708588687424384</v>
       </c>
       <c r="M80" t="n">
-        <v>0.007941170970118086</v>
+        <v>0.007971637345060081</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>1.064711167499284</v>
+        <v>1.064735336395441</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.356938230057074</v>
+        <v>1.356969032494557</v>
       </c>
     </row>
     <row r="81">
@@ -7148,13 +7148,13 @@
         <v>-0.3065132117171383</v>
       </c>
       <c r="K81" t="n">
-        <v>1.710130129992031</v>
+        <v>1.710176936062064</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.006087677361729882</v>
+        <v>-0.006035977785060487</v>
       </c>
       <c r="M81" t="n">
-        <v>0.02139020794298874</v>
+        <v>0.0213650144170448</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="U81" t="n">
-        <v>0.8355780036318021</v>
+        <v>0.8356083316023313</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.395472641687409</v>
+        <v>2.395559587278802</v>
       </c>
     </row>
     <row r="82">
@@ -7231,13 +7231,13 @@
         <v>2.175871313460834</v>
       </c>
       <c r="K82" t="n">
-        <v>1.713757703395073</v>
+        <v>1.713843790339649</v>
       </c>
       <c r="L82" t="n">
-        <v>0.02305119094695729</v>
+        <v>0.0230386346724889</v>
       </c>
       <c r="M82" t="n">
-        <v>0.03864274872152855</v>
+        <v>0.03854202437259159</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>0.6138517469073569</v>
+        <v>0.6138437448935737</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>3.491670133792448</v>
+        <v>3.491624617276974</v>
       </c>
     </row>
     <row r="83">
@@ -7314,13 +7314,13 @@
         <v>1.308459526385786</v>
       </c>
       <c r="K83" t="n">
-        <v>1.758118475380813</v>
+        <v>1.758133147984172</v>
       </c>
       <c r="L83" t="n">
-        <v>0.07100971697221414</v>
+        <v>0.07085875899002581</v>
       </c>
       <c r="M83" t="n">
-        <v>0.04420345784697243</v>
+        <v>0.04412823448262317</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="U83" t="n">
-        <v>0.4866303054277152</v>
+        <v>0.4865441056975822</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>4.693450251498335</v>
+        <v>4.692618872645519</v>
       </c>
     </row>
     <row r="84">
@@ -7397,13 +7397,13 @@
         <v>0.1292865975342495</v>
       </c>
       <c r="K84" t="n">
-        <v>1.821019693986739</v>
+        <v>1.820889794323622</v>
       </c>
       <c r="L84" t="n">
-        <v>0.1005212429190608</v>
+        <v>0.1003469849459221</v>
       </c>
       <c r="M84" t="n">
-        <v>0.03148470105517165</v>
+        <v>0.03154946154140034</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="U84" t="n">
-        <v>0.4519532471052569</v>
+        <v>0.4518614856795659</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.810376807389153</v>
+        <v>5.809197109128187</v>
       </c>
     </row>
     <row r="85">
@@ -7480,13 +7480,13 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1.970471156555899</v>
+        <v>1.970195474239109</v>
       </c>
       <c r="L85" t="n">
-        <v>0.1160498385995481</v>
+        <v>0.1161753843314863</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.0130205440157867</v>
+        <v>-0.0126426528002398</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>0.3986225228757163</v>
+        <v>0.398694486239512</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>8.122841800740616</v>
+        <v>8.124308218180715</v>
       </c>
     </row>
     <row r="86">
@@ -7563,13 +7563,13 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>2.0652286156912</v>
+        <v>2.065192094737068</v>
       </c>
       <c r="L86" t="n">
-        <v>0.09106415160851666</v>
+        <v>0.09158130015979138</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.05271576770692579</v>
+        <v>-0.0522695559692183</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="U86" t="n">
-        <v>0.2898669904112506</v>
+        <v>0.2901181820107435</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.724798552309098</v>
+        <v>7.731492672606693</v>
       </c>
     </row>
     <row r="87">
@@ -7646,13 +7646,13 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>2.100704797672048</v>
+        <v>2.100956921210598</v>
       </c>
       <c r="L87" t="n">
-        <v>0.06181795091420161</v>
+        <v>0.06253013281758912</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.06265098786192866</v>
+        <v>-0.06236056537679935</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="U87" t="n">
-        <v>0.1984817328435625</v>
+        <v>0.198817181226913</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>5.827313622048893</v>
+        <v>5.837162200584498</v>
       </c>
     </row>
     <row r="88">
@@ -7729,13 +7729,13 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>2.117754022569127</v>
+        <v>2.119179048041742</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.0100179557286697</v>
+        <v>-0.009456372285179038</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.03346831723782027</v>
+        <v>-0.03398973697388988</v>
       </c>
       <c r="N88" t="n">
         <v>0.04237394890341881</v>
@@ -7761,19 +7761,19 @@
         </is>
       </c>
       <c r="U88" t="n">
-        <v>0.02234185349890289</v>
+        <v>0.02261003493142559</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001199902254549623</v>
+        <v>0.001200259006210183</v>
       </c>
       <c r="W88" t="n">
         <v>0.001170181728185258</v>
       </c>
       <c r="X88" t="n">
-        <v>0.03822148098967892</v>
+        <v>0.03823284489599749</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.7116735763639597</v>
+        <v>0.720216181802099</v>
       </c>
     </row>
     <row r="89">
@@ -7812,13 +7812,13 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>2.087215716866762</v>
+        <v>2.088927690428526</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.02582351642175973</v>
+        <v>-0.02615655681116524</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.003182449610328446</v>
+        <v>-0.003872547638034603</v>
       </c>
       <c r="N89" t="n">
         <v>0.08735887304521579</v>
@@ -7844,19 +7844,19 @@
         </is>
       </c>
       <c r="U89" t="n">
-        <v>-0.004140233686431001</v>
+        <v>-0.004289525333668436</v>
       </c>
       <c r="V89" t="n">
-        <v>0.001356498243043499</v>
+        <v>0.001356088509913993</v>
       </c>
       <c r="W89" t="n">
         <v>0.001367861175509034</v>
       </c>
       <c r="X89" t="n">
-        <v>0.0431778176211845</v>
+        <v>0.04316477567112677</v>
       </c>
       <c r="Y89" t="n">
-        <v>-0.1317850988297001</v>
+        <v>-0.1365371046283376</v>
       </c>
     </row>
     <row r="90">
@@ -7895,13 +7895,13 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>2.066827954913856</v>
+        <v>2.067795170069929</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.0198134799459786</v>
+        <v>-0.02063577719138032</v>
       </c>
       <c r="M90" t="n">
-        <v>0.006538852478252349</v>
+        <v>0.006350757477629117</v>
       </c>
       <c r="N90" t="n">
         <v>0.1275061606761601</v>
@@ -7927,19 +7927,19 @@
         </is>
       </c>
       <c r="U90" t="n">
-        <v>0.007945309412866825</v>
+        <v>0.007552124862059606</v>
       </c>
       <c r="V90" t="n">
-        <v>0.001403936309238141</v>
+        <v>0.00140238289834316</v>
       </c>
       <c r="W90" t="n">
         <v>0.001372545629770688</v>
       </c>
       <c r="X90" t="n">
-        <v>0.04530943777625759</v>
+        <v>0.04525930432374699</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.2564201097204752</v>
+        <v>0.243730808345363</v>
       </c>
     </row>
     <row r="91">
@@ -7978,13 +7978,13 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>2.051773362756858</v>
+        <v>2.05200661583767</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.01407157940694259</v>
+        <v>-0.01471834531695149</v>
       </c>
       <c r="M91" t="n">
-        <v>0.005656133668469661</v>
+        <v>0.00589501481217024</v>
       </c>
       <c r="N91" t="n">
         <v>0.1711895453687214</v>
@@ -8010,19 +8010,19 @@
         </is>
       </c>
       <c r="U91" t="n">
-        <v>0.01182665729059543</v>
+        <v>0.01151224982399719</v>
       </c>
       <c r="V91" t="n">
-        <v>0.001445284641078882</v>
+        <v>0.001443646344088566</v>
       </c>
       <c r="W91" t="n">
         <v>0.001383658951160251</v>
       </c>
       <c r="X91" t="n">
-        <v>0.04748220118532685</v>
+        <v>0.04742837791405936</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.3885433393956031</v>
+        <v>0.3782140532751594</v>
       </c>
     </row>
     <row r="92">
@@ -8061,13 +8061,13 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>2.038192318106796</v>
+        <v>2.037879477419884</v>
       </c>
       <c r="L92" t="n">
-        <v>-0.008037363165663169</v>
+        <v>-0.008304745121873958</v>
       </c>
       <c r="M92" t="n">
-        <v>0.004520981411469255</v>
+        <v>0.004791853458431045</v>
       </c>
       <c r="N92" t="n">
         <v>0.233717249579028</v>
@@ -8093,19 +8093,19 @@
         </is>
       </c>
       <c r="U92" t="n">
-        <v>0.01282681721411007</v>
+        <v>0.01269500588359046</v>
       </c>
       <c r="V92" t="n">
-        <v>0.001496452948857194</v>
+        <v>0.001495535766120965</v>
       </c>
       <c r="W92" t="n">
-        <v>0.001407200111008052</v>
+        <v>0.001407200111008051</v>
       </c>
       <c r="X92" t="n">
-        <v>0.05026326609411727</v>
+        <v>0.05023245951248487</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.4308306033048176</v>
+        <v>0.4264032887105389</v>
       </c>
     </row>
     <row r="93">
@@ -8144,13 +8144,13 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>2.031137146384127</v>
+        <v>2.030740878677251</v>
       </c>
       <c r="L93" t="n">
-        <v>-0.001493627936065167</v>
+        <v>-0.001397580689606936</v>
       </c>
       <c r="M93" t="n">
-        <v>0.003677054428447219</v>
+        <v>0.003858036097509609</v>
       </c>
       <c r="N93" t="n">
         <v>0.3170919465744321</v>
@@ -8176,19 +8176,19 @@
         </is>
       </c>
       <c r="U93" t="n">
-        <v>0.01384828246872307</v>
+        <v>0.013895435626426</v>
       </c>
       <c r="V93" t="n">
-        <v>0.001555765062151862</v>
+        <v>0.001556199325996475</v>
       </c>
       <c r="W93" t="n">
-        <v>0.001428227296302813</v>
+        <v>0.001428227296302814</v>
       </c>
       <c r="X93" t="n">
-        <v>0.0535656445194559</v>
+        <v>0.05358059640601906</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.4768021817501293</v>
+        <v>0.4784256847744172</v>
       </c>
     </row>
     <row r="94">
@@ -8227,13 +8227,13 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>2.035633519970628</v>
+        <v>2.035805105904229</v>
       </c>
       <c r="L94" t="n">
-        <v>0.004708907919431515</v>
+        <v>0.00504425939445094</v>
       </c>
       <c r="M94" t="n">
-        <v>0.00269458281162871</v>
+        <v>0.00277091710397757</v>
       </c>
       <c r="N94" t="n">
         <v>0.4275724209378097</v>
@@ -8259,19 +8259,19 @@
         </is>
       </c>
       <c r="U94" t="n">
-        <v>0.01448290988117382</v>
+        <v>0.01464744162082032</v>
       </c>
       <c r="V94" t="n">
-        <v>0.001611576392596405</v>
+        <v>0.001613565936864088</v>
       </c>
       <c r="W94" t="n">
         <v>0.001436446716125748</v>
       </c>
       <c r="X94" t="n">
-        <v>0.05698448985673704</v>
+        <v>0.0570548390909788</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.5121080421699066</v>
+        <v>0.5179257975627443</v>
       </c>
     </row>
     <row r="95">
@@ -8310,13 +8310,13 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>2.079142224861755</v>
+        <v>2.081249820890327</v>
       </c>
       <c r="L95" t="n">
-        <v>0.01256711206847716</v>
+        <v>0.01282653925998256</v>
       </c>
       <c r="M95" t="n">
-        <v>0.000849240225396646</v>
+        <v>0.000729018955751449</v>
       </c>
       <c r="N95" t="n">
         <v>0.6773094646637046</v>
@@ -8342,19 +8342,19 @@
         </is>
       </c>
       <c r="U95" t="n">
-        <v>0.01388829799400032</v>
+        <v>0.01400682681814485</v>
       </c>
       <c r="V95" t="n">
-        <v>0.001676268716009134</v>
+        <v>0.001678444171120302</v>
       </c>
       <c r="W95" t="n">
         <v>0.001421365581058319</v>
       </c>
       <c r="X95" t="n">
-        <v>0.06185924769452287</v>
+        <v>0.06193952838895142</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.5125190594212161</v>
+        <v>0.5168931217786843</v>
       </c>
     </row>
     <row r="96">
@@ -8393,13 +8393,13 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>2.101707053763695</v>
+        <v>2.104126935900627</v>
       </c>
       <c r="L96" t="n">
-        <v>0.01336444096894196</v>
+        <v>0.01335766586415282</v>
       </c>
       <c r="M96" t="n">
-        <v>3.949545837342826e-05</v>
+        <v>-0.0001620711106730724</v>
       </c>
       <c r="N96" t="n">
         <v>0.7736707373393487</v>
@@ -8425,19 +8425,19 @@
         </is>
       </c>
       <c r="U96" t="n">
-        <v>0.01281705022982444</v>
+        <v>0.01280651722767065</v>
       </c>
       <c r="V96" t="n">
-        <v>0.001664957030669107</v>
+        <v>0.001664738806095621</v>
       </c>
       <c r="W96" t="n">
         <v>0.001399411151259112</v>
       </c>
       <c r="X96" t="n">
-        <v>0.06217384413473686</v>
+        <v>0.06216569505919414</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.4786221317290983</v>
+        <v>0.4782288019181078</v>
       </c>
     </row>
     <row r="97">
@@ -8476,13 +8476,13 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>2.134463944790217</v>
+        <v>2.136138838778407</v>
       </c>
       <c r="L97" t="n">
-        <v>0.01181729755773009</v>
+        <v>0.01114968656306303</v>
       </c>
       <c r="M97" t="n">
-        <v>-0.0008948971162764828</v>
+        <v>-0.001120220367477728</v>
       </c>
       <c r="N97" t="n">
         <v>0.9146965461484002</v>
@@ -8508,19 +8508,19 @@
         </is>
       </c>
       <c r="U97" t="n">
-        <v>0.0101949418713682</v>
+        <v>0.009878069247843929</v>
       </c>
       <c r="V97" t="n">
-        <v>0.001584720709046247</v>
+        <v>0.001577065205328077</v>
       </c>
       <c r="W97" t="n">
         <v>0.001338415381262659</v>
       </c>
       <c r="X97" t="n">
-        <v>0.05999854523680726</v>
+        <v>0.05970870294250062</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.3859870559930031</v>
+        <v>0.3739900546739069</v>
       </c>
     </row>
     <row r="98">
@@ -8559,13 +8559,13 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>2.152731153105458</v>
+        <v>2.152882677952347</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0100190915286118</v>
+        <v>0.009019287453887026</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.001062381479664619</v>
+        <v>-0.001172038739690828</v>
       </c>
       <c r="N98" t="n">
         <v>1.004613956853115</v>
@@ -8591,19 +8591,19 @@
         </is>
       </c>
       <c r="U98" t="n">
-        <v>0.008267985217046022</v>
+        <v>0.007803255159356828</v>
       </c>
       <c r="V98" t="n">
-        <v>0.001498781179389131</v>
+        <v>0.001486533797816385</v>
       </c>
       <c r="W98" t="n">
         <v>0.00128088873168627</v>
       </c>
       <c r="X98" t="n">
-        <v>0.05713404232628472</v>
+        <v>0.056667168024161</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.3151783754959723</v>
+        <v>0.2974627094925246</v>
       </c>
     </row>
     <row r="99">
@@ -8642,13 +8642,13 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>2.176811640371411</v>
+        <v>2.173674094847271</v>
       </c>
       <c r="L99" t="n">
-        <v>0.007055161721050418</v>
+        <v>0.00618308344552404</v>
       </c>
       <c r="M99" t="n">
-        <v>-0.0009308320182838202</v>
+        <v>-0.0007271339905342432</v>
       </c>
       <c r="N99" t="n">
         <v>1.147638215923621</v>
@@ -8674,19 +8674,19 @@
         </is>
       </c>
       <c r="U99" t="n">
-        <v>0.005328867197648854</v>
+        <v>0.004932345324158175</v>
       </c>
       <c r="V99" t="n">
-        <v>0.00130425972320819</v>
+        <v>0.001292417196996624</v>
       </c>
       <c r="W99" t="n">
         <v>0.001145107722561769</v>
       </c>
       <c r="X99" t="n">
-        <v>0.05011778624923392</v>
+        <v>0.04966272259376639</v>
       </c>
       <c r="Y99" t="n">
-        <v>0.204768285342266</v>
+        <v>0.1895314439792061</v>
       </c>
     </row>
     <row r="100">
@@ -8725,13 +8725,13 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>2.193469671369374</v>
+        <v>2.188600271910131</v>
       </c>
       <c r="L100" t="n">
-        <v>0.004634171927431985</v>
+        <v>0.004837282148425159</v>
       </c>
       <c r="M100" t="n">
-        <v>-0.000716498340384688</v>
+        <v>-0.0001819506659246502</v>
       </c>
       <c r="N100" t="n">
         <v>1.273252413771963</v>
@@ -8757,19 +8757,19 @@
         </is>
       </c>
       <c r="U100" t="n">
-        <v>0.002930938446158824</v>
+        <v>0.003028442712860842</v>
       </c>
       <c r="V100" t="n">
-        <v>0.00105786953175706</v>
+        <v>0.001061087283189659</v>
       </c>
       <c r="W100" t="n">
-        <v>0.0009611452374981006</v>
+        <v>0.0009611452374981003</v>
       </c>
       <c r="X100" t="n">
-        <v>0.04081480681791529</v>
+        <v>0.0409389543608467</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.1130817013667857</v>
+        <v>0.116843618777107</v>
       </c>
     </row>
     <row r="101">
@@ -8808,13 +8808,13 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>2.204249697598105</v>
+        <v>2.202485451218219</v>
       </c>
       <c r="L101" t="n">
-        <v>0.002802193816956455</v>
+        <v>0.005153757308895945</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.0004546411618555052</v>
+        <v>0.0004841143620388914</v>
       </c>
       <c r="N101" t="n">
         <v>1.374160465684623</v>
@@ -8840,19 +8840,19 @@
         </is>
       </c>
       <c r="U101" t="n">
-        <v>0.001076057011114318</v>
+        <v>0.002144761606631627</v>
       </c>
       <c r="V101" t="n">
-        <v>0.0007521797408048471</v>
+        <v>0.0007902155798456332</v>
       </c>
       <c r="W101" t="n">
         <v>0.0007138822248728211</v>
       </c>
       <c r="X101" t="n">
-        <v>0.0290418152142911</v>
+        <v>0.03051038681894646</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.04154678354323343</v>
+        <v>0.0828096888010473</v>
       </c>
     </row>
     <row r="102">
@@ -8891,13 +8891,13 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>2.209706430113592</v>
+        <v>2.216557122654333</v>
       </c>
       <c r="L102" t="n">
-        <v>0.001973230333554898</v>
+        <v>0.007146560847689637</v>
       </c>
       <c r="M102" t="n">
-        <v>-0.0002896734882714569</v>
+        <v>0.0009037293549751451</v>
       </c>
       <c r="N102" t="n">
         <v>1.430093764837538</v>
@@ -8923,19 +8923,19 @@
         </is>
       </c>
       <c r="U102" t="n">
-        <v>0.0005286169748632762</v>
+        <v>0.002859805695050554</v>
       </c>
       <c r="V102" t="n">
-        <v>0.0004497287669375862</v>
+        <v>0.0005361940506457551</v>
       </c>
       <c r="W102" t="n">
         <v>0.0004301220245453036</v>
       </c>
       <c r="X102" t="n">
-        <v>0.01734006988633109</v>
+        <v>0.02067388833973052</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.0203817410872946</v>
+        <v>0.1102647512436897</v>
       </c>
     </row>
     <row r="103">
@@ -8974,13 +8974,13 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>2.219633582472838</v>
+        <v>2.300815726331576</v>
       </c>
       <c r="L103" t="n">
-        <v>0.0007527611609747797</v>
+        <v>0.01599081315979101</v>
       </c>
       <c r="M103" t="n">
-        <v>-4.546678795191661e-05</v>
+        <v>0.001524898282215161</v>
       </c>
       <c r="N103" t="n">
         <v>1.41318925985422</v>
@@ -9006,19 +9006,19 @@
         </is>
       </c>
       <c r="U103" t="n">
-        <v>0.001083341852967938</v>
+        <v>0.007694266799697597</v>
       </c>
       <c r="V103" t="n">
-        <v>-0.0005238439765556357</v>
+        <v>-0.0002818745868992157</v>
       </c>
       <c r="W103" t="n">
         <v>-0.0005634958511517288</v>
       </c>
       <c r="X103" t="n">
-        <v>-0.02022572417593911</v>
+        <v>-0.01088323604351843</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.04182805279245808</v>
+        <v>0.2970772309915856</v>
       </c>
     </row>
     <row r="104">
@@ -9039,10 +9039,10 @@
         <v>0.2107142857143181</v>
       </c>
       <c r="E104" t="n">
-        <v>0.2996120690308404</v>
+        <v>0.3700021222441493</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1858926673667783</v>
+        <v>-0.0525717727379148</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -9057,13 +9057,13 @@
         <v>0.4697829032810299</v>
       </c>
       <c r="K104" t="n">
-        <v>1.7519190460133</v>
+        <v>1.751888953410846</v>
       </c>
       <c r="L104" t="n">
-        <v>-0.0289750664007582</v>
+        <v>-0.02894007387539932</v>
       </c>
       <c r="M104" t="n">
-        <v>4.935593215207174e-06</v>
+        <v>1.973968278289745e-06</v>
       </c>
       <c r="N104" t="n">
         <v>0</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="U104" t="n">
-        <v>1.405348741108562</v>
+        <v>1.739422921008011</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.2961270561622067</v>
+        <v>0.3665212583553157</v>
       </c>
     </row>
     <row r="105">
@@ -9119,13 +9119,13 @@
         <v>0.6500000000000004</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4460534679810709</v>
+        <v>0.4538442698855736</v>
       </c>
       <c r="E105" t="n">
-        <v>0.4245084917899373</v>
+        <v>0.378090136744329</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1984040180458277</v>
+        <v>0.07745797120000647</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -9140,13 +9140,13 @@
         <v>0.1194921971218895</v>
       </c>
       <c r="K105" t="n">
-        <v>1.733334821152476</v>
+        <v>1.733326606496472</v>
       </c>
       <c r="L105" t="n">
-        <v>-0.02820716394023881</v>
+        <v>-0.02817483970728918</v>
       </c>
       <c r="M105" t="n">
-        <v>0.00235784120838289</v>
+        <v>0.002352592702829816</v>
       </c>
       <c r="N105" t="n">
         <v>0</v>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="U105" t="n">
-        <v>0.9354253191780092</v>
+        <v>0.8168286422318699</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
@@ -9184,7 +9184,7 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0.4172497076566511</v>
+        <v>0.3707129987553474</v>
       </c>
     </row>
     <row r="106">
@@ -9202,13 +9202,13 @@
         <v>1.383333333333332</v>
       </c>
       <c r="D106" t="n">
-        <v>0.8090262496658301</v>
+        <v>0.7344561812913177</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5751804073557321</v>
+        <v>0.4886827310653197</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2529529051282783</v>
+        <v>0.2664628079616739</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -9223,13 +9223,13 @@
         <v>-0.4114184687505051</v>
       </c>
       <c r="K106" t="n">
-        <v>1.712967229810738</v>
+        <v>1.712981615785798</v>
       </c>
       <c r="L106" t="n">
-        <v>-0.0255047416543126</v>
+        <v>-0.02547721235126277</v>
       </c>
       <c r="M106" t="n">
-        <v>0.006095260736560606</v>
+        <v>0.00608637968739149</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="U106" t="n">
-        <v>0.6960647318850139</v>
+        <v>0.6504937403772176</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -9267,7 +9267,7 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0.5631346395615845</v>
+        <v>0.4777591485113571</v>
       </c>
     </row>
     <row r="107">
@@ -9285,13 +9285,13 @@
         <v>2.15</v>
       </c>
       <c r="D107" t="n">
-        <v>1.314293455599225</v>
+        <v>1.194097693161027</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8071758859880831</v>
+        <v>0.7856698981047963</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4016230163507482</v>
+        <v>0.496834753421999</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -9306,13 +9306,13 @@
         <v>-1.124912891978527</v>
       </c>
       <c r="K107" t="n">
-        <v>1.695232430025936</v>
+        <v>1.6952652850241</v>
       </c>
       <c r="L107" t="n">
-        <v>-0.01889994514647264</v>
+        <v>-0.01888110220375827</v>
       </c>
       <c r="M107" t="n">
-        <v>0.01148074251726751</v>
+        <v>0.01146662710858551</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="U107" t="n">
-        <v>0.6030030666861583</v>
+        <v>0.6468236054173178</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0.7925229842518809</v>
+        <v>0.7723705751109176</v>
       </c>
     </row>
     <row r="108">
@@ -9368,13 +9368,13 @@
         <v>2.733333333333332</v>
       </c>
       <c r="D108" t="n">
-        <v>1.850892917284805</v>
+        <v>1.735020505774627</v>
       </c>
       <c r="E108" t="n">
-        <v>1.085405169879255</v>
+        <v>1.124073044106381</v>
       </c>
       <c r="F108" t="n">
-        <v>0.5510719718023769</v>
+        <v>0.6441312772719269</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -9389,13 +9389,13 @@
         <v>-0.7666611442762989</v>
       </c>
       <c r="K108" t="n">
-        <v>1.686085973958131</v>
+        <v>1.686127491802555</v>
       </c>
       <c r="L108" t="n">
-        <v>-0.01093089120546276</v>
+        <v>-0.01092151851291823</v>
       </c>
       <c r="M108" t="n">
-        <v>0.01580601479384376</v>
+        <v>0.0157876954845624</v>
       </c>
       <c r="N108" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="U108" t="n">
-        <v>0.5799394582166518</v>
+        <v>0.6413957807344324</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.073405835667188</v>
+        <v>1.112834831891567</v>
       </c>
     </row>
     <row r="109">
@@ -9451,13 +9451,13 @@
         <v>3.633333333333332</v>
       </c>
       <c r="D109" t="n">
-        <v>3.05759443849406</v>
+        <v>3.019924879301957</v>
       </c>
       <c r="E109" t="n">
-        <v>1.684273480998688</v>
+        <v>1.792675870303298</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7681775062545757</v>
+        <v>0.8117818506878421</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -9472,13 +9472,13 @@
         <v>0.9180792406552831</v>
       </c>
       <c r="K109" t="n">
-        <v>1.682842147345238</v>
+        <v>1.682884494156072</v>
       </c>
       <c r="L109" t="n">
-        <v>0.006272701596623853</v>
+        <v>0.00626269230216836</v>
       </c>
       <c r="M109" t="n">
-        <v>0.02208936783849695</v>
+        <v>0.02206494149364947</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="U109" t="n">
-        <v>0.5545766550465557</v>
+        <v>0.5973374509353581</v>
       </c>
       <c r="V109" t="n">
         <v>0</v>
@@ -9516,7 +9516,7 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.695670496188987</v>
+        <v>1.8039142294185</v>
       </c>
     </row>
     <row r="110">
@@ -9534,13 +9534,13 @@
         <v>4.583333333333335</v>
       </c>
       <c r="D110" t="n">
-        <v>5.002102408467303</v>
+        <v>5.088985201207922</v>
       </c>
       <c r="E110" t="n">
-        <v>2.517095851039292</v>
+        <v>2.632949810652408</v>
       </c>
       <c r="F110" t="n">
-        <v>0.958819077232937</v>
+        <v>0.9315722614061488</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -9555,13 +9555,13 @@
         <v>1.234159743267291</v>
       </c>
       <c r="K110" t="n">
-        <v>1.698705603232393</v>
+        <v>1.698727480483116</v>
       </c>
       <c r="L110" t="n">
-        <v>0.03024012761472195</v>
+        <v>0.03020401445891463</v>
       </c>
       <c r="M110" t="n">
-        <v>0.02789521981099954</v>
+        <v>0.027866028912337</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="U110" t="n">
-        <v>0.5210094455092956</v>
+        <v>0.5351624688828446</v>
       </c>
       <c r="V110" t="n">
         <v>0</v>
@@ -9599,7 +9599,7 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.606142602216261</v>
+        <v>2.723433884386691</v>
       </c>
     </row>
     <row r="111">
@@ -9617,13 +9617,13 @@
         <v>5.55</v>
       </c>
       <c r="D111" t="n">
-        <v>7.897840496839257</v>
+        <v>8.081711440760806</v>
       </c>
       <c r="E111" t="n">
-        <v>3.52477286860467</v>
+        <v>3.57977224803796</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8677975346506814</v>
+        <v>0.7909872947208969</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         <v>0.3167391304347822</v>
       </c>
       <c r="K111" t="n">
-        <v>1.741257743283577</v>
+        <v>1.741230383411629</v>
       </c>
       <c r="L111" t="n">
-        <v>0.05982819754624447</v>
+        <v>0.0597621814234357</v>
       </c>
       <c r="M111" t="n">
-        <v>0.02910685395216801</v>
+        <v>0.02908819877268348</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="U111" t="n">
-        <v>0.4806549632942718</v>
+        <v>0.4772691100090605</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -9682,7 +9682,7 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>3.796136234112287</v>
+        <v>3.857151226681951</v>
       </c>
     </row>
     <row r="112">
@@ -9700,13 +9700,13 @@
         <v>6.183333333333334</v>
       </c>
       <c r="D112" t="n">
-        <v>10.34977665743332</v>
+        <v>10.54966987285555</v>
       </c>
       <c r="E112" t="n">
-        <v>4.001917818910186</v>
+        <v>4.002520760677387</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4903318506362861</v>
+        <v>0.4136965802013699</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -9721,13 +9721,13 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>1.785708654577622</v>
+        <v>1.785633226676442</v>
       </c>
       <c r="L112" t="n">
-        <v>0.07763950456045576</v>
+        <v>0.0775667685385435</v>
       </c>
       <c r="M112" t="n">
-        <v>0.02444224131585432</v>
+        <v>0.02444718499952357</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="U112" t="n">
-        <v>0.4301453300101384</v>
+        <v>0.4228370883092321</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>4.451908095842881</v>
+        <v>4.460791691661866</v>
       </c>
     </row>
     <row r="113">
@@ -9783,13 +9783,13 @@
         <v>7.449999999999998</v>
       </c>
       <c r="D113" t="n">
-        <v>15.7493197269158</v>
+        <v>15.88741503505066</v>
       </c>
       <c r="E113" t="n">
-        <v>3.956599050106016</v>
+        <v>3.883573714884891</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.5239705523481573</v>
+        <v>-0.5592765269073445</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -9804,13 +9804,13 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>1.902935126731175</v>
+        <v>1.902775574063654</v>
       </c>
       <c r="L113" t="n">
-        <v>0.09927479350385715</v>
+        <v>0.09924772307630203</v>
       </c>
       <c r="M113" t="n">
-        <v>0.009261036841796744</v>
+        <v>0.009324614170724478</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="U113" t="n">
-        <v>0.3033927889306563</v>
+        <v>0.2966028456107576</v>
       </c>
       <c r="V113" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>4.778230035709586</v>
+        <v>4.712252508795158</v>
       </c>
     </row>
     <row r="114">
@@ -9866,13 +9866,13 @@
         <v>8.350000000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>19.11445323850371</v>
+        <v>19.17132649277149</v>
       </c>
       <c r="E114" t="n">
-        <v>3.172839247189312</v>
+        <v>3.082632355513489</v>
       </c>
       <c r="F114" t="n">
-        <v>-1.004468107488447</v>
+        <v>-1.011970712396516</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -9887,13 +9887,13 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>1.996584550387085</v>
+        <v>1.996425793698932</v>
       </c>
       <c r="L114" t="n">
-        <v>0.1026093913290472</v>
+        <v>0.1026571423585004</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.001991540221225843</v>
+        <v>-0.001905002782075331</v>
       </c>
       <c r="N114" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
         </is>
       </c>
       <c r="U114" t="n">
-        <v>0.2173840897160017</v>
+        <v>0.2122143648835911</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>4.15517801767121</v>
+        <v>4.068430875639464</v>
       </c>
     </row>
     <row r="115">
@@ -9949,13 +9949,13 @@
         <v>9.350000000000001</v>
       </c>
       <c r="D115" t="n">
-        <v>21.65818361023929</v>
+        <v>21.62489423376809</v>
       </c>
       <c r="E115" t="n">
-        <v>2.019900159672592</v>
+        <v>1.935066233505289</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.9943073314490398</v>
+        <v>-0.9850469044278518</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -9970,13 +9970,13 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>2.097587804111481</v>
+        <v>2.097528872461596</v>
       </c>
       <c r="L115" t="n">
-        <v>0.09428824120128643</v>
+        <v>0.0944263102109113</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.01330592893482931</v>
+        <v>-0.0132332977871721</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="U115" t="n">
-        <v>0.1382134718180471</v>
+        <v>0.1345011526641492</v>
       </c>
       <c r="V115" t="n">
         <v>0</v>
@@ -10014,7 +10014,7 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.993452750043898</v>
+        <v>2.908573200682123</v>
       </c>
     </row>
     <row r="116">
@@ -10032,13 +10032,13 @@
         <v>10.5</v>
       </c>
       <c r="D116" t="n">
-        <v>23.28830333840948</v>
+        <v>23.16450215864191</v>
       </c>
       <c r="E116" t="n">
-        <v>1.086237225905704</v>
+        <v>1.017193958663271</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.6138141076207885</v>
+        <v>-0.5975768071318633</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -10053,13 +10053,13 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>2.197138677431148</v>
+        <v>2.197289102794452</v>
       </c>
       <c r="L116" t="n">
-        <v>0.07239405295388468</v>
+        <v>0.07259225694731497</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.02332805580968898</v>
+        <v>-0.02330210618724756</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="U116" t="n">
-        <v>0.07959227988629636</v>
+        <v>0.07694894536995561</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
@@ -10097,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.853569157387657</v>
+        <v>1.782484011127556</v>
       </c>
     </row>
     <row r="117">
@@ -10115,13 +10115,13 @@
         <v>11.91666666666667</v>
       </c>
       <c r="D117" t="n">
-        <v>24.24903785723786</v>
+        <v>24.04428833791605</v>
       </c>
       <c r="E117" t="n">
-        <v>0.5623271287404528</v>
+        <v>0.5206606084372858</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.2075108301967473</v>
+        <v>-0.1870254726406558</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -10136,13 +10136,13 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>2.274964515785845</v>
+        <v>2.275423922328484</v>
       </c>
       <c r="L117" t="n">
-        <v>0.03185984206464387</v>
+        <v>0.03204883735894115</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.02715066096464509</v>
+        <v>-0.02724973852055389</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -10151,7 +10151,7 @@
         <v>0.04331870889820037</v>
       </c>
       <c r="P117" t="n">
-        <v>0.03417475714223775</v>
+        <v>0.02555529823895503</v>
       </c>
       <c r="Q117" t="n">
         <v>36.96</v>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="U117" t="n">
-        <v>0.03719421226749242</v>
+        <v>0.03573900892330918</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -10180,7 +10180,7 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0.9019238613445647</v>
+        <v>0.8593190354634006</v>
       </c>
     </row>
     <row r="118">
@@ -10198,13 +10198,13 @@
         <v>12.81666666666666</v>
       </c>
       <c r="D118" t="n">
-        <v>24.68889995641544</v>
+        <v>24.45549776089937</v>
       </c>
       <c r="E118" t="n">
-        <v>0.4683694028493468</v>
+        <v>0.445803291611619</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.08062752562744983</v>
+        <v>-0.06034668239199277</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -10219,22 +10219,22 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>2.290444306229041</v>
+        <v>2.291057164999081</v>
       </c>
       <c r="L118" t="n">
-        <v>0.008260008927685192</v>
+        <v>0.008306901990275284</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.0205553572250682</v>
+        <v>-0.02078706591921876</v>
       </c>
       <c r="N118" t="n">
-        <v>0.07228700779647691</v>
+        <v>0.07790473552950697</v>
       </c>
       <c r="O118" t="n">
-        <v>0.07613253933762341</v>
+        <v>0.0634467239399686</v>
       </c>
       <c r="P118" t="n">
-        <v>0.01846914457861556</v>
+        <v>0.01087678132715291</v>
       </c>
       <c r="Q118" t="n">
         <v>31.995</v>
@@ -10251,19 +10251,19 @@
         </is>
       </c>
       <c r="U118" t="n">
-        <v>0.02257714050178286</v>
+        <v>0.02185495879141676</v>
       </c>
       <c r="V118" t="n">
-        <v>0.003094233743329843</v>
+        <v>0.00260592489706846</v>
       </c>
       <c r="W118" t="n">
-        <v>0.00302812978833972</v>
+        <v>0.002536304364241857</v>
       </c>
       <c r="X118" t="n">
-        <v>0.07639322733083535</v>
+        <v>0.06372919048532963</v>
       </c>
       <c r="Y118" t="n">
-        <v>0.5574047631504522</v>
+        <v>0.5344738957880404</v>
       </c>
     </row>
     <row r="119">
@@ -10281,13 +10281,13 @@
         <v>14.25</v>
       </c>
       <c r="D119" t="n">
-        <v>25.31373903863702</v>
+        <v>25.06915330805948</v>
       </c>
       <c r="E119" t="n">
-        <v>0.4070633236283516</v>
+        <v>0.4114164825728679</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.03999284415639892</v>
+        <v>-0.02324528555518547</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -10302,22 +10302,22 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>2.281876722766255</v>
+        <v>2.282274629736696</v>
       </c>
       <c r="L119" t="n">
-        <v>-0.00826724930615963</v>
+        <v>-0.008720976032358663</v>
       </c>
       <c r="M119" t="n">
-        <v>-0.006194760464289825</v>
+        <v>-0.006476713703435878</v>
       </c>
       <c r="N119" t="n">
-        <v>0.1718540470967996</v>
+        <v>0.1609355713051363</v>
       </c>
       <c r="O119" t="n">
-        <v>0.06153739555295379</v>
+        <v>0.05281366605660436</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.01022264989225095</v>
+        <v>-0.00710389630350909</v>
       </c>
       <c r="Q119" t="n">
         <v>32.01</v>
@@ -10334,19 +10334,19 @@
         </is>
       </c>
       <c r="U119" t="n">
-        <v>0.01245772251766014</v>
+        <v>0.01259008626540013</v>
       </c>
       <c r="V119" t="n">
-        <v>0.002406391544874938</v>
+        <v>0.002082188499211797</v>
       </c>
       <c r="W119" t="n">
-        <v>0.002321816523026087</v>
+        <v>0.002001364360438363</v>
       </c>
       <c r="X119" t="n">
-        <v>0.06091476759174676</v>
+        <v>0.05219870270301883</v>
       </c>
       <c r="Y119" t="n">
-        <v>0.315351536827801</v>
+        <v>0.3156228027490097</v>
       </c>
     </row>
     <row r="120">
@@ -10364,13 +10364,13 @@
         <v>15.75</v>
       </c>
       <c r="D120" t="n">
-        <v>25.87901339418912</v>
+        <v>25.66003890680712</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3514361884151525</v>
+        <v>0.3777188338396273</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.03353544752169235</v>
+        <v>-0.02151288469179706</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -10385,22 +10385,22 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>2.265881292506861</v>
+        <v>2.26512177627356</v>
       </c>
       <c r="L120" t="n">
-        <v>-0.009183291746274969</v>
+        <v>-0.009954277268090561</v>
       </c>
       <c r="M120" t="n">
-        <v>0.0007310512656245724</v>
+        <v>0.0006985879566776481</v>
       </c>
       <c r="N120" t="n">
-        <v>0.2517150544388291</v>
+        <v>0.2321269861735177</v>
       </c>
       <c r="O120" t="n">
-        <v>0.04614064345751816</v>
+        <v>0.04265153885005755</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.009379685711600999</v>
+        <v>-0.00637303148429085</v>
       </c>
       <c r="Q120" t="n">
         <v>32.01</v>
@@ -10417,19 +10417,19 @@
         </is>
       </c>
       <c r="U120" t="n">
-        <v>0.00952711205653349</v>
+        <v>0.01032553116695748</v>
       </c>
       <c r="V120" t="n">
-        <v>0.001743516175570568</v>
+        <v>0.001622422962937229</v>
       </c>
       <c r="W120" t="n">
-        <v>0.001650849678072112</v>
+        <v>0.001529015683270528</v>
       </c>
       <c r="X120" t="n">
-        <v>0.04512047846057613</v>
+        <v>0.04163143635226656</v>
       </c>
       <c r="Y120" t="n">
-        <v>0.2465522605189709</v>
+        <v>0.2649535314775784</v>
       </c>
     </row>
     <row r="121">
@@ -10447,13 +10447,13 @@
         <v>17.75</v>
       </c>
       <c r="D121" t="n">
-        <v>26.51411675247832</v>
+        <v>26.37226351139624</v>
       </c>
       <c r="E121" t="n">
-        <v>0.2938301181373864</v>
+        <v>0.3372323030258908</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.02555954101228416</v>
+        <v>-0.0193730955314233</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -10468,22 +10468,22 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>2.25146225148539</v>
+        <v>2.249162444068046</v>
       </c>
       <c r="L121" t="n">
-        <v>-0.00414319927982193</v>
+        <v>-0.004501664606738176</v>
       </c>
       <c r="M121" t="n">
-        <v>0.002513933584402321</v>
+        <v>0.002741568290999149</v>
       </c>
       <c r="N121" t="n">
-        <v>0.3250629330769729</v>
+        <v>0.304604985485553</v>
       </c>
       <c r="O121" t="n">
-        <v>0.02974078052859898</v>
+        <v>0.03097672917945008</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.007391353161914887</v>
+        <v>-0.005470297797812553</v>
       </c>
       <c r="Q121" t="n">
         <v>31.98</v>
@@ -10500,19 +10500,19 @@
         </is>
       </c>
       <c r="U121" t="n">
-        <v>0.009241799548130016</v>
+        <v>0.01078590074156519</v>
       </c>
       <c r="V121" t="n">
-        <v>0.001099134908134269</v>
+        <v>0.001151477456453691</v>
       </c>
       <c r="W121" t="n">
-        <v>0.000985830493883179</v>
+        <v>0.001026898118111597</v>
       </c>
       <c r="X121" t="n">
-        <v>0.02914259128099655</v>
+        <v>0.03036706690902902</v>
       </c>
       <c r="Y121" t="n">
-        <v>0.2450381522221206</v>
+        <v>0.2844486165643213</v>
       </c>
     </row>
     <row r="122">
@@ -10530,13 +10530,13 @@
         <v>22.08333333333333</v>
       </c>
       <c r="D122" t="n">
-        <v>27.56466149717262</v>
+        <v>27.65634127581926</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2135249130505557</v>
+        <v>0.2614521506647343</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.01080164273625846</v>
+        <v>-0.01541382259815037</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -10551,22 +10551,22 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>2.262297737274182</v>
+        <v>2.262309800373687</v>
       </c>
       <c r="L122" t="n">
-        <v>0.006693121938627589</v>
+        <v>0.007521757503957005</v>
       </c>
       <c r="M122" t="n">
-        <v>0.001532681339414351</v>
+        <v>0.001562657183201134</v>
       </c>
       <c r="N122" t="n">
-        <v>0.3888449911681286</v>
+        <v>0.3894306057887302</v>
       </c>
       <c r="O122" t="n">
-        <v>0.005303235334193024</v>
+        <v>0.0107188325742629</v>
       </c>
       <c r="P122" t="n">
-        <v>-0.003712321885336485</v>
+        <v>-0.003799960777227666</v>
       </c>
       <c r="Q122" t="n">
         <v>31.995</v>
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="U122" t="n">
-        <v>0.01070487856881287</v>
+        <v>0.01277841909339471</v>
       </c>
       <c r="V122" t="n">
-        <v>0.0002341277744280816</v>
+        <v>0.0004343892229278844</v>
       </c>
       <c r="W122" t="n">
-        <v>8.311781506497117e-05</v>
+        <v>0.0002544555347030464</v>
       </c>
       <c r="X122" t="n">
-        <v>0.006453652849196456</v>
+        <v>0.0120136165958315</v>
       </c>
       <c r="Y122" t="n">
-        <v>0.2950763541176645</v>
+        <v>0.3534043194123691</v>
       </c>
     </row>
     <row r="123">
@@ -10613,13 +10613,13 @@
         <v>23.75</v>
       </c>
       <c r="D123" t="n">
-        <v>27.90200526919842</v>
+        <v>28.06974006072264</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2004775134057626</v>
+        <v>0.2370918725330791</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.004341779320751256</v>
+        <v>-0.01361837208848466</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -10634,22 +10634,22 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>2.276140520773264</v>
+        <v>2.277722827112753</v>
       </c>
       <c r="L123" t="n">
-        <v>0.008627072778333855</v>
+        <v>0.009349276726921874</v>
       </c>
       <c r="M123" t="n">
-        <v>0.0006643646156860147</v>
+        <v>0.0004784216143222239</v>
       </c>
       <c r="N123" t="n">
-        <v>0.3916480108607699</v>
+        <v>0.4016182045838965</v>
       </c>
       <c r="O123" t="n">
-        <v>0.0003513601541866307</v>
+        <v>0.004946422586161653</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.002089204690189239</v>
+        <v>-0.003042496589870878</v>
       </c>
       <c r="Q123" t="n">
         <v>31.98</v>
@@ -10666,19 +10666,19 @@
         </is>
       </c>
       <c r="U123" t="n">
-        <v>0.0109752773023198</v>
+        <v>0.01255118850536495</v>
       </c>
       <c r="V123" t="n">
-        <v>6.579427414616336e-05</v>
+        <v>0.000234947974791381</v>
       </c>
       <c r="W123" t="n">
-        <v>-8.826080120155897e-05</v>
+        <v>5.536719556029123e-05</v>
       </c>
       <c r="X123" t="n">
-        <v>0.001835792183909335</v>
+        <v>0.00659492858018728</v>
       </c>
       <c r="Y123" t="n">
-        <v>0.3062322451202408</v>
+        <v>0.3523085987987239</v>
       </c>
     </row>
     <row r="124">
@@ -10696,13 +10696,13 @@
         <v>26.25</v>
       </c>
       <c r="D124" t="n">
-        <v>28.39596624092639</v>
+        <v>28.62141699802177</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2026980418518516</v>
+        <v>0.2067876727762741</v>
       </c>
       <c r="F124" t="n">
-        <v>0.002663315221819396</v>
+        <v>-0.0107868393137892</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -10717,22 +10717,22 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>2.298913462764915</v>
+        <v>2.301476496493114</v>
       </c>
       <c r="L124" t="n">
-        <v>0.008427962237032349</v>
+        <v>0.008227493564764821</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.0004135900704281699</v>
+        <v>-0.0007861243739321921</v>
       </c>
       <c r="N124" t="n">
-        <v>0.3875372175159932</v>
+        <v>0.4051112484582827</v>
       </c>
       <c r="O124" t="n">
-        <v>-0.001564450004481743</v>
+        <v>-0.001081258627303544</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.00014870938964822</v>
+        <v>-0.001847930289874596</v>
       </c>
       <c r="Q124" t="n">
         <v>31.98</v>
@@ -10749,19 +10749,19 @@
         </is>
       </c>
       <c r="U124" t="n">
-        <v>0.01080433215319584</v>
+        <v>0.01079980405549942</v>
       </c>
       <c r="V124" t="n">
-        <v>-5.061072381350162e-06</v>
+        <v>1.282130564689127e-05</v>
       </c>
       <c r="W124" t="n">
-        <v>-0.000152514438970206</v>
+        <v>-0.0001400405217158347</v>
       </c>
       <c r="X124" t="n">
-        <v>-0.0001437140404837041</v>
+        <v>0.0003669639353787663</v>
       </c>
       <c r="Y124" t="n">
-        <v>0.3067994510779046</v>
+        <v>0.3091056953693756</v>
       </c>
     </row>
     <row r="125">
@@ -10779,13 +10779,13 @@
         <v>27.91666666666666</v>
       </c>
       <c r="D125" t="n">
-        <v>28.73947814752466</v>
+        <v>28.95063745026737</v>
       </c>
       <c r="E125" t="n">
-        <v>0.2091092381586437</v>
+        <v>0.1902927634632174</v>
       </c>
       <c r="F125" t="n">
-        <v>0.00312787002091983</v>
+        <v>-0.008955076321904357</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
@@ -10800,22 +10800,22 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>2.312203161427049</v>
+        <v>2.313773458892856</v>
       </c>
       <c r="L125" t="n">
-        <v>0.007367594504199215</v>
+        <v>0.006542385042578536</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.0006469654449942448</v>
+        <v>-0.0009151848816731751</v>
       </c>
       <c r="N125" t="n">
-        <v>0.3850185423234447</v>
+        <v>0.4005552883271568</v>
       </c>
       <c r="O125" t="n">
-        <v>-0.001126060460763079</v>
+        <v>-0.003535428893192888</v>
       </c>
       <c r="P125" t="n">
-        <v>0.0003152317813900813</v>
+        <v>-0.001075146602099324</v>
       </c>
       <c r="Q125" t="n">
         <v>32.01</v>
@@ -10832,19 +10832,19 @@
         </is>
       </c>
       <c r="U125" t="n">
-        <v>0.01046242349453234</v>
+        <v>0.009400590091008743</v>
       </c>
       <c r="V125" t="n">
-        <v>3.506014103856397e-06</v>
+        <v>-8.299733729467654e-05</v>
       </c>
       <c r="W125" t="n">
-        <v>-0.000136657527570694</v>
+        <v>-0.0002130620407340354</v>
       </c>
       <c r="X125" t="n">
-        <v>0.0001007610157226942</v>
+        <v>-0.002402825821355735</v>
       </c>
       <c r="Y125" t="n">
-        <v>0.3006845913912608</v>
+        <v>0.27215307554337</v>
       </c>
     </row>
     <row r="126">
@@ -10862,13 +10862,13 @@
         <v>30.7</v>
       </c>
       <c r="D126" t="n">
-        <v>29.3354530945887</v>
+        <v>29.44663520267652</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2144738188390969</v>
+        <v>0.1697457663601689</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0001867597164298407</v>
+        <v>-0.006025849868610385</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -10883,22 +10883,22 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>2.32989179938618</v>
+        <v>2.328098194900139</v>
       </c>
       <c r="L126" t="n">
-        <v>0.005516930369822814</v>
+        <v>0.004440787751949671</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.0005999021027103894</v>
+        <v>-0.0004974838167732701</v>
       </c>
       <c r="N126" t="n">
-        <v>0.3836745572537825</v>
+        <v>0.3869878657170909</v>
       </c>
       <c r="O126" t="n">
-        <v>-6.040075839673642e-06</v>
+        <v>-0.004680945412155212</v>
       </c>
       <c r="P126" t="n">
-        <v>0.0003402937690272116</v>
+        <v>0.0001606346812521692</v>
       </c>
       <c r="Q126" t="n">
         <v>31.995</v>
@@ -10915,19 +10915,19 @@
         </is>
       </c>
       <c r="U126" t="n">
-        <v>0.009678970363111127</v>
+        <v>0.007671996076401387</v>
       </c>
       <c r="V126" t="n">
-        <v>3.076344320953171e-05</v>
+        <v>-0.0001338956363148501</v>
       </c>
       <c r="W126" t="n">
-        <v>-9.582654525136444e-05</v>
+        <v>-0.0002347210571808174</v>
       </c>
       <c r="X126" t="n">
-        <v>0.0009024595453012609</v>
+        <v>-0.003942775957793638</v>
       </c>
       <c r="Y126" t="n">
-        <v>0.2839369810909607</v>
+        <v>0.2259144697381572</v>
       </c>
     </row>
     <row r="127">
@@ -10945,13 +10945,13 @@
         <v>33.75</v>
       </c>
       <c r="D127" t="n">
-        <v>29.99077163834306</v>
+        <v>29.93609460971918</v>
       </c>
       <c r="E127" t="n">
-        <v>0.2092258601148522</v>
+        <v>0.1558999872100433</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.003687345484199168</v>
+        <v>-0.003007141875694268</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -10966,22 +10966,22 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>2.343916761655924</v>
+        <v>2.339283581624709</v>
       </c>
       <c r="L127" t="n">
-        <v>0.003904496922610412</v>
+        <v>0.003784353600139179</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.0004552165880612599</v>
+        <v>7.581067507196008e-05</v>
       </c>
       <c r="N127" t="n">
-        <v>0.3852497996998289</v>
+        <v>0.3733579605501811</v>
       </c>
       <c r="O127" t="n">
-        <v>0.0008242750400914711</v>
+        <v>-0.002278602233229593</v>
       </c>
       <c r="P127" t="n">
-        <v>0.0002020591873632122</v>
+        <v>0.001434166412932715</v>
       </c>
       <c r="Q127" t="n">
         <v>31.98</v>
@@ -10998,19 +10998,19 @@
         </is>
       </c>
       <c r="U127" t="n">
-        <v>0.008642141506427718</v>
+        <v>0.006825500122633723</v>
       </c>
       <c r="V127" t="n">
-        <v>4.888251081829854e-05</v>
+        <v>-5.593935988448026e-05</v>
       </c>
       <c r="W127" t="n">
-        <v>-6.213108111183558e-05</v>
+        <v>-0.0001410658547978875</v>
       </c>
       <c r="X127" t="n">
-        <v>0.001466024219060425</v>
+        <v>-0.001674605969908931</v>
       </c>
       <c r="Y127" t="n">
-        <v>0.2591844923855197</v>
+        <v>0.204328817429813</v>
       </c>
     </row>
     <row r="128">
@@ -11028,13 +11028,13 @@
         <v>36.75</v>
       </c>
       <c r="D128" t="n">
-        <v>30.6018281992158</v>
+        <v>30.390284223113</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1923604369357763</v>
+        <v>0.151400568340641</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.008239993382676031</v>
+        <v>0.0005402875017627914</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -11049,22 +11049,22 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>2.353582822173603</v>
+        <v>2.350981928724797</v>
       </c>
       <c r="L128" t="n">
-        <v>0.002755585205470978</v>
+        <v>0.004870577390689079</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.0002851896605268836</v>
+        <v>0.0007495166867425111</v>
       </c>
       <c r="N128" t="n">
-        <v>0.3886308933324487</v>
+        <v>0.3729850955543391</v>
       </c>
       <c r="O128" t="n">
-        <v>0.00122337801467666</v>
+        <v>0.003931640023539254</v>
       </c>
       <c r="P128" t="n">
-        <v>3.961306235677705e-05</v>
+        <v>0.002930754982840081</v>
       </c>
       <c r="Q128" t="n">
         <v>32.01</v>
@@ -11081,19 +11081,19 @@
         </is>
       </c>
       <c r="U128" t="n">
-        <v>0.007456717671039857</v>
+        <v>0.007053594521764335</v>
       </c>
       <c r="V128" t="n">
-        <v>5.484603001815776e-05</v>
+        <v>0.0001547981863926214</v>
       </c>
       <c r="W128" t="n">
-        <v>-3.985128123262358e-05</v>
+        <v>6.82282284617594e-05</v>
       </c>
       <c r="X128" t="n">
-        <v>0.001678388788024696</v>
+        <v>0.004704360881694189</v>
       </c>
       <c r="Y128" t="n">
-        <v>0.2281891930992183</v>
+        <v>0.214360742311011</v>
       </c>
     </row>
     <row r="129">
@@ -11111,13 +11111,13 @@
         <v>39.33333333333334</v>
       </c>
       <c r="D129" t="n">
-        <v>31.07356626059552</v>
+        <v>30.78141132408451</v>
       </c>
       <c r="E129" t="n">
-        <v>0.165249536401546</v>
+        <v>0.1573345752518907</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.01124150682098886</v>
+        <v>0.002879070817613808</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -11132,22 +11132,22 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>2.359663815428079</v>
+        <v>2.365724564649334</v>
       </c>
       <c r="L129" t="n">
-        <v>0.002236362509041953</v>
+        <v>0.007668708110113567</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.0001730926744980744</v>
+        <v>0.001193684057598926</v>
       </c>
       <c r="N129" t="n">
-        <v>0.3920056135704909</v>
+        <v>0.3921643951281641</v>
       </c>
       <c r="O129" t="n">
-        <v>0.001117892700609307</v>
+        <v>0.01341735876529982</v>
       </c>
       <c r="P129" t="n">
-        <v>-6.748597936174069e-05</v>
+        <v>0.00391744027113252</v>
       </c>
       <c r="Q129" t="n">
         <v>32.01</v>
@@ -11164,19 +11164,19 @@
         </is>
       </c>
       <c r="U129" t="n">
-        <v>0.006265756249527881</v>
+        <v>0.0083529398606636</v>
       </c>
       <c r="V129" t="n">
-        <v>4.79318831475481e-05</v>
+        <v>0.0004771904260518148</v>
       </c>
       <c r="W129" t="n">
-        <v>-3.111316763550425e-05</v>
+        <v>0.0003707714716539693</v>
       </c>
       <c r="X129" t="n">
-        <v>0.001489414546980458</v>
+        <v>0.01468859478421604</v>
       </c>
       <c r="Y129" t="n">
-        <v>0.1946993919924451</v>
+        <v>0.2571152776164274</v>
       </c>
     </row>
     <row r="130">
@@ -11194,13 +11194,13 @@
         <v>46.93333333333334</v>
       </c>
       <c r="D130" t="n">
-        <v>31.94134358797329</v>
+        <v>32.10975323236918</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0631129181715524</v>
+        <v>0.1922290848230235</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.01563655060795684</v>
+        <v>0.006303694859000092</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -11215,22 +11215,22 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>2.374031448869096</v>
+        <v>2.467871880708222</v>
       </c>
       <c r="L130" t="n">
-        <v>0.001544593659646765</v>
+        <v>0.01921216453696217</v>
       </c>
       <c r="M130" t="n">
-        <v>-8.95175955329075e-06</v>
+        <v>0.001844067633677023</v>
       </c>
       <c r="N130" t="n">
-        <v>0.3962880854534297</v>
+        <v>0.6281346125688212</v>
       </c>
       <c r="O130" t="n">
-        <v>9.073584374602595e-06</v>
+        <v>0.04868006687697835</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.0002243085249105499</v>
+        <v>0.005362219758256564</v>
       </c>
       <c r="Q130" t="n">
         <v>32.01</v>
@@ -11247,19 +11247,19 @@
         </is>
       </c>
       <c r="U130" t="n">
-        <v>0.002626521099334869</v>
+        <v>0.01377153768226499</v>
       </c>
       <c r="V130" t="n">
-        <v>8.35615314271211e-06</v>
+        <v>0.001668341670143457</v>
       </c>
       <c r="W130" t="n">
-        <v>-2.423042277860768e-05</v>
+        <v>0.001398941297492627</v>
       </c>
       <c r="X130" t="n">
-        <v>0.0002669067586050903</v>
+        <v>0.05357003933558507</v>
       </c>
       <c r="Y130" t="n">
-        <v>0.08389461287491637</v>
+        <v>0.4422006766078022</v>
       </c>
     </row>
     <row r="131">
@@ -11280,10 +11280,10 @@
         <v>0.1803571428572935</v>
       </c>
       <c r="E131" t="n">
-        <v>0.1201581623370555</v>
+        <v>0.1200214838093057</v>
       </c>
       <c r="F131" t="n">
-        <v>0.5272743961133084</v>
+        <v>0.5274718166679908</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -11298,13 +11298,13 @@
         <v>-0.4200795102373955</v>
       </c>
       <c r="K131" t="n">
-        <v>1.751659471177489</v>
+        <v>1.75166168629959</v>
       </c>
       <c r="L131" t="n">
-        <v>-0.008846326384768677</v>
+        <v>-0.008872480537637784</v>
       </c>
       <c r="M131" t="n">
-        <v>0.0001863758479513995</v>
+        <v>0.0002201097130064785</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="U131" t="n">
-        <v>0.6611732196962319</v>
+        <v>0.6604004734900479</v>
       </c>
       <c r="V131" t="n">
         <v>0</v>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0.11924731283817</v>
+        <v>0.1191079425402689</v>
       </c>
     </row>
     <row r="132">
@@ -11360,13 +11360,13 @@
         <v>0.7999999999999998</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4393936031639649</v>
+        <v>0.4393374609117737</v>
       </c>
       <c r="E132" t="n">
-        <v>0.5274329884296229</v>
+        <v>0.5274293113268949</v>
       </c>
       <c r="F132" t="n">
-        <v>0.4909126691181103</v>
+        <v>0.4910477521259822</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -11381,13 +11381,13 @@
         <v>-0.764991274833384</v>
       </c>
       <c r="K132" t="n">
-        <v>1.744614188526386</v>
+        <v>1.744604565851576</v>
       </c>
       <c r="L132" t="n">
-        <v>-0.008766880242987773</v>
+        <v>-0.008770320582397906</v>
       </c>
       <c r="M132" t="n">
-        <v>1.223950650086191e-05</v>
+        <v>3.529017509321802e-05</v>
       </c>
       <c r="N132" t="n">
         <v>0</v>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="U132" t="n">
-        <v>1.195340539655349</v>
+        <v>1.195483563159258</v>
       </c>
       <c r="V132" t="n">
         <v>0</v>
@@ -11425,7 +11425,7 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0.5252249867271221</v>
+        <v>0.5252207132001485</v>
       </c>
     </row>
     <row r="133">
@@ -11443,13 +11443,13 @@
         <v>1.85</v>
       </c>
       <c r="D133" t="n">
-        <v>1.273836050869479</v>
+        <v>1.273867693953852</v>
       </c>
       <c r="E133" t="n">
-        <v>1.01783578849601</v>
+        <v>1.017930994085698</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4872356754159723</v>
+        <v>0.4872600613145051</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -11464,13 +11464,13 @@
         <v>-0.932941997857871</v>
       </c>
       <c r="K133" t="n">
-        <v>1.73546370762832</v>
+        <v>1.735466123834215</v>
       </c>
       <c r="L133" t="n">
-        <v>-0.008874019583942627</v>
+        <v>-0.008860618111393381</v>
       </c>
       <c r="M133" t="n">
-        <v>0.0004426917366595006</v>
+        <v>0.0004476188407434426</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="U133" t="n">
-        <v>0.7939186744941727</v>
+        <v>0.7939812930665195</v>
       </c>
       <c r="V133" t="n">
         <v>0</v>
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.011322229029188</v>
+        <v>1.011427118841145</v>
       </c>
     </row>
     <row r="134">
@@ -11526,13 +11526,13 @@
         <v>3.033333333333333</v>
       </c>
       <c r="D134" t="n">
-        <v>2.775839023269351</v>
+        <v>2.775998796713435</v>
       </c>
       <c r="E134" t="n">
-        <v>1.621317197306361</v>
+        <v>1.621348190287861</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6023071583833031</v>
+        <v>0.6021699330691626</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -11547,13 +11547,13 @@
         <v>0.4151273660361725</v>
       </c>
       <c r="K134" t="n">
-        <v>1.72475037448885</v>
+        <v>1.724771230778567</v>
       </c>
       <c r="L134" t="n">
-        <v>-0.007623717981659728</v>
+        <v>-0.007619305998256332</v>
       </c>
       <c r="M134" t="n">
-        <v>0.006600266970879957</v>
+        <v>0.006584928426490119</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="U134" t="n">
-        <v>0.5796616656036678</v>
+        <v>0.5796418246814649</v>
       </c>
       <c r="V134" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.60904747167597</v>
+        <v>1.609085007840527</v>
       </c>
     </row>
     <row r="135">
@@ -11609,13 +11609,13 @@
         <v>4.000000000000001</v>
       </c>
       <c r="D135" t="n">
-        <v>4.621091566542147</v>
+        <v>4.621220269172949</v>
       </c>
       <c r="E135" t="n">
-        <v>2.276452176266931</v>
+        <v>2.276285006076469</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7562855377510397</v>
+        <v>0.7560099477855864</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -11630,13 +11630,13 @@
         <v>1.548632677629808</v>
       </c>
       <c r="K135" t="n">
-        <v>1.718509854906813</v>
+        <v>1.718526154548144</v>
       </c>
       <c r="L135" t="n">
-        <v>0.003134220738832294</v>
+        <v>0.003117691990440874</v>
       </c>
       <c r="M135" t="n">
-        <v>0.02045704784471947</v>
+        <v>0.02043392037309092</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="U135" t="n">
-        <v>0.4944459759764817</v>
+        <v>0.4943864465270892</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -11674,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>2.284880129695621</v>
+        <v>2.284668667495373</v>
       </c>
     </row>
     <row r="136">
@@ -11692,13 +11692,13 @@
         <v>4.966666666666666</v>
       </c>
       <c r="D136" t="n">
-        <v>7.176979897385414</v>
+        <v>7.176816475127938</v>
       </c>
       <c r="E136" t="n">
-        <v>3.08346923695837</v>
+        <v>3.082967422673327</v>
       </c>
       <c r="F136" t="n">
-        <v>0.894031883704556</v>
+        <v>0.8938116039450095</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -11713,13 +11713,13 @@
         <v>0.7727488920116748</v>
       </c>
       <c r="K136" t="n">
-        <v>1.730809867917259</v>
+        <v>1.730798768626752</v>
       </c>
       <c r="L136" t="n">
-        <v>0.03192657451813119</v>
+        <v>0.03188627338971939</v>
       </c>
       <c r="M136" t="n">
-        <v>0.03732014236801555</v>
+        <v>0.03730423178270745</v>
       </c>
       <c r="N136" t="n">
         <v>0</v>
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="U136" t="n">
-        <v>0.448079287537107</v>
+        <v>0.4479959826748935</v>
       </c>
       <c r="V136" t="n">
         <v>0</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>3.215856039088596</v>
+        <v>3.215184949252306</v>
       </c>
     </row>
     <row r="137">
@@ -11775,13 +11775,13 @@
         <v>5.833333333333333</v>
       </c>
       <c r="D137" t="n">
-        <v>10.19077513746318</v>
+        <v>10.19002170546863</v>
       </c>
       <c r="E137" t="n">
-        <v>3.904285575698185</v>
+        <v>3.903690680977539</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9287648508347501</v>
+        <v>0.9293971181325009</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1.773400069320948</v>
+        <v>1.773344751344053</v>
       </c>
       <c r="L137" t="n">
-        <v>0.07012543973245633</v>
+        <v>0.07007809508022711</v>
       </c>
       <c r="M137" t="n">
-        <v>0.04008781367508615</v>
+        <v>0.04011525420722638</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="U137" t="n">
-        <v>0.4226625211360417</v>
+        <v>0.4226070037585303</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -11840,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>4.307258711930682</v>
+        <v>4.306374541182488</v>
       </c>
     </row>
     <row r="138">
@@ -11858,13 +11858,13 @@
         <v>6.916666666666667</v>
       </c>
       <c r="D138" t="n">
-        <v>14.998416165606</v>
+        <v>14.99713456794405</v>
       </c>
       <c r="E138" t="n">
-        <v>4.885624370326928</v>
+        <v>4.88671606532518</v>
       </c>
       <c r="F138" t="n">
-        <v>0.6592139303105498</v>
+        <v>0.6617982712682151</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -11879,13 +11879,13 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>1.877783638975546</v>
+        <v>1.877682010106324</v>
       </c>
       <c r="L138" t="n">
-        <v>0.1081537586680958</v>
+        <v>0.1081843058189231</v>
       </c>
       <c r="M138" t="n">
-        <v>0.01772385284769055</v>
+        <v>0.01787436019084214</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="U138" t="n">
-        <v>0.3833391826215346</v>
+        <v>0.3834591988486971</v>
       </c>
       <c r="V138" t="n">
         <v>0</v>
@@ -11923,7 +11923,7 @@
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>5.749480593541015</v>
+        <v>5.750789206449928</v>
       </c>
     </row>
     <row r="139">
@@ -11941,13 +11941,13 @@
         <v>7.633333333333334</v>
       </c>
       <c r="D139" t="n">
-        <v>18.71208431852404</v>
+        <v>18.71233382047279</v>
       </c>
       <c r="E139" t="n">
-        <v>5.241129660770438</v>
+        <v>5.244560601914909</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.2626738113066089</v>
+        <v>-0.2612723764161737</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -11962,13 +11962,13 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>1.960888098044857</v>
+        <v>1.960843110963972</v>
       </c>
       <c r="L139" t="n">
-        <v>0.112616324813595</v>
+        <v>0.1127920034436043</v>
       </c>
       <c r="M139" t="n">
-        <v>-0.009553728033755343</v>
+        <v>-0.009315952044578565</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="U139" t="n">
-        <v>0.3375245972595111</v>
+        <v>0.3377951255209399</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -12006,7 +12006,7 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>6.315788723495839</v>
+        <v>6.320935151676336</v>
       </c>
     </row>
     <row r="140">
@@ -12024,13 +12024,13 @@
         <v>8.25</v>
       </c>
       <c r="D140" t="n">
-        <v>21.97556260536534</v>
+        <v>21.9786147543922</v>
       </c>
       <c r="E140" t="n">
-        <v>4.676551264699274</v>
+        <v>4.679858075272302</v>
       </c>
       <c r="F140" t="n">
-        <v>-1.363458844903703</v>
+        <v>-1.36531555464647</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>2.028560763939225</v>
+        <v>2.028675393043067</v>
       </c>
       <c r="L140" t="n">
-        <v>0.09835137360278123</v>
+        <v>0.09869239411310793</v>
       </c>
       <c r="M140" t="n">
-        <v>-0.03360382446940179</v>
+        <v>-0.03344706031127833</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -12077,7 +12077,7 @@
         </is>
       </c>
       <c r="U140" t="n">
-        <v>0.2612902223267993</v>
+        <v>0.2615764864269791</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>5.741999638912405</v>
+        <v>5.749088823986074</v>
       </c>
     </row>
     <row r="141">
@@ -12107,13 +12107,13 @@
         <v>9.050000000000001</v>
       </c>
       <c r="D141" t="n">
-        <v>25.07793587717033</v>
+        <v>25.0823486080334</v>
       </c>
       <c r="E141" t="n">
-        <v>3.120909314933201</v>
+        <v>3.12101270339067</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.742867704636333</v>
+        <v>-1.746308232475405</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -12128,13 +12128,13 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>2.095422877718607</v>
+        <v>2.095895616328929</v>
       </c>
       <c r="L141" t="n">
-        <v>0.0606006250452209</v>
+        <v>0.06095148553333241</v>
       </c>
       <c r="M141" t="n">
-        <v>-0.04737902655493811</v>
+        <v>-0.04756599132527704</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>0.01984067189471752</v>
       </c>
       <c r="P141" t="n">
-        <v>0.01821745767384323</v>
+        <v>0.02134946752914934</v>
       </c>
       <c r="Q141" t="n">
         <v>37.02</v>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="U141" t="n">
-        <v>0.1533688877946125</v>
+        <v>0.1535119960452812</v>
       </c>
       <c r="V141" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>3.846175133666223</v>
+        <v>3.850441400322788</v>
       </c>
     </row>
     <row r="142">
@@ -12190,13 +12190,13 @@
         <v>10.13333333333333</v>
       </c>
       <c r="D142" t="n">
-        <v>27.3483074314982</v>
+        <v>27.35048884826322</v>
       </c>
       <c r="E142" t="n">
-        <v>1.528676938769382</v>
+        <v>1.525880117528869</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.115294966596787</v>
+        <v>-1.11687795447228</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
@@ -12211,22 +12211,22 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>2.127365951524089</v>
+        <v>2.128076816680966</v>
       </c>
       <c r="L142" t="n">
-        <v>0.00899374684160803</v>
+        <v>0.008849738016936448</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.03592025573400803</v>
+        <v>-0.03631360376504571</v>
       </c>
       <c r="N142" t="n">
-        <v>0.06174320854979103</v>
+        <v>0.0559861369961135</v>
       </c>
       <c r="O142" t="n">
-        <v>0.02991833792610701</v>
+        <v>0.03790605056055957</v>
       </c>
       <c r="P142" t="n">
-        <v>0.004322299855940482</v>
+        <v>0.007802512902614564</v>
       </c>
       <c r="Q142" t="n">
         <v>29.01</v>
@@ -12243,19 +12243,19 @@
         </is>
       </c>
       <c r="U142" t="n">
-        <v>0.06012422753422365</v>
+        <v>0.05994842771092763</v>
       </c>
       <c r="V142" t="n">
-        <v>0.001103518612044737</v>
+        <v>0.00139444938472766</v>
       </c>
       <c r="W142" t="n">
-        <v>0.0009677784852073051</v>
+        <v>0.001271735640737716</v>
       </c>
       <c r="X142" t="n">
-        <v>0.03017936625857966</v>
+        <v>0.03813887234646138</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.644295858687297</v>
+        <v>1.63961880357864</v>
       </c>
     </row>
     <row r="143">
@@ -12273,13 +12273,13 @@
         <v>11.56666666666667</v>
       </c>
       <c r="D143" t="n">
-        <v>28.46405037547181</v>
+        <v>28.46082508258495</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6022852657586331</v>
+        <v>0.5992944122488968</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.360053881150505</v>
+        <v>-0.3593901699047911</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -12294,22 +12294,22 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>2.101395432153724</v>
+        <v>2.101209936580359</v>
       </c>
       <c r="L143" t="n">
-        <v>-0.02027197462144348</v>
+        <v>-0.02085944669375994</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.008004647669356267</v>
+        <v>-0.008047887731083631</v>
       </c>
       <c r="N143" t="n">
-        <v>0.1022310869594348</v>
+        <v>0.1061209445179696</v>
       </c>
       <c r="O143" t="n">
-        <v>0.02666920580504741</v>
+        <v>0.03226238460085087</v>
       </c>
       <c r="P143" t="n">
-        <v>-0.002189665929867298</v>
+        <v>-0.003760463504501162</v>
       </c>
       <c r="Q143" t="n">
         <v>28.995</v>
@@ -12326,19 +12326,19 @@
         </is>
       </c>
       <c r="U143" t="n">
-        <v>0.01151259578173216</v>
+        <v>0.01112946783281489</v>
       </c>
       <c r="V143" t="n">
-        <v>0.000902295747556234</v>
+        <v>0.001096555870749458</v>
       </c>
       <c r="W143" t="n">
-        <v>0.0008609472688623766</v>
+        <v>0.001055057789264696</v>
       </c>
       <c r="X143" t="n">
-        <v>0.02568299161201464</v>
+        <v>0.03120888483068196</v>
       </c>
       <c r="Y143" t="n">
-        <v>0.3276951062836685</v>
+        <v>0.3167538372520005</v>
       </c>
     </row>
     <row r="144">
@@ -12356,13 +12356,13 @@
         <v>12.66666666666667</v>
       </c>
       <c r="D144" t="n">
-        <v>28.97786920043766</v>
+        <v>28.97201350550327</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4478876670289793</v>
+        <v>0.4463014702673647</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.09375374226497546</v>
+        <v>-0.09249258214162012</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -12377,22 +12377,22 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>2.077278721080258</v>
+        <v>2.07647899739963</v>
       </c>
       <c r="L144" t="n">
-        <v>-0.01859795448544499</v>
+        <v>-0.01900830805976916</v>
       </c>
       <c r="M144" t="n">
-        <v>0.003248003278876897</v>
+        <v>0.003438903134404271</v>
       </c>
       <c r="N144" t="n">
-        <v>0.1302349601016103</v>
+        <v>0.1393172748434631</v>
       </c>
       <c r="O144" t="n">
-        <v>0.02432571948549465</v>
+        <v>0.028275276988164</v>
       </c>
       <c r="P144" t="n">
-        <v>-0.002059196469469883</v>
+        <v>-0.00346125297583441</v>
       </c>
       <c r="Q144" t="n">
         <v>28.995</v>
@@ -12409,19 +12409,19 @@
         </is>
       </c>
       <c r="U144" t="n">
-        <v>0.006503159819879348</v>
+        <v>0.006250466457274683</v>
       </c>
       <c r="V144" t="n">
-        <v>0.0007992209789928847</v>
+        <v>0.0009319321880903103</v>
       </c>
       <c r="W144" t="n">
-        <v>0.0007699938900783005</v>
+        <v>0.0009018756663659028</v>
       </c>
       <c r="X144" t="n">
-        <v>0.02315972099150155</v>
+        <v>0.02699995193956568</v>
       </c>
       <c r="Y144" t="n">
-        <v>0.1884477146500055</v>
+        <v>0.1810885986158573</v>
       </c>
     </row>
     <row r="145">
@@ -12439,13 +12439,13 @@
         <v>14.13333333333333</v>
       </c>
       <c r="D145" t="n">
-        <v>29.59718463877531</v>
+        <v>29.59057689634123</v>
       </c>
       <c r="E145" t="n">
-        <v>0.4015261467971136</v>
+        <v>0.40175875268321</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.02828585116984849</v>
+        <v>-0.02726865926126411</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -12460,22 +12460,22 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>2.056506540971785</v>
+        <v>2.055394457249715</v>
       </c>
       <c r="L145" t="n">
-        <v>-0.01045860128395248</v>
+        <v>-0.01053053046023594</v>
       </c>
       <c r="M145" t="n">
-        <v>0.005052995665750842</v>
+        <v>0.005245462509269749</v>
       </c>
       <c r="N145" t="n">
-        <v>0.1636983145325466</v>
+        <v>0.1770658577354137</v>
       </c>
       <c r="O145" t="n">
-        <v>0.0214448894691804</v>
+        <v>0.02351829144897399</v>
       </c>
       <c r="P145" t="n">
-        <v>-0.001869923576551122</v>
+        <v>-0.003027186320082213</v>
       </c>
       <c r="Q145" t="n">
         <v>28.995</v>
@@ -12492,19 +12492,19 @@
         </is>
       </c>
       <c r="U145" t="n">
-        <v>0.008480747496735483</v>
+        <v>0.008453890833230813</v>
       </c>
       <c r="V145" t="n">
-        <v>0.0006964305238984141</v>
+        <v>0.0007641324124643306</v>
       </c>
       <c r="W145" t="n">
-        <v>0.0006495245736151253</v>
+        <v>0.0007135455166146369</v>
       </c>
       <c r="X145" t="n">
-        <v>0.02061238280390039</v>
+        <v>0.02261111891001251</v>
       </c>
       <c r="Y145" t="n">
-        <v>0.2510062495357116</v>
+        <v>0.2501555067739906</v>
       </c>
     </row>
     <row r="146">
@@ -12522,13 +12522,13 @@
         <v>16.85</v>
       </c>
       <c r="D146" t="n">
-        <v>30.58366178364559</v>
+        <v>30.58143663893776</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3414107011147993</v>
+        <v>0.3432850398093028</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.01805098696945927</v>
+        <v>-0.01772006759000701</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -12543,22 +12543,22 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>2.046733815457519</v>
+        <v>2.046136056499152</v>
       </c>
       <c r="L146" t="n">
-        <v>0.0007699931430980855</v>
+        <v>0.001028321747827049</v>
       </c>
       <c r="M146" t="n">
-        <v>0.003524164153454311</v>
+        <v>0.00359878262226218</v>
       </c>
       <c r="N146" t="n">
-        <v>0.2150578774167018</v>
+        <v>0.2297892857166264</v>
       </c>
       <c r="O146" t="n">
-        <v>0.01683934158891357</v>
+        <v>0.01638242028647034</v>
       </c>
       <c r="P146" t="n">
-        <v>-0.001579655954233453</v>
+        <v>-0.002361504646655055</v>
       </c>
       <c r="Q146" t="n">
         <v>28.995</v>
@@ -12575,19 +12575,19 @@
         </is>
       </c>
       <c r="U146" t="n">
-        <v>0.01153937859759997</v>
+        <v>0.01172784274873255</v>
       </c>
       <c r="V146" t="n">
-        <v>0.0005532446614977355</v>
+        <v>0.0005394744902894036</v>
       </c>
       <c r="W146" t="n">
-        <v>0.0004721021781200712</v>
+        <v>0.0004513513376708359</v>
       </c>
       <c r="X146" t="n">
-        <v>0.01692024761085423</v>
+        <v>0.01649790494310864</v>
       </c>
       <c r="Y146" t="n">
-        <v>0.3529164522224361</v>
+        <v>0.3586542799317901</v>
       </c>
     </row>
     <row r="147">
@@ -12605,13 +12605,13 @@
         <v>22.4</v>
       </c>
       <c r="D147" t="n">
-        <v>32.23233890740552</v>
+        <v>32.24347692611086</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2874586621503354</v>
+        <v>0.2880697065564881</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.0006600694074655467</v>
+        <v>-0.001495253333881036</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -12626,22 +12626,22 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>2.100525400041643</v>
+        <v>2.102143785444098</v>
       </c>
       <c r="L147" t="n">
-        <v>0.01342336372100172</v>
+        <v>0.01356350306130993</v>
       </c>
       <c r="M147" t="n">
-        <v>0.0009263980985296924</v>
+        <v>0.0008007704937910308</v>
       </c>
       <c r="N147" t="n">
-        <v>0.2850909902199914</v>
+        <v>0.2864134953075173</v>
       </c>
       <c r="O147" t="n">
-        <v>0.009383391512969796</v>
+        <v>0.00628295733171122</v>
       </c>
       <c r="P147" t="n">
-        <v>-0.001086437852673271</v>
+        <v>-0.001230388993487751</v>
       </c>
       <c r="Q147" t="n">
         <v>28.995</v>
@@ -12658,19 +12658,19 @@
         </is>
       </c>
       <c r="U147" t="n">
-        <v>0.01530880996608005</v>
+        <v>0.01538642531270043</v>
       </c>
       <c r="V147" t="n">
-        <v>0.0003476402865753588</v>
+        <v>0.0002521738410450705</v>
       </c>
       <c r="W147" t="n">
-        <v>0.0002122357847532248</v>
+        <v>0.0001154987590060771</v>
       </c>
       <c r="X147" t="n">
-        <v>0.01120525953476454</v>
+        <v>0.008130961425105476</v>
       </c>
       <c r="Y147" t="n">
-        <v>0.4934387510957593</v>
+        <v>0.4961118495453845</v>
       </c>
     </row>
     <row r="148">
@@ -12688,13 +12688,13 @@
         <v>24.05</v>
       </c>
       <c r="D148" t="n">
-        <v>32.70193637387037</v>
+        <v>32.7132012455741</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2908143446361375</v>
+        <v>0.289749301117471</v>
       </c>
       <c r="F148" t="n">
-        <v>0.005958378862213135</v>
+        <v>0.004701876460281695</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -12709,22 +12709,22 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>2.124504248334809</v>
+        <v>2.126226732243604</v>
       </c>
       <c r="L148" t="n">
-        <v>0.01428797960705364</v>
+        <v>0.0141696542052645</v>
       </c>
       <c r="M148" t="n">
-        <v>-9.519851664598154e-05</v>
+        <v>-0.000293750307107845</v>
       </c>
       <c r="N148" t="n">
-        <v>0.2989865956549137</v>
+        <v>0.2948576507526223</v>
       </c>
       <c r="O148" t="n">
-        <v>0.007716826484273992</v>
+        <v>0.004541907741506215</v>
       </c>
       <c r="P148" t="n">
-        <v>-0.0008851285948424789</v>
+        <v>-0.0007687188886404113</v>
       </c>
       <c r="Q148" t="n">
         <v>28.98</v>
@@ -12741,19 +12741,19 @@
         </is>
       </c>
       <c r="U148" t="n">
-        <v>0.01561820252417522</v>
+        <v>0.01552148455655769</v>
       </c>
       <c r="V148" t="n">
-        <v>0.0002974627596454867</v>
+        <v>0.0001989076379162201</v>
       </c>
       <c r="W148" t="n">
-        <v>0.0001546689767463408</v>
+        <v>5.900606001244045e-05</v>
       </c>
       <c r="X148" t="n">
-        <v>0.009727608239522602</v>
+        <v>0.006506905588435094</v>
       </c>
       <c r="Y148" t="n">
-        <v>0.5107454652197997</v>
+        <v>0.5077574479287422</v>
       </c>
     </row>
     <row r="149">
@@ -12771,13 +12771,13 @@
         <v>25.55</v>
       </c>
       <c r="D149" t="n">
-        <v>33.14662582651447</v>
+        <v>33.15473596368054</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3051036837037131</v>
+        <v>0.3018256708479612</v>
       </c>
       <c r="F149" t="n">
-        <v>0.009105086945152135</v>
+        <v>0.007836449475190063</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -12792,22 +12792,22 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>2.14560259630611</v>
+        <v>2.146900207468178</v>
       </c>
       <c r="L149" t="n">
-        <v>0.01330080708950798</v>
+        <v>0.01282750878536099</v>
       </c>
       <c r="M149" t="n">
-        <v>-0.0008570637649848618</v>
+        <v>-0.001062783733013854</v>
       </c>
       <c r="N149" t="n">
-        <v>0.3096008091533328</v>
+        <v>0.3008853820577578</v>
       </c>
       <c r="O149" t="n">
-        <v>0.006559466523585245</v>
+        <v>0.003779460337428514</v>
       </c>
       <c r="P149" t="n">
-        <v>-0.0006754470977203206</v>
+        <v>-0.0002878484120212748</v>
       </c>
       <c r="Q149" t="n">
         <v>29.01</v>
@@ -12824,19 +12824,19 @@
         </is>
       </c>
       <c r="U149" t="n">
-        <v>0.01540376887744909</v>
+        <v>0.01507844375563558</v>
       </c>
       <c r="V149" t="n">
-        <v>0.0002557941564727905</v>
+        <v>0.0001682178882382971</v>
       </c>
       <c r="W149" t="n">
-        <v>0.0001119176927437326</v>
+        <v>3.137821274756879e-05</v>
       </c>
       <c r="X149" t="n">
-        <v>0.008478713193212481</v>
+        <v>0.005577219668908662</v>
       </c>
       <c r="Y149" t="n">
-        <v>0.5105829632989139</v>
+        <v>0.4999218214613053</v>
       </c>
     </row>
     <row r="150">
@@ -12854,13 +12854,13 @@
         <v>27.01666666666667</v>
       </c>
       <c r="D150" t="n">
-        <v>33.60650743528318</v>
+        <v>33.60812498901727</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3178538665585267</v>
+        <v>0.3130115732771155</v>
       </c>
       <c r="F150" t="n">
-        <v>0.006226158618857267</v>
+        <v>0.005570657085305637</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -12875,22 +12875,22 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>2.164013726761088</v>
+        <v>2.164344621577035</v>
       </c>
       <c r="L150" t="n">
-        <v>0.01175847298503752</v>
+        <v>0.0110278060126251</v>
       </c>
       <c r="M150" t="n">
-        <v>-0.001043516318232963</v>
+        <v>-0.001154687881417951</v>
       </c>
       <c r="N150" t="n">
-        <v>0.3184804086726417</v>
+        <v>0.3060858078430974</v>
       </c>
       <c r="O150" t="n">
-        <v>0.005706662885009567</v>
+        <v>0.003673424091542817</v>
       </c>
       <c r="P150" t="n">
-        <v>-0.0005026647215329997</v>
+        <v>0.0001083999204683676</v>
       </c>
       <c r="Q150" t="n">
         <v>29.01</v>
@@ -12907,19 +12907,19 @@
         </is>
       </c>
       <c r="U150" t="n">
-        <v>0.01489174538373089</v>
+        <v>0.01440878570365691</v>
       </c>
       <c r="V150" t="n">
-        <v>0.0002213015142634324</v>
+        <v>0.0001557063292271108</v>
       </c>
       <c r="W150" t="n">
-        <v>8.017619307994671e-05</v>
+        <v>2.447839510156408e-05</v>
       </c>
       <c r="X150" t="n">
-        <v>0.007437170984533468</v>
+        <v>0.005232997774245813</v>
       </c>
       <c r="Y150" t="n">
-        <v>0.5004595519626962</v>
+        <v>0.4842522708684667</v>
       </c>
     </row>
     <row r="151">
@@ -12937,13 +12937,13 @@
         <v>30.05</v>
       </c>
       <c r="D151" t="n">
-        <v>34.5976290083399</v>
+        <v>34.58195143968543</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3212622662351068</v>
+        <v>0.3170103549647241</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.00402119203103507</v>
+        <v>-0.002999851203788345</v>
       </c>
       <c r="G151" t="n">
         <v>1</v>
@@ -12958,22 +12958,22 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>2.194696368779029</v>
+        <v>2.192362088260938</v>
       </c>
       <c r="L151" t="n">
-        <v>0.008643799274912711</v>
+        <v>0.007979341350247637</v>
       </c>
       <c r="M151" t="n">
-        <v>-0.0009652523434678254</v>
+        <v>-0.0008137773671506002</v>
       </c>
       <c r="N151" t="n">
-        <v>0.3336098964013117</v>
+        <v>0.3180295213518891</v>
       </c>
       <c r="O151" t="n">
-        <v>0.0046762155598358</v>
+        <v>0.005135839339052373</v>
       </c>
       <c r="P151" t="n">
-        <v>-0.0001938570609676674</v>
+        <v>0.0008166001620623204</v>
       </c>
       <c r="Q151" t="n">
         <v>28.995</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="U151" t="n">
-        <v>0.01322416726636053</v>
+        <v>0.01280654003312175</v>
       </c>
       <c r="V151" t="n">
-        <v>0.0001731371896756962</v>
+        <v>0.0001819834412702878</v>
       </c>
       <c r="W151" t="n">
-        <v>4.562229347686444e-05</v>
+        <v>6.420935313038018e-05</v>
       </c>
       <c r="X151" t="n">
-        <v>0.005990136255946315</v>
+        <v>0.006293342528835937</v>
       </c>
       <c r="Y151" t="n">
-        <v>0.4575248330257741</v>
+        <v>0.4428751455358038</v>
       </c>
     </row>
     <row r="152">
@@ -13020,13 +13020,13 @@
         <v>33.05</v>
       </c>
       <c r="D152" t="n">
-        <v>35.54515317446911</v>
+        <v>35.52102140943061</v>
       </c>
       <c r="E152" t="n">
-        <v>0.2939337794328081</v>
+        <v>0.2951987646734038</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.01481686994613171</v>
+        <v>-0.01206080308671577</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -13041,22 +13041,22 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>2.216262200589915</v>
+        <v>2.212569999624321</v>
       </c>
       <c r="L152" t="n">
-        <v>0.005930702185700687</v>
+        <v>0.006105338539264038</v>
       </c>
       <c r="M152" t="n">
-        <v>-0.0008360712476423337</v>
+        <v>-0.0004125497145050438</v>
       </c>
       <c r="N152" t="n">
-        <v>0.3467142302807875</v>
+        <v>0.3369925873873175</v>
       </c>
       <c r="O152" t="n">
-        <v>0.004527388652495162</v>
+        <v>0.008578068575033307</v>
       </c>
       <c r="P152" t="n">
-        <v>0.000112189132657267</v>
+        <v>0.001518467427489923</v>
       </c>
       <c r="Q152" t="n">
         <v>29.01</v>
@@ -13073,19 +13073,19 @@
         </is>
       </c>
       <c r="U152" t="n">
-        <v>0.01094529989548966</v>
+        <v>0.01106992479933209</v>
       </c>
       <c r="V152" t="n">
-        <v>0.0001534722184735378</v>
+        <v>0.0002676714073288779</v>
       </c>
       <c r="W152" t="n">
-        <v>4.670966747733546e-05</v>
+        <v>0.0001626495793439559</v>
       </c>
       <c r="X152" t="n">
-        <v>0.005455193513667488</v>
+        <v>0.009507961790421491</v>
       </c>
       <c r="Y152" t="n">
-        <v>0.3890523613256806</v>
+        <v>0.3932150357978619</v>
       </c>
     </row>
     <row r="153">
@@ -13103,13 +13103,13 @@
         <v>35.71666666666666</v>
       </c>
       <c r="D153" t="n">
-        <v>36.27704743837425</v>
+        <v>36.26596730971526</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2408935352022574</v>
+        <v>0.2516819019482739</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.02587000667387462</v>
+        <v>-0.02204425763778248</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -13124,22 +13124,22 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>2.229095697575954</v>
+        <v>2.227356071189299</v>
       </c>
       <c r="L153" t="n">
-        <v>0.003863061996459916</v>
+        <v>0.005508003926731841</v>
       </c>
       <c r="M153" t="n">
-        <v>-0.0006937381224151099</v>
+        <v>2.952724237245924e-05</v>
       </c>
       <c r="N153" t="n">
-        <v>0.3591648130206834</v>
+        <v>0.3652174732187516</v>
       </c>
       <c r="O153" t="n">
-        <v>0.005210081099334241</v>
+        <v>0.0135068591838371</v>
       </c>
       <c r="P153" t="n">
-        <v>0.0004493941309906995</v>
+        <v>0.002291792353591941</v>
       </c>
       <c r="Q153" t="n">
         <v>28.98</v>
@@ -13156,19 +13156,19 @@
         </is>
       </c>
       <c r="U153" t="n">
-        <v>0.008373401835163687</v>
+        <v>0.00941278097290961</v>
       </c>
       <c r="V153" t="n">
-        <v>0.0001607771425911803</v>
+        <v>0.0003973422594022253</v>
       </c>
       <c r="W153" t="n">
-        <v>7.787537641016748e-05</v>
+        <v>0.0003025505762374235</v>
       </c>
       <c r="X153" t="n">
-        <v>0.005832520028786509</v>
+        <v>0.0144100013902495</v>
       </c>
       <c r="Y153" t="n">
-        <v>0.3037622955948031</v>
+        <v>0.3413636070570498</v>
       </c>
     </row>
     <row r="154">
@@ -13186,13 +13186,13 @@
         <v>38.41666666666666</v>
       </c>
       <c r="D154" t="n">
-        <v>36.835696706298</v>
+        <v>36.86985789883801</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1546969243125667</v>
+        <v>0.1765105008120322</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.03362783079533318</v>
+        <v>-0.02962948019904615</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
@@ -13207,22 +13207,22 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>2.236930271054624</v>
+        <v>2.242127153848393</v>
       </c>
       <c r="L154" t="n">
-        <v>0.002213116736538179</v>
+        <v>0.006280808891351908</v>
       </c>
       <c r="M154" t="n">
-        <v>-0.000585596353735072</v>
+        <v>0.0003654081831800483</v>
       </c>
       <c r="N154" t="n">
-        <v>0.3747112984822444</v>
+        <v>0.4096754511932953</v>
       </c>
       <c r="O154" t="n">
-        <v>0.006952110029900082</v>
+        <v>0.02090710538761079</v>
       </c>
       <c r="P154" t="n">
-        <v>0.0007055955238098011</v>
+        <v>0.002879348659543106</v>
       </c>
       <c r="Q154" t="n">
         <v>28.98</v>
@@ -13239,19 +13239,19 @@
         </is>
       </c>
       <c r="U154" t="n">
-        <v>0.005189001400015388</v>
+        <v>0.00758866542262381</v>
       </c>
       <c r="V154" t="n">
-        <v>0.0001987971708125328</v>
+        <v>0.0005981774591723834</v>
       </c>
       <c r="W154" t="n">
-        <v>0.0001460120295966885</v>
+        <v>0.0005138568214444482</v>
       </c>
       <c r="X154" t="n">
-        <v>0.007322832290120574</v>
+        <v>0.02205471791797375</v>
       </c>
       <c r="Y154" t="n">
-        <v>0.1911404817795225</v>
+        <v>0.2797930157739653</v>
       </c>
     </row>
     <row r="155">
@@ -13269,13 +13269,13 @@
         <v>46.41666666666666</v>
       </c>
       <c r="D155" t="n">
-        <v>36.835696706298</v>
+        <v>37.16424874161186</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.1546969243125638</v>
+        <v>-0.1029127901185696</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.04372063136094942</v>
+        <v>-0.04022634253360428</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -13290,22 +13290,22 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>2.238313376337733</v>
+        <v>2.311574514724551</v>
       </c>
       <c r="L155" t="n">
-        <v>-0.001867340415760699</v>
+        <v>0.01108103132768778</v>
       </c>
       <c r="M155" t="n">
-        <v>-0.0004345179343396473</v>
+        <v>0.0008346474259039211</v>
       </c>
       <c r="N155" t="n">
-        <v>0.4586340146098989</v>
+        <v>0.6822048897137082</v>
       </c>
       <c r="O155" t="n">
-        <v>0.01402856900201359</v>
+        <v>0.04722525424249244</v>
       </c>
       <c r="P155" t="n">
-        <v>0.001063519219218576</v>
+        <v>0.003700188554177305</v>
       </c>
       <c r="Q155" t="n">
         <v>28.98</v>
@@ -13322,19 +13322,19 @@
         </is>
       </c>
       <c r="U155" t="n">
-        <v>-0.005033909308933797</v>
+        <v>0.002024581679390566</v>
       </c>
       <c r="V155" t="n">
-        <v>0.0003704544549032005</v>
+        <v>0.001358713073094444</v>
       </c>
       <c r="W155" t="n">
-        <v>0.0004331306696072843</v>
+        <v>0.001321548874487664</v>
       </c>
       <c r="X155" t="n">
-        <v>0.01364594794431124</v>
+        <v>0.05049555061696176</v>
       </c>
       <c r="Y155" t="n">
-        <v>-0.1854275565508955</v>
+        <v>0.07524205713058127</v>
       </c>
     </row>
     <row r="156">

--- a/data/processed/BR_processed.xlsx
+++ b/data/processed/BR_processed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB199"/>
+  <dimension ref="A1:AC199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,11 @@
           <t>rX</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -624,13 +629,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.720009759406404</v>
+        <v>3.793</v>
       </c>
       <c r="R2" t="n">
-        <v>0.272194387120507</v>
+        <v>0.1211713191023502</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09800680767970055</v>
+        <v>0.1823200773785827</v>
       </c>
       <c r="T2" t="n">
         <v>36.98999999999999</v>
@@ -661,6 +666,9 @@
       <c r="AB2" t="n">
         <v>-0.1894867880277713</v>
       </c>
+      <c r="AC2" t="n">
+        <v>6.408531830959417</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -716,13 +724,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.840220529403128</v>
+        <v>3.862</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2252294887280062</v>
+        <v>0.1643459222769561</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.09633070290995899</v>
+        <v>-0.003666547000902715</v>
       </c>
       <c r="T3" t="n">
         <v>36.98999999999999</v>
@@ -753,6 +761,9 @@
       <c r="AB3" t="n">
         <v>0.2335002217749586</v>
       </c>
+      <c r="AC3" t="n">
+        <v>6.041180577277775</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -808,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.931735462857129</v>
+        <v>3.945</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1822317874694273</v>
+        <v>0.1237349849849849</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.09408222420884896</v>
+        <v>-0.1784278001598938</v>
       </c>
       <c r="T4" t="n">
         <v>37.02</v>
@@ -845,6 +856,9 @@
       <c r="AB4" t="n">
         <v>0.4684119414051205</v>
       </c>
+      <c r="AC4" t="n">
+        <v>5.586210832457092</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -900,13 +914,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.026251579220495</v>
+        <v>3.97</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1254551549674314</v>
+        <v>-0.06081411062224973</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09019502216252946</v>
+        <v>-0.08642503747442144</v>
       </c>
       <c r="T5" t="n">
         <v>37.02</v>
@@ -937,6 +951,9 @@
       <c r="AB5" t="n">
         <v>0.5886193578271629</v>
       </c>
+      <c r="AC5" t="n">
+        <v>4.664400380018596</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -992,13 +1009,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.092995116777141</v>
+        <v>3.842</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06237720499086308</v>
+        <v>0.05452187546153775</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0859307330282086</v>
+        <v>0.1595135569078454</v>
       </c>
       <c r="T6" t="n">
         <v>36.98999999999999</v>
@@ -1029,6 +1046,9 @@
       <c r="AB6" t="n">
         <v>0.7562525785496449</v>
       </c>
+      <c r="AC6" t="n">
+        <v>2.998200813562025</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1084,13 +1104,13 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.115595156373407</v>
+        <v>4.075</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.00179299128394117</v>
+        <v>0.1756506729374099</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08135968960571585</v>
+        <v>0.007603290266636836</v>
       </c>
       <c r="T7" t="n">
         <v>36.98999999999999</v>
@@ -1121,6 +1141,9 @@
       <c r="AB7" t="n">
         <v>0.9699123106156134</v>
       </c>
+      <c r="AC7" t="n">
+        <v>-0.04298135787803536</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1176,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.102270442384963</v>
+        <v>4.121</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.0456173144747174</v>
+        <v>0.1204935064935073</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07775734492003358</v>
+        <v>-0.1395586398558323</v>
       </c>
       <c r="T8" t="n">
         <v>37.02</v>
@@ -1213,6 +1236,9 @@
       <c r="AB8" t="n">
         <v>1.148274152646601</v>
       </c>
+      <c r="AC8" t="n">
+        <v>-1.88873635131474</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1268,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.069738802525579</v>
+        <v>4.198</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.08362178570766154</v>
+        <v>0.03286287625418227</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.07446553506561125</v>
+        <v>-0.1908673934760898</v>
       </c>
       <c r="T9" t="n">
         <v>37.005</v>
@@ -1305,6 +1331,9 @@
       <c r="AB9" t="n">
         <v>1.332862611765866</v>
       </c>
+      <c r="AC9" t="n">
+        <v>-1.486039421947599</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1360,13 +1389,13 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.999702704254983</v>
+        <v>4.117</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1307202042470745</v>
+        <v>-0.1043881118881123</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.07023465692005948</v>
+        <v>-0.1699142216264099</v>
       </c>
       <c r="T10" t="n">
         <v>36.975</v>
@@ -1397,6 +1426,9 @@
       <c r="AB10" t="n">
         <v>1.604951469242643</v>
       </c>
+      <c r="AC10" t="n">
+        <v>-0.9739759648784792</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1452,13 +1484,13 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.917115608645185</v>
+        <v>4.069</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1683140414317683</v>
+        <v>-0.1786479394968361</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06671434081788104</v>
+        <v>-0.09709318694887389</v>
       </c>
       <c r="T11" t="n">
         <v>37.02</v>
@@ -1489,6 +1521,9 @@
       <c r="AB11" t="n">
         <v>1.869132450344215</v>
       </c>
+      <c r="AC11" t="n">
+        <v>-2.312407534393096</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1544,13 +1579,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.707943394050008</v>
+        <v>3.707</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.2340719816903203</v>
+        <v>-0.2053500531726331</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.06080467728556996</v>
+        <v>-0.3417604751194493</v>
       </c>
       <c r="T12" t="n">
         <v>36.98999999999999</v>
@@ -1581,6 +1616,9 @@
       <c r="AB12" t="n">
         <v>2.454139740045096</v>
       </c>
+      <c r="AC12" t="n">
+        <v>-5.68839737056028</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1636,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.529086081351898</v>
+        <v>3.632</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.275292321123219</v>
+        <v>-0.594389478764473</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.05653563143294205</v>
+        <v>-0.2272054966611423</v>
       </c>
       <c r="T13" t="n">
         <v>36.98999999999999</v>
@@ -1673,6 +1711,9 @@
       <c r="AB13" t="n">
         <v>2.922457930352179</v>
       </c>
+      <c r="AC13" t="n">
+        <v>-8.131465330134601</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1728,13 +1769,13 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.374225161118914</v>
+        <v>3.117</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.3044895065449631</v>
+        <v>-0.5820535714285668</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0529814049300289</v>
+        <v>0.7090592250413654</v>
       </c>
       <c r="T14" t="n">
         <v>36.98999999999999</v>
@@ -1765,6 +1806,9 @@
       <c r="AB14" t="n">
         <v>3.32810920700856</v>
       </c>
+      <c r="AC14" t="n">
+        <v>-10.06931167936583</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1820,13 +1864,13 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.226362234945449</v>
+        <v>3.002</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.3284941407702155</v>
+        <v>0.02892857142856986</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.04999420547638744</v>
+        <v>0.4970778061224418</v>
       </c>
       <c r="T15" t="n">
         <v>36.98999999999999</v>
@@ -1857,6 +1901,9 @@
       <c r="AB15" t="n">
         <v>3.720198978202901</v>
       </c>
+      <c r="AC15" t="n">
+        <v>-11.77657847189712</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1912,13 +1959,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.067630629733379</v>
+        <v>3.144</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.3511507649895913</v>
+        <v>-0.1181142857142934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.04708821144478381</v>
+        <v>-0.5393055321302125</v>
       </c>
       <c r="T16" t="n">
         <v>36.98999999999999</v>
@@ -1949,6 +1996,9 @@
       <c r="AB16" t="n">
         <v>4.147837664908577</v>
       </c>
+      <c r="AC16" t="n">
+        <v>-13.46059191897283</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2004,13 +2054,13 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.93570295655479</v>
+        <v>2.979</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.3679953344021905</v>
+        <v>-0.3804545454545485</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.04478255749755211</v>
+        <v>-0.6047366430360981</v>
       </c>
       <c r="T17" t="n">
         <v>36.98999999999999</v>
@@ -2041,6 +2091,9 @@
       <c r="AB17" t="n">
         <v>4.509989514130527</v>
       </c>
+      <c r="AC17" t="n">
+        <v>-14.75498429632322</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2096,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.797767384505106</v>
+        <v>2.865</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.3839913071544627</v>
+        <v>-0.5615878239407621</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.04234929502997165</v>
+        <v>-0.2212720525577436</v>
       </c>
       <c r="T18" t="n">
         <v>36.98999999999999</v>
@@ -2133,6 +2186,9 @@
       <c r="AB18" t="n">
         <v>4.89598446832408</v>
       </c>
+      <c r="AC18" t="n">
+        <v>-16.07102917490204</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2188,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.687261379449545</v>
+        <v>2.651</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.3957108887585525</v>
+        <v>-0.5645707133917375</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.04092894061923225</v>
+        <v>0.4802334714256511</v>
       </c>
       <c r="T19" t="n">
         <v>36.975</v>
@@ -2225,6 +2281,9 @@
       <c r="AB19" t="n">
         <v>5.211742876391597</v>
       </c>
+      <c r="AC19" t="n">
+        <v>-17.05334026099019</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2280,13 +2339,13 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.484385616442498</v>
+        <v>2.537</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.415792163269634</v>
+        <v>0.1085707133917388</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.03939615742509339</v>
+        <v>2.212332235708255</v>
       </c>
       <c r="T20" t="n">
         <v>36.975</v>
@@ -2317,6 +2376,9 @@
       <c r="AB20" t="n">
         <v>5.796534404237628</v>
       </c>
+      <c r="AC20" t="n">
+        <v>-18.68203745361305</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2372,13 +2434,13 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.061741439889001</v>
+        <v>5.714</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3054288786537924</v>
+        <v>2.17918552314104</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1578883408507746</v>
+        <v>-3.029447874058492</v>
       </c>
       <c r="T21" t="n">
         <v>36.975</v>
@@ -2409,6 +2471,9 @@
       <c r="AB21" t="n">
         <v>0.3867603473799655</v>
       </c>
+      <c r="AC21" t="n">
+        <v>6.607120314284542</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2464,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.264213121979524</v>
+        <v>6.735</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1805031583634609</v>
+        <v>0.2712144768589542</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1419333878460203</v>
+        <v>-1.549682637018501</v>
       </c>
       <c r="T22" t="n">
         <v>36.98999999999999</v>
@@ -2501,6 +2566,9 @@
       <c r="AB22" t="n">
         <v>0.7094015748352079</v>
       </c>
+      <c r="AC22" t="n">
+        <v>4.399605000292152</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2556,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.359613776677344</v>
+        <v>6.245</v>
       </c>
       <c r="R23" t="n">
-        <v>0.07519608641532916</v>
+        <v>-0.3979033540353163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1250667591998688</v>
+        <v>-0.5919499147737698</v>
       </c>
       <c r="T23" t="n">
         <v>37.005</v>
@@ -2593,6 +2661,9 @@
       <c r="AB23" t="n">
         <v>1.121020564592929</v>
       </c>
+      <c r="AC23" t="n">
+        <v>1.325198546446967</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2648,13 +2719,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.306819229481454</v>
+        <v>6.449</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.1084301495022082</v>
+        <v>-0.3988010291595225</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.08001895875657117</v>
+        <v>0.05805436189352953</v>
       </c>
       <c r="T24" t="n">
         <v>37.11</v>
@@ -2685,6 +2756,9 @@
       <c r="AB24" t="n">
         <v>2.602636611509764</v>
       </c>
+      <c r="AC24" t="n">
+        <v>-5.91182852435043</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2740,13 +2814,13 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.203394051497787</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1598292832121821</v>
+        <v>-0.33840126423259</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.05971704065046127</v>
+        <v>-0.08848768950894562</v>
       </c>
       <c r="T25" t="n">
         <v>36.705</v>
@@ -2777,6 +2851,9 @@
       <c r="AB25" t="n">
         <v>3.400331998303826</v>
       </c>
+      <c r="AC25" t="n">
+        <v>-8.755073270195446</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2832,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.878017891831871</v>
+        <v>6.429</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.2194034181496045</v>
+        <v>-1.090371933878425</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.01716376362856573</v>
+        <v>0.3041098272373764</v>
       </c>
       <c r="T26" t="n">
         <v>36.855</v>
@@ -2869,6 +2946,9 @@
       <c r="AB26" t="n">
         <v>4.852384690381618</v>
       </c>
+      <c r="AC26" t="n">
+        <v>-13.3351650591084</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2924,13 +3004,13 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.695314034976831</v>
+        <v>5.02</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.2253411226296556</v>
+        <v>-0.5425576923076991</v>
       </c>
       <c r="S27" t="n">
-        <v>0.00476374377250538</v>
+        <v>0.5545953409370558</v>
       </c>
       <c r="T27" t="n">
         <v>37.32</v>
@@ -2961,6 +3041,9 @@
       <c r="AB27" t="n">
         <v>4.970900120515864</v>
       </c>
+      <c r="AC27" t="n">
+        <v>-12.57821071788904</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3016,13 +3099,13 @@
         <v>0.0320301807753974</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.502871395565659</v>
+        <v>5.694</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.209771362643683</v>
+        <v>-0.18412587412588</v>
       </c>
       <c r="S28" t="n">
-        <v>0.02899263136098165</v>
+        <v>-0.130175432471791</v>
       </c>
       <c r="T28" t="n">
         <v>37.11</v>
@@ -3053,6 +3136,9 @@
       <c r="AB28" t="n">
         <v>4.235858944436043</v>
       </c>
+      <c r="AC28" t="n">
+        <v>-9.157837181360259</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3108,13 +3194,13 @@
         <v>0.05443836246253775</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.382108602445239</v>
+        <v>5.184</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.187795120142614</v>
+        <v>-0.4880967704861525</v>
       </c>
       <c r="S29" t="n">
-        <v>0.03918978104830084</v>
+        <v>-0.2112393043113611</v>
       </c>
       <c r="T29" t="n">
         <v>36.93</v>
@@ -3145,6 +3231,9 @@
       <c r="AB29" t="n">
         <v>3.212068818003286</v>
       </c>
+      <c r="AC29" t="n">
+        <v>-5.802791097457179</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3200,13 +3289,13 @@
         <v>0.02803753103562011</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.178095790866871</v>
+        <v>5.551</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.1304671655500824</v>
+        <v>0.05160039960039975</v>
       </c>
       <c r="S30" t="n">
-        <v>0.04385413982233808</v>
+        <v>0.1746218723130543</v>
       </c>
       <c r="T30" t="n">
         <v>27.99</v>
@@ -3237,6 +3326,9 @@
       <c r="AB30" t="n">
         <v>1.124583943411706</v>
       </c>
+      <c r="AC30" t="n">
+        <v>0.249695268178288</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3292,13 +3384,13 @@
         <v>-0.007010515913380644</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.017798817704199</v>
+        <v>5.082</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.05567206474214381</v>
+        <v>-0.2296691555796904</v>
       </c>
       <c r="S31" t="n">
-        <v>0.04111207151267104</v>
+        <v>-0.07248445480228022</v>
       </c>
       <c r="T31" t="n">
         <v>28.02</v>
@@ -3329,6 +3421,9 @@
       <c r="AB31" t="n">
         <v>0.05896524415184423</v>
       </c>
+      <c r="AC31" t="n">
+        <v>3.415177593435335</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3384,13 +3479,13 @@
         <v>0.0089492289119854</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.991936403001823</v>
+        <v>4.694</v>
       </c>
       <c r="R32" t="n">
-        <v>0.02718058382067734</v>
+        <v>-0.1571836048327968</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0344387439198068</v>
+        <v>0.146435644841408</v>
       </c>
       <c r="T32" t="n">
         <v>27.99</v>
@@ -3421,6 +3516,9 @@
       <c r="AB32" t="n">
         <v>0.115222492751227</v>
       </c>
+      <c r="AC32" t="n">
+        <v>3.467936919385896</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3476,13 +3574,13 @@
         <v>0.04451854124995235</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.120752463480209</v>
+        <v>4.429</v>
       </c>
       <c r="R33" t="n">
-        <v>0.08716816995349497</v>
+        <v>0.3477012333657894</v>
       </c>
       <c r="S33" t="n">
-        <v>0.01448825872320491</v>
+        <v>0.1118647240534484</v>
       </c>
       <c r="T33" t="n">
         <v>28.02</v>
@@ -3513,6 +3611,9 @@
       <c r="AB33" t="n">
         <v>0.1239112748227083</v>
       </c>
+      <c r="AC33" t="n">
+        <v>3.588172588883364</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3568,13 +3669,13 @@
         <v>0.09969346862095835</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.334003110521341</v>
+        <v>6.02</v>
       </c>
       <c r="R34" t="n">
-        <v>0.08594037729372817</v>
+        <v>0.2985641025641019</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.03093166043981172</v>
+        <v>-0.478043411215818</v>
       </c>
       <c r="T34" t="n">
         <v>27.99</v>
@@ -3605,6 +3706,9 @@
       <c r="AB34" t="n">
         <v>-0.0966586741807568</v>
       </c>
+      <c r="AC34" t="n">
+        <v>5.00605570996961</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3660,13 +3764,13 @@
         <v>0.1396218551781902</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.410999804581532</v>
+        <v>6.041</v>
       </c>
       <c r="R35" t="n">
-        <v>0.03632983611183471</v>
+        <v>-0.459413008989952</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.06796230141085968</v>
+        <v>-0.366661396245335</v>
       </c>
       <c r="T35" t="n">
         <v>27.99</v>
@@ -3697,6 +3801,9 @@
       <c r="AB35" t="n">
         <v>-0.297227370619138</v>
       </c>
+      <c r="AC35" t="n">
+        <v>6.690989079221494</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3752,13 +3859,13 @@
         <v>0.1704121024990759</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.411512307924802</v>
+        <v>5.102</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.05315602091197569</v>
+        <v>-0.4825083249806434</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.09701100421408849</v>
+        <v>0.4337329331166945</v>
       </c>
       <c r="T36" t="n">
         <v>27.99</v>
@@ -3789,6 +3896,9 @@
       <c r="AB36" t="n">
         <v>-0.5602861066626278</v>
       </c>
+      <c r="AC36" t="n">
+        <v>9.171112393228372</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3844,13 +3954,13 @@
         <v>0.1885370639025594</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.310807757574504</v>
+        <v>5.041</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.155198221192089</v>
+        <v>0.3563014284289183</v>
       </c>
       <c r="S37" t="n">
-        <v>-0.1141107894689042</v>
+        <v>1.30173552221343</v>
       </c>
       <c r="T37" t="n">
         <v>27.99</v>
@@ -3881,6 +3991,9 @@
       <c r="AB37" t="n">
         <v>-0.8621711121897764</v>
       </c>
+      <c r="AC37" t="n">
+        <v>12.07049448446898</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3936,13 +4049,13 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.679646816338743</v>
+        <v>4.507</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.1298225483414255</v>
+        <v>0.2643946541931173</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0003388477310381915</v>
+        <v>-0.1273859323550632</v>
       </c>
       <c r="T38" t="n">
         <v>36.98999999999999</v>
@@ -3973,6 +4086,9 @@
       <c r="AB38" t="n">
         <v>0.1228716992743445</v>
       </c>
+      <c r="AC38" t="n">
+        <v>3.61206990209875</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4028,13 +4144,13 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.522281289941776</v>
+        <v>4.667</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.1288605087494794</v>
+        <v>-0.001380955562979569</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001242587214626584</v>
+        <v>-0.3095054809426309</v>
       </c>
       <c r="T39" t="n">
         <v>36.98999999999999</v>
@@ -4065,6 +4181,9 @@
       <c r="AB39" t="n">
         <v>0.2288131121036305</v>
       </c>
+      <c r="AC39" t="n">
+        <v>2.964101982474601</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4120,13 +4239,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.415172087328609</v>
+        <v>4.59</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.1275671028846683</v>
+        <v>-0.3112769466988397</v>
       </c>
       <c r="S40" t="n">
-        <v>0.002510147587957354</v>
+        <v>-0.2223206301487446</v>
       </c>
       <c r="T40" t="n">
         <v>37.005</v>
@@ -4157,6 +4276,9 @@
       <c r="AB40" t="n">
         <v>0.4146584939605738</v>
       </c>
+      <c r="AC40" t="n">
+        <v>2.06219207578188</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4212,13 +4334,13 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.315954304740536</v>
+        <v>4.185</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.1248953686889829</v>
+        <v>-0.3753060998805706</v>
       </c>
       <c r="S41" t="n">
-        <v>0.003995796248640335</v>
+        <v>-0.04867019760941246</v>
       </c>
       <c r="T41" t="n">
         <v>37.02</v>
@@ -4249,6 +4371,9 @@
       <c r="AB41" t="n">
         <v>0.8553138834517061</v>
       </c>
+      <c r="AC41" t="n">
+        <v>0.1559647411768088</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4304,13 +4429,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.021593376654234</v>
+        <v>4.36</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.1104945991232438</v>
+        <v>-0.2384987599364075</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0074051021323331</v>
+        <v>0.01746474976939794</v>
       </c>
       <c r="T42" t="n">
         <v>36.98999999999999</v>
@@ -4341,6 +4466,9 @@
       <c r="AB42" t="n">
         <v>3.323450694693622</v>
       </c>
+      <c r="AC42" t="n">
+        <v>-7.326426366769332</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4396,13 +4524,13 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.844110762107021</v>
+        <v>3.592</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.09607005029372395</v>
+        <v>-0.2533275950479825</v>
       </c>
       <c r="S43" t="n">
-        <v>0.01002758432126026</v>
+        <v>0.2580522247206228</v>
       </c>
       <c r="T43" t="n">
         <v>37.035</v>
@@ -4433,6 +4561,9 @@
       <c r="AB43" t="n">
         <v>5.489431708794079</v>
       </c>
+      <c r="AC43" t="n">
+        <v>-9.958094783816009</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4488,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.776294973613721</v>
+        <v>3.469</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.08822851662189879</v>
+        <v>0.02030229350497881</v>
       </c>
       <c r="S44" t="n">
-        <v>0.01136747508890937</v>
+        <v>0.2141756848695081</v>
       </c>
       <c r="T44" t="n">
         <v>37.035</v>
@@ -4525,6 +4656,9 @@
       <c r="AB44" t="n">
         <v>6.275959303859973</v>
       </c>
+      <c r="AC44" t="n">
+        <v>-9.288696433079481</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4580,13 +4714,13 @@
         <v>0.04833087383949691</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.702879250634389</v>
+        <v>3.687</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.07746959573723755</v>
+        <v>0.04035924257097845</v>
       </c>
       <c r="S45" t="n">
-        <v>0.01297736076564769</v>
+        <v>-0.1026180170929935</v>
       </c>
       <c r="T45" t="n">
         <v>37.065</v>
@@ -4617,6 +4751,9 @@
       <c r="AB45" t="n">
         <v>6.428786065227143</v>
       </c>
+      <c r="AC45" t="n">
+        <v>-6.640064437400662</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4672,13 +4809,13 @@
         <v>0.08139622242857786</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.658697095819752</v>
+        <v>3.627084274946381</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.06935818065271815</v>
+        <v>-0.07228700803995936</v>
       </c>
       <c r="S46" t="n">
-        <v>0.01406692586266444</v>
+        <v>-0.09556881808354613</v>
       </c>
       <c r="T46" t="n">
         <v>36.98999999999999</v>
@@ -4709,6 +4846,9 @@
       <c r="AB46" t="n">
         <v>4.711677287100157</v>
       </c>
+      <c r="AC46" t="n">
+        <v>-4.469475518432679</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4764,13 +4904,13 @@
         <v>0.03270764869073212</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.581432186854011</v>
+        <v>3.61</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.04980168904584292</v>
+        <v>0.05807799827585247</v>
       </c>
       <c r="S47" t="n">
-        <v>0.01623739009660047</v>
+        <v>0.04585309101989664</v>
       </c>
       <c r="T47" t="n">
         <v>30</v>
@@ -4801,6 +4941,9 @@
       <c r="AB47" t="n">
         <v>0.5267164103912014</v>
       </c>
+      <c r="AC47" t="n">
+        <v>-0.5296706066929328</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4856,13 +4999,13 @@
         <v>-0.03311824047486412</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.519108708753577</v>
+        <v>3.882</v>
       </c>
       <c r="R48" t="n">
-        <v>-0.01900331605574701</v>
+        <v>0.005328788642799065</v>
       </c>
       <c r="S48" t="n">
-        <v>0.01893889925203274</v>
+        <v>-0.04017829336138937</v>
       </c>
       <c r="T48" t="n">
         <v>30.015</v>
@@ -4893,6 +5036,9 @@
       <c r="AB48" t="n">
         <v>-0.4676556280473815</v>
       </c>
+      <c r="AC48" t="n">
+        <v>3.13832222171261</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4948,13 +5094,13 @@
         <v>0.03095467918531082</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.521409515630263</v>
+        <v>3.509</v>
       </c>
       <c r="R49" t="n">
-        <v>0.02451419553391787</v>
+        <v>-0.1054087315502568</v>
       </c>
       <c r="S49" t="n">
-        <v>0.02220594544328378</v>
+        <v>0.02514730115285493</v>
       </c>
       <c r="T49" t="n">
         <v>30</v>
@@ -4985,6 +5131,9 @@
       <c r="AB49" t="n">
         <v>0.1466294976475842</v>
       </c>
+      <c r="AC49" t="n">
+        <v>5.191306641151922</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5040,13 +5189,13 @@
         <v>0.182774664945801</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.614709781014519</v>
+        <v>3.432</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0720375657570913</v>
+        <v>0.09127498538866197</v>
       </c>
       <c r="S50" t="n">
-        <v>0.02527151967257393</v>
+        <v>0.06128258130735412</v>
       </c>
       <c r="T50" t="n">
         <v>30</v>
@@ -5077,6 +5226,9 @@
       <c r="AB50" t="n">
         <v>0.589360073971491</v>
       </c>
+      <c r="AC50" t="n">
+        <v>4.466439627179489</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5132,13 +5284,13 @@
         <v>0.3299149962450657</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.801428699717416</v>
+        <v>3.851</v>
       </c>
       <c r="R51" t="n">
-        <v>0.123717550159157</v>
+        <v>0.1404949712643679</v>
       </c>
       <c r="S51" t="n">
-        <v>0.02759689768479523</v>
+        <v>-0.04176749301902744</v>
       </c>
       <c r="T51" t="n">
         <v>30.015</v>
@@ -5169,6 +5321,9 @@
       <c r="AB51" t="n">
         <v>0.2349656118969819</v>
       </c>
+      <c r="AC51" t="n">
+        <v>1.050758959383074</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5224,13 +5379,13 @@
         <v>0.3933788333966759</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.949365425797802</v>
+        <v>3.956</v>
       </c>
       <c r="R52" t="n">
-        <v>0.1536638112415663</v>
+        <v>0.05638002873563153</v>
       </c>
       <c r="S52" t="n">
-        <v>0.028552341844722</v>
+        <v>-0.1159480242223528</v>
       </c>
       <c r="T52" t="n">
         <v>30</v>
@@ -5261,6 +5416,9 @@
       <c r="AB52" t="n">
         <v>-0.1830436921785885</v>
       </c>
+      <c r="AC52" t="n">
+        <v>-1.537696032057543</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5316,13 +5474,13 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.806430666043341</v>
+        <v>5.058</v>
       </c>
       <c r="R53" t="n">
-        <v>0.2875367713465891</v>
+        <v>0.005007829627310389</v>
       </c>
       <c r="S53" t="n">
-        <v>-2.343504235530203e-07</v>
+        <v>-0.05355707639366866</v>
       </c>
       <c r="T53" t="n">
         <v>37.02</v>
@@ -5353,6 +5511,9 @@
       <c r="AB53" t="n">
         <v>-0.09669831485755673</v>
       </c>
+      <c r="AC53" t="n">
+        <v>12.17244300907387</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5408,13 +5569,13 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.001807059351691</v>
+        <v>5.058</v>
       </c>
       <c r="R54" t="n">
-        <v>0.2842965749217532</v>
+        <v>-0.005007829627309501</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.009483267380803226</v>
+        <v>0.0242429517460007</v>
       </c>
       <c r="T54" t="n">
         <v>36.98999999999999</v>
@@ -5445,6 +5606,9 @@
       <c r="AB54" t="n">
         <v>0.08782427960950868</v>
       </c>
+      <c r="AC54" t="n">
+        <v>9.898165849403114</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5500,13 +5664,13 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.293048618669806</v>
+        <v>5.045</v>
       </c>
       <c r="R55" t="n">
-        <v>0.2670880972118379</v>
+        <v>0.08082844574780346</v>
       </c>
       <c r="S55" t="n">
-        <v>-0.03278734958261803</v>
+        <v>0.02363734514945008</v>
       </c>
       <c r="T55" t="n">
         <v>37.035</v>
@@ -5537,6 +5701,9 @@
       <c r="AB55" t="n">
         <v>0.5093672732434701</v>
       </c>
+      <c r="AC55" t="n">
+        <v>5.339030585263112</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5592,13 +5759,13 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.406104859877487</v>
+        <v>5.097</v>
       </c>
       <c r="R56" t="n">
-        <v>0.2499483712038701</v>
+        <v>0.08027164685908428</v>
       </c>
       <c r="S56" t="n">
-        <v>-0.04822975515647004</v>
+        <v>-0.05728058367639445</v>
       </c>
       <c r="T56" t="n">
         <v>36.98999999999999</v>
@@ -5629,6 +5796,9 @@
       <c r="AB56" t="n">
         <v>0.7687689691352048</v>
       </c>
+      <c r="AC56" t="n">
+        <v>3.626113930846518</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5684,13 +5854,13 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.528498972348228</v>
+        <v>5.114</v>
       </c>
       <c r="R57" t="n">
-        <v>0.2196846924617812</v>
+        <v>0.01618191433104244</v>
       </c>
       <c r="S57" t="n">
-        <v>-0.06610936805900039</v>
+        <v>0.9694324918589451</v>
       </c>
       <c r="T57" t="n">
         <v>36.98999999999999</v>
@@ -5721,6 +5891,9 @@
       <c r="AB57" t="n">
         <v>1.126470717633211</v>
       </c>
+      <c r="AC57" t="n">
+        <v>1.863239611772474</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5776,13 +5949,13 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.630015284001658</v>
+        <v>5.114</v>
       </c>
       <c r="R58" t="n">
-        <v>0.1829842797334722</v>
+        <v>1.030000000000004</v>
       </c>
       <c r="S58" t="n">
-        <v>-0.07692676905678833</v>
+        <v>1.096818085668958</v>
       </c>
       <c r="T58" t="n">
         <v>37.035</v>
@@ -5813,6 +5986,9 @@
       <c r="AB58" t="n">
         <v>1.517922212740104</v>
       </c>
+      <c r="AC58" t="n">
+        <v>-0.9177531969335253</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5868,13 +6044,13 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.7114832520817</v>
+        <v>6.144</v>
       </c>
       <c r="R59" t="n">
-        <v>0.1427579234049929</v>
+        <v>1.113000000000004</v>
       </c>
       <c r="S59" t="n">
-        <v>-0.07991444686084206</v>
+        <v>-0.872661601402685</v>
       </c>
       <c r="T59" t="n">
         <v>37.02</v>
@@ -5905,6 +6081,9 @@
       <c r="AB59" t="n">
         <v>1.95830483351225</v>
       </c>
+      <c r="AC59" t="n">
+        <v>-4.604571759336294</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5960,13 +6139,13 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.77277320740665</v>
+        <v>6.227</v>
       </c>
       <c r="R60" t="n">
-        <v>0.1030698328726301</v>
+        <v>0.1573383985973127</v>
       </c>
       <c r="S60" t="n">
-        <v>-0.07783449911248744</v>
+        <v>-1.036109384352134</v>
       </c>
       <c r="T60" t="n">
         <v>37.02</v>
@@ -5997,6 +6176,9 @@
       <c r="AB60" t="n">
         <v>2.450226494649462</v>
       </c>
+      <c r="AC60" t="n">
+        <v>-6.895550874234955</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6052,13 +6234,13 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.813474751400262</v>
+        <v>6.299</v>
       </c>
       <c r="R61" t="n">
-        <v>0.06617013303594588</v>
+        <v>0.06547154133776489</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.07501737863600764</v>
+        <v>-0.235805051365734</v>
       </c>
       <c r="T61" t="n">
         <v>37.029</v>
@@ -6089,6 +6271,9 @@
       <c r="AB61" t="n">
         <v>2.982963814489862</v>
       </c>
+      <c r="AC61" t="n">
+        <v>-6.40253013626112</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6144,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.842795389819284</v>
+        <v>6.218</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0008780728511519342</v>
+        <v>-0.2233997155049785</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.0702078500893646</v>
+        <v>-0.1710992062624362</v>
       </c>
       <c r="T62" t="n">
         <v>37.035</v>
@@ -6181,6 +6366,9 @@
       <c r="AB62" t="n">
         <v>4.120490689294455</v>
       </c>
+      <c r="AC62" t="n">
+        <v>-5.991770965222028</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6236,13 +6424,13 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.811841088040446</v>
+        <v>5.872</v>
       </c>
       <c r="R63" t="n">
-        <v>-0.06347400438597894</v>
+        <v>-0.2356588021778583</v>
       </c>
       <c r="S63" t="n">
-        <v>-0.0612255235871807</v>
+        <v>0.05445146388706981</v>
       </c>
       <c r="T63" t="n">
         <v>37.185</v>
@@ -6273,6 +6461,9 @@
       <c r="AB63" t="n">
         <v>5.538164584872975</v>
       </c>
+      <c r="AC63" t="n">
+        <v>-8.217293743558002</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6328,13 +6519,13 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.771974999313429</v>
+        <v>5.788</v>
       </c>
       <c r="R64" t="n">
-        <v>-0.09237268589444225</v>
+        <v>-0.1907078687480084</v>
       </c>
       <c r="S64" t="n">
-        <v>-0.05153777455815977</v>
+        <v>-0.09481392400159955</v>
       </c>
       <c r="T64" t="n">
         <v>37.005</v>
@@ -6365,6 +6556,9 @@
       <c r="AB64" t="n">
         <v>6.495330179033808</v>
       </c>
+      <c r="AC64" t="n">
+        <v>-8.86681881395247</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6420,13 +6614,13 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.692789963252237</v>
+        <v>5.628</v>
       </c>
       <c r="R65" t="n">
-        <v>-0.122878102627646</v>
+        <v>-0.4484020127838981</v>
       </c>
       <c r="S65" t="n">
-        <v>-0.0338080600699498</v>
+        <v>-0.1720994288834547</v>
       </c>
       <c r="T65" t="n">
         <v>36.885</v>
@@ -6457,6 +6651,9 @@
       <c r="AB65" t="n">
         <v>7.935472143654233</v>
       </c>
+      <c r="AC65" t="n">
+        <v>-8.768139622603149</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6512,13 +6709,13 @@
         <v>0.03075634099896449</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.608034087365832</v>
+        <v>5.218</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.1393883124413593</v>
+        <v>-0.4524711237553349</v>
       </c>
       <c r="S66" t="n">
-        <v>-0.01690730456396101</v>
+        <v>0.2920958380403781</v>
       </c>
       <c r="T66" t="n">
         <v>37.065</v>
@@ -6549,6 +6746,9 @@
       <c r="AB66" t="n">
         <v>7.656129859726126</v>
       </c>
+      <c r="AC66" t="n">
+        <v>-7.728296769790107</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6604,13 +6804,13 @@
         <v>0.05495921041486124</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.5187375741891</v>
+        <v>5.056</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.1443135967461986</v>
+        <v>-0.09310197674989018</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0002619043465117918</v>
+        <v>0.4418284352312768</v>
       </c>
       <c r="T67" t="n">
         <v>37.05</v>
@@ -6641,6 +6841,9 @@
       <c r="AB67" t="n">
         <v>5.237237488835593</v>
       </c>
+      <c r="AC67" t="n">
+        <v>-5.774102480816334</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6696,13 +6899,13 @@
         <v>0.008651385330049385</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.379979298695361</v>
+        <v>5.223</v>
       </c>
       <c r="R68" t="n">
-        <v>-0.1315608109754156</v>
+        <v>0.1204419051471333</v>
       </c>
       <c r="S68" t="n">
-        <v>0.02468276755472088</v>
+        <v>0.1014219077559285</v>
       </c>
       <c r="T68" t="n">
         <v>32.985</v>
@@ -6733,6 +6936,9 @@
       <c r="AB68" t="n">
         <v>1.854368830795771</v>
       </c>
+      <c r="AC68" t="n">
+        <v>-1.402530114214224</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6788,13 +6994,13 @@
         <v>-0.02156544142506893</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.250260856442693</v>
+        <v>5.29</v>
       </c>
       <c r="R69" t="n">
-        <v>-0.09002716773481589</v>
+        <v>0.08244304875452446</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0518657041594046</v>
+        <v>-0.007424586209027598</v>
       </c>
       <c r="T69" t="n">
         <v>33</v>
@@ -6825,6 +7031,9 @@
       <c r="AB69" t="n">
         <v>0.4349746584691095</v>
       </c>
+      <c r="AC69" t="n">
+        <v>3.6634139576301</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6880,13 +7089,13 @@
         <v>0.0002592121117928302</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.18832900702664</v>
+        <v>5.384</v>
       </c>
       <c r="R70" t="n">
-        <v>-0.0304469026530354</v>
+        <v>0.09699014778325177</v>
       </c>
       <c r="S70" t="n">
-        <v>0.076460223068408</v>
+        <v>0.00233882684867398</v>
       </c>
       <c r="T70" t="n">
         <v>33</v>
@@ -6917,6 +7126,9 @@
       <c r="AB70" t="n">
         <v>-0.1601039334494191</v>
       </c>
+      <c r="AC70" t="n">
+        <v>6.856841057740805</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6972,13 +7184,13 @@
         <v>0.02377783591582186</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.196355658258678</v>
+        <v>5.477</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0595392755223374</v>
+        <v>0.08513538461538417</v>
       </c>
       <c r="S71" t="n">
-        <v>0.1023999495136532</v>
+        <v>-0.1250652767269084</v>
       </c>
       <c r="T71" t="n">
         <v>33</v>
@@ -7009,6 +7221,9 @@
       <c r="AB71" t="n">
         <v>-0.5703054782838444</v>
       </c>
+      <c r="AC71" t="n">
+        <v>8.799973865714499</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7064,13 +7279,13 @@
         <v>0.04237510135172184</v>
       </c>
       <c r="Q72" t="n">
-        <v>5.32131232830413</v>
+        <v>5.56</v>
       </c>
       <c r="R72" t="n">
-        <v>0.1850414941355272</v>
+        <v>-0.1832171151129178</v>
       </c>
       <c r="S72" t="n">
-        <v>0.1229116929752026</v>
+        <v>-0.3754960165602028</v>
       </c>
       <c r="T72" t="n">
         <v>32.97000000000001</v>
@@ -7101,6 +7316,9 @@
       <c r="AB72" t="n">
         <v>-0.7446511251075507</v>
       </c>
+      <c r="AC72" t="n">
+        <v>9.185766247945754</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7156,13 +7374,13 @@
         <v>0.05281889853409094</v>
       </c>
       <c r="Q73" t="n">
-        <v>5.534965269572661</v>
+        <v>5.211012191461332</v>
       </c>
       <c r="R73" t="n">
-        <v>0.2987010143969968</v>
+        <v>-0.6069439608236866</v>
       </c>
       <c r="S73" t="n">
-        <v>0.1344306170507666</v>
+        <v>-0.5838855208981423</v>
       </c>
       <c r="T73" t="n">
         <v>32.925</v>
@@ -7193,6 +7411,9 @@
       <c r="AB73" t="n">
         <v>-0.763681692843301</v>
       </c>
+      <c r="AC73" t="n">
+        <v>8.711532299826835</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7248,13 +7469,13 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>5.594268793151639</v>
+        <v>5.774</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3626917571026627</v>
+        <v>0.000231222262113473</v>
       </c>
       <c r="S74" t="n">
-        <v>-0.1108985914738323</v>
+        <v>0.07412523885196148</v>
       </c>
       <c r="T74" t="n">
         <v>36.98999999999999</v>
@@ -7285,6 +7506,9 @@
       <c r="AB74" t="n">
         <v>0.0306273210347785</v>
       </c>
+      <c r="AC74" t="n">
+        <v>8.425172889342988</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7340,13 +7564,13 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.816402512877722</v>
+        <v>5.792</v>
       </c>
       <c r="R75" t="n">
-        <v>0.2874557152663608</v>
+        <v>0.0524517045671562</v>
       </c>
       <c r="S75" t="n">
-        <v>-0.1093044578031485</v>
+        <v>0.07871519716279766</v>
       </c>
       <c r="T75" t="n">
         <v>36.98999999999999</v>
@@ -7377,6 +7601,9 @@
       <c r="AB75" t="n">
         <v>0.144104797906225</v>
       </c>
+      <c r="AC75" t="n">
+        <v>7.664821675792473</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7432,13 +7659,13 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.054658104665411</v>
+        <v>5.887</v>
       </c>
       <c r="R76" t="n">
-        <v>0.1757532734693896</v>
+        <v>0.1373768797953101</v>
       </c>
       <c r="S76" t="n">
-        <v>-0.1054197622367088</v>
+        <v>0.04052034512236188</v>
       </c>
       <c r="T76" t="n">
         <v>37.02</v>
@@ -7469,6 +7696,9 @@
       <c r="AB76" t="n">
         <v>0.4461081831462915</v>
       </c>
+      <c r="AC76" t="n">
+        <v>5.82229073132288</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7524,13 +7754,13 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.120856550548019</v>
+        <v>5.954787611256691</v>
       </c>
       <c r="R77" t="n">
-        <v>0.1305582736750548</v>
+        <v>0.1473642582657568</v>
       </c>
       <c r="S77" t="n">
-        <v>-0.1027789841525424</v>
+        <v>0.0546761396168505</v>
       </c>
       <c r="T77" t="n">
         <v>37.005</v>
@@ -7561,6 +7791,9 @@
       <c r="AB77" t="n">
         <v>0.6587208509243141</v>
       </c>
+      <c r="AC77" t="n">
+        <v>4.513964766559551</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7616,13 +7849,13 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>6.170623117618923</v>
+        <v>6.019</v>
       </c>
       <c r="R78" t="n">
-        <v>0.08335722252418609</v>
+        <v>0.1887750599760087</v>
       </c>
       <c r="S78" t="n">
-        <v>-0.09987685457285715</v>
+        <v>0.03404157487248477</v>
       </c>
       <c r="T78" t="n">
         <v>37.02</v>
@@ -7653,6 +7886,9 @@
       <c r="AB78" t="n">
         <v>0.9477138696893034</v>
       </c>
+      <c r="AC78" t="n">
+        <v>2.585944734935426</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7708,13 +7944,13 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>6.201375647337044</v>
+        <v>6.156</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02924705354147417</v>
+        <v>0.1720432900432893</v>
       </c>
       <c r="S79" t="n">
-        <v>-0.09688606335991951</v>
+        <v>-0.03548411332043327</v>
       </c>
       <c r="T79" t="n">
         <v>37.005</v>
@@ -7745,6 +7981,9 @@
       <c r="AB79" t="n">
         <v>1.35242708084327</v>
       </c>
+      <c r="AC79" t="n">
+        <v>-0.09741734014646664</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7800,13 +8039,13 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>6.203877975537276</v>
+        <v>6.207</v>
       </c>
       <c r="R80" t="n">
-        <v>-0.01851594992794325</v>
+        <v>0.1519999999999992</v>
       </c>
       <c r="S80" t="n">
-        <v>-0.09411347007976803</v>
+        <v>-0.04329869623849711</v>
       </c>
       <c r="T80" t="n">
         <v>36.98999999999999</v>
@@ -7837,6 +8076,9 @@
       <c r="AB80" t="n">
         <v>1.783465136302094</v>
       </c>
+      <c r="AC80" t="n">
+        <v>-2.295027460708333</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7892,13 +8134,13 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>6.182859697409101</v>
+        <v>6.308</v>
       </c>
       <c r="R81" t="n">
-        <v>-0.06486641653829395</v>
+        <v>0.1287445938047922</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.09113027852734094</v>
+        <v>-0.1750837143741194</v>
       </c>
       <c r="T81" t="n">
         <v>36.96</v>
@@ -7929,6 +8171,9 @@
       <c r="AB81" t="n">
         <v>2.280455504978595</v>
       </c>
+      <c r="AC81" t="n">
+        <v>-3.621252928313545</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7984,13 +8229,13 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>6.140840978028306</v>
+        <v>6.336</v>
       </c>
       <c r="R82" t="n">
-        <v>-0.108178873050333</v>
+        <v>-0.01595131845841768</v>
       </c>
       <c r="S82" t="n">
-        <v>-0.08820526302500195</v>
+        <v>-0.2770472494445837</v>
       </c>
       <c r="T82" t="n">
         <v>37.065</v>
@@ -8021,6 +8266,9 @@
       <c r="AB82" t="n">
         <v>2.833999305046683</v>
       </c>
+      <c r="AC82" t="n">
+        <v>-4.026552198396986</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8076,13 +8324,13 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>6.017133429222349</v>
+        <v>6.212</v>
       </c>
       <c r="R83" t="n">
-        <v>-0.1810505487905112</v>
+        <v>-0.2180715421303661</v>
       </c>
       <c r="S83" t="n">
-        <v>-0.08292311176317639</v>
+        <v>-0.156834786104562</v>
       </c>
       <c r="T83" t="n">
         <v>36.96</v>
@@ -8113,6 +8361,9 @@
       <c r="AB83" t="n">
         <v>3.986096028023777</v>
       </c>
+      <c r="AC83" t="n">
+        <v>-4.840680738678863</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8168,13 +8419,13 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.794303755634638</v>
+        <v>5.909</v>
       </c>
       <c r="R84" t="n">
-        <v>-0.2606698117765553</v>
+        <v>-0.2796666666666656</v>
       </c>
       <c r="S84" t="n">
-        <v>-0.06476490425365738</v>
+        <v>0.07306143896646755</v>
       </c>
       <c r="T84" t="n">
         <v>37.125</v>
@@ -8205,6 +8456,9 @@
       <c r="AB84" t="n">
         <v>5.584222489339185</v>
       </c>
+      <c r="AC84" t="n">
+        <v>-7.428230802788781</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8260,13 +8514,13 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.654508815199148</v>
+        <v>5.775</v>
       </c>
       <c r="R85" t="n">
-        <v>-0.2893386742202875</v>
+        <v>-0.2094718063077394</v>
       </c>
       <c r="S85" t="n">
-        <v>-0.04110722942485306</v>
+        <v>-0.1780025485823539</v>
       </c>
       <c r="T85" t="n">
         <v>37.035</v>
@@ -8297,6 +8551,9 @@
       <c r="AB85" t="n">
         <v>6.30836263216888</v>
       </c>
+      <c r="AC85" t="n">
+        <v>-8.581286794730328</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8352,13 +8609,13 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.437135254839679</v>
+        <v>5.685</v>
       </c>
       <c r="R86" t="n">
-        <v>-0.3021265296912281</v>
+        <v>-0.6640999138673562</v>
       </c>
       <c r="S86" t="n">
-        <v>0.005928860344370734</v>
+        <v>-0.4940367105982512</v>
       </c>
       <c r="T86" t="n">
         <v>37.035</v>
@@ -8389,6 +8646,9 @@
       <c r="AB86" t="n">
         <v>6.872100782227083</v>
       </c>
+      <c r="AC86" t="n">
+        <v>-8.85434811230456</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8444,13 +8704,13 @@
         <v>0.01986596221612337</v>
       </c>
       <c r="Q87" t="n">
-        <v>5.246451917529346</v>
+        <v>4.963</v>
       </c>
       <c r="R87" t="n">
-        <v>-0.2850664235075149</v>
+        <v>-0.8984496124031018</v>
       </c>
       <c r="S87" t="n">
-        <v>0.04991187955432078</v>
+        <v>0.2924987055564149</v>
       </c>
       <c r="T87" t="n">
         <v>36.98999999999999</v>
@@ -8481,6 +8741,9 @@
       <c r="AB87" t="n">
         <v>6.58915118392846</v>
       </c>
+      <c r="AC87" t="n">
+        <v>-7.79506293207429</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8536,13 +8799,13 @@
         <v>0.04051199681788326</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.055139914116312</v>
+        <v>4.515</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.2306644298958873</v>
+        <v>-0.1515413802843444</v>
       </c>
       <c r="S88" t="n">
-        <v>0.09637627062333105</v>
+        <v>0.7132157299787971</v>
       </c>
       <c r="T88" t="n">
         <v>36.96</v>
@@ -8573,6 +8836,9 @@
       <c r="AB88" t="n">
         <v>4.640789317347886</v>
       </c>
+      <c r="AC88" t="n">
+        <v>-5.081734837403502</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8628,13 +8894,13 @@
         <v>0.01711461552917037</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.893257105708582</v>
+        <v>4.88</v>
       </c>
       <c r="R89" t="n">
-        <v>-0.1256881547718787</v>
+        <v>0.121785587294063</v>
       </c>
       <c r="S89" t="n">
-        <v>0.1249147605818942</v>
+        <v>0.229667085832981</v>
       </c>
       <c r="T89" t="n">
         <v>36.945</v>
@@ -8665,6 +8931,9 @@
       <c r="AB89" t="n">
         <v>1.884927092948308</v>
       </c>
+      <c r="AC89" t="n">
+        <v>-0.2044999054645352</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8720,13 +8989,13 @@
         <v>-0.01098395222704836</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.840304718125667</v>
+        <v>4.596</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01700711652374709</v>
+        <v>0.2547547780362032</v>
       </c>
       <c r="S90" t="n">
-        <v>0.1137135168665147</v>
+        <v>0.113795308497991</v>
       </c>
       <c r="T90" t="n">
         <v>36.96</v>
@@ -8757,6 +9026,9 @@
       <c r="AB90" t="n">
         <v>0.04924267899408696</v>
       </c>
+      <c r="AC90" t="n">
+        <v>6.298504437124906</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8812,13 +9084,13 @@
         <v>-0.01312461346510742</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.912085832008034</v>
+        <v>5.278</v>
       </c>
       <c r="R91" t="n">
-        <v>0.113330229929598</v>
+        <v>0.3587375803623618</v>
       </c>
       <c r="S91" t="n">
-        <v>0.08131192069080476</v>
+        <v>-0.112727149228043</v>
       </c>
       <c r="T91" t="n">
         <v>36.98999999999999</v>
@@ -8849,6 +9121,9 @@
       <c r="AB91" t="n">
         <v>-0.797861052096557</v>
       </c>
+      <c r="AC91" t="n">
+        <v>10.80538107476989</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8904,13 +9179,13 @@
         <v>-0.01527016551214571</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.065837343203529</v>
+        <v>5.278</v>
       </c>
       <c r="R92" t="n">
-        <v>0.1756773098781128</v>
+        <v>0.01811846689895535</v>
       </c>
       <c r="S92" t="n">
-        <v>0.04460178470623562</v>
+        <v>-0.1835944771732361</v>
       </c>
       <c r="T92" t="n">
         <v>36.93</v>
@@ -8941,6 +9216,9 @@
       <c r="AB92" t="n">
         <v>-1.11697088199055</v>
       </c>
+      <c r="AC92" t="n">
+        <v>13.88204385935657</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8996,13 +9274,13 @@
         <v>-0.01693171964649547</v>
       </c>
       <c r="Q93" t="n">
-        <v>5.274471711623132</v>
+        <v>5.317</v>
       </c>
       <c r="R93" t="n">
-        <v>0.2029449958150473</v>
+        <v>-0.001536072623029572</v>
       </c>
       <c r="S93" t="n">
-        <v>0.01617279446015786</v>
+        <v>-0.04882468907366223</v>
       </c>
       <c r="T93" t="n">
         <v>36.96</v>
@@ -9033,6 +9311,9 @@
       <c r="AB93" t="n">
         <v>-0.8705332084222246</v>
       </c>
+      <c r="AC93" t="n">
+        <v>15.28262305416456</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9088,13 +9369,13 @@
         <v>-0.01787689785680881</v>
       </c>
       <c r="Q94" t="n">
-        <v>5.453394436872836</v>
+        <v>5.288</v>
       </c>
       <c r="R94" t="n">
-        <v>0.2099536009150373</v>
+        <v>-0.06538700430004596</v>
       </c>
       <c r="S94" t="n">
-        <v>9.096167422062429e-07</v>
+        <v>-0.09852361479637552</v>
       </c>
       <c r="T94" t="n">
         <v>36.975</v>
@@ -9125,6 +9406,9 @@
       <c r="AB94" t="n">
         <v>-0.4395382734757554</v>
       </c>
+      <c r="AC94" t="n">
+        <v>15.58170267730281</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9180,13 +9464,13 @@
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.541676718541927</v>
+        <v>5.177</v>
       </c>
       <c r="R95" t="n">
-        <v>-0.144313804226524</v>
+        <v>0.05474509803921723</v>
       </c>
       <c r="S95" t="n">
-        <v>0.008217091899568707</v>
+        <v>0.2060181660899626</v>
       </c>
       <c r="T95" t="n">
         <v>36.93</v>
@@ -9217,6 +9501,9 @@
       <c r="AB95" t="n">
         <v>0.3192073006243564</v>
       </c>
+      <c r="AC95" t="n">
+        <v>2.932811325886003</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9272,13 +9559,13 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.435730392345268</v>
+        <v>5.235</v>
       </c>
       <c r="R96" t="n">
-        <v>-0.1382097322979021</v>
+        <v>0.09992156862745105</v>
       </c>
       <c r="S96" t="n">
-        <v>0.008060433243422871</v>
+        <v>-0.08554757785467246</v>
       </c>
       <c r="T96" t="n">
         <v>37.005</v>
@@ -9309,6 +9596,9 @@
       <c r="AB96" t="n">
         <v>0.186872330004158</v>
       </c>
+      <c r="AC96" t="n">
+        <v>2.499190168459612</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9364,13 +9654,13 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.34539918471811</v>
+        <v>5.315</v>
       </c>
       <c r="R97" t="n">
-        <v>-0.132882527515219</v>
+        <v>-0.04349999999999987</v>
       </c>
       <c r="S97" t="n">
-        <v>0.007845810884507989</v>
+        <v>-0.1070036764705886</v>
       </c>
       <c r="T97" t="n">
         <v>36.98999999999999</v>
@@ -9401,6 +9691,9 @@
       <c r="AB97" t="n">
         <v>0.2380631536105936</v>
       </c>
+      <c r="AC97" t="n">
+        <v>1.9698216176519</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9456,13 +9749,13 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.258553688991642</v>
+        <v>5.177</v>
       </c>
       <c r="R98" t="n">
-        <v>-0.1277486511185582</v>
+        <v>-0.04274999999999984</v>
       </c>
       <c r="S98" t="n">
-        <v>0.007552859197519232</v>
+        <v>0.1664500000000016</v>
       </c>
       <c r="T98" t="n">
         <v>36.98999999999999</v>
@@ -9493,6 +9786,9 @@
       <c r="AB98" t="n">
         <v>0.637429542660837</v>
       </c>
+      <c r="AC98" t="n">
+        <v>1.135271034255885</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9548,13 +9844,13 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.175067649893364</v>
+        <v>5.258</v>
       </c>
       <c r="R99" t="n">
-        <v>-0.1228120485851933</v>
+        <v>0.1784333333333348</v>
       </c>
       <c r="S99" t="n">
-        <v>0.007259184173028121</v>
+        <v>0.17003823987539</v>
       </c>
       <c r="T99" t="n">
         <v>37.035</v>
@@ -9585,6 +9881,9 @@
       <c r="AB99" t="n">
         <v>1.356956153093132</v>
       </c>
+      <c r="AC99" t="n">
+        <v>-0.1974170981460426</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9640,13 +9939,13 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.075241994887186</v>
+        <v>5.466</v>
       </c>
       <c r="R100" t="n">
-        <v>-0.1169145197191481</v>
+        <v>0.1516560747663549</v>
       </c>
       <c r="S100" t="n">
-        <v>0.006902806788030812</v>
+        <v>-0.1467484784194996</v>
       </c>
       <c r="T100" t="n">
         <v>37.005</v>
@@ -9677,6 +9976,9 @@
       <c r="AB100" t="n">
         <v>2.395519514089109</v>
       </c>
+      <c r="AC100" t="n">
+        <v>-3.52235470021624</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9732,13 +10034,13 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.967288197544187</v>
+        <v>5.504</v>
       </c>
       <c r="R101" t="n">
-        <v>-0.1105455420333938</v>
+        <v>-0.1118838566268407</v>
       </c>
       <c r="S101" t="n">
-        <v>0.006516649809763547</v>
+        <v>-0.2181847350071632</v>
       </c>
       <c r="T101" t="n">
         <v>36.975</v>
@@ -9769,6 +10071,9 @@
       <c r="AB101" t="n">
         <v>3.491625453038942</v>
       </c>
+      <c r="AC101" t="n">
+        <v>-6.945607737013958</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9824,13 +10129,13 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.858262223070425</v>
+        <v>5.225</v>
       </c>
       <c r="R102" t="n">
-        <v>-0.1041243240908107</v>
+        <v>-0.2692667288147144</v>
       </c>
       <c r="S102" t="n">
-        <v>0.006079016588457872</v>
+        <v>-0.06858709667021634</v>
       </c>
       <c r="T102" t="n">
         <v>37.005</v>
@@ -9861,6 +10166,9 @@
       <c r="AB102" t="n">
         <v>4.692923317443761</v>
       </c>
+      <c r="AC102" t="n">
+        <v>-11.6769836732051</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9916,13 +10224,13 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.786876205652505</v>
+        <v>5.039</v>
       </c>
       <c r="R103" t="n">
-        <v>-0.09998320761486879</v>
+        <v>-0.2757245421245422</v>
       </c>
       <c r="S103" t="n">
-        <v>0.00576929102457906</v>
+        <v>-0.009668751739534187</v>
       </c>
       <c r="T103" t="n">
         <v>36.98999999999999</v>
@@ -9953,6 +10261,9 @@
       <c r="AB103" t="n">
         <v>5.80969213096696</v>
       </c>
+      <c r="AC103" t="n">
+        <v>-15.77211868686475</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10008,13 +10319,13 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.666354377535423</v>
+        <v>4.672</v>
       </c>
       <c r="R104" t="n">
-        <v>-0.09309880288623873</v>
+        <v>-0.2887999999999997</v>
       </c>
       <c r="S104" t="n">
-        <v>0.005280974478298797</v>
+        <v>-0.05952170496170292</v>
       </c>
       <c r="T104" t="n">
         <v>37.065</v>
@@ -10045,6 +10356,9 @@
       <c r="AB104" t="n">
         <v>8.124078415313139</v>
       </c>
+      <c r="AC104" t="n">
+        <v>-16.86117230784222</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10100,13 +10414,13 @@
         <v>0.01348493027138882</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.590615741578795</v>
+        <v>4.434</v>
       </c>
       <c r="R105" t="n">
-        <v>-0.08882385154577044</v>
+        <v>-0.3656577200577171</v>
       </c>
       <c r="S105" t="n">
-        <v>0.004894750171542589</v>
+        <v>0.0377313553978475</v>
       </c>
       <c r="T105" t="n">
         <v>36.78</v>
@@ -10137,6 +10451,9 @@
       <c r="AB105" t="n">
         <v>7.729238052345338</v>
       </c>
+      <c r="AC105" t="n">
+        <v>-12.65852298479927</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10192,13 +10509,13 @@
         <v>0.02125759829891417</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.551146198702528</v>
+        <v>4.25</v>
       </c>
       <c r="R106" t="n">
-        <v>-0.08667836548777197</v>
+        <v>-0.3170981795981779</v>
       </c>
       <c r="S106" t="n">
-        <v>0.004669106070178772</v>
+        <v>0.1391127443984561</v>
       </c>
       <c r="T106" t="n">
         <v>36.825</v>
@@ -10229,6 +10546,9 @@
       <c r="AB106" t="n">
         <v>5.833247136914298</v>
       </c>
+      <c r="AC106" t="n">
+        <v>-8.473991864042345</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10284,13 +10604,13 @@
         <v>0.01325311210845598</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.4436849666609</v>
+        <v>4.179</v>
       </c>
       <c r="R107" t="n">
-        <v>-0.08104735890804182</v>
+        <v>-0.0243722943722946</v>
       </c>
       <c r="S107" t="n">
-        <v>0.004153435985263555</v>
+        <v>0.1120958962498602</v>
       </c>
       <c r="T107" t="n">
         <v>29.01</v>
@@ -10321,6 +10641,9 @@
       <c r="AB107" t="n">
         <v>0.7142044802905348</v>
       </c>
+      <c r="AC107" t="n">
+        <v>1.330188487440613</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10376,13 +10699,13 @@
         <v>0.003937378394383906</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.36089504837672</v>
+        <v>4.18</v>
       </c>
       <c r="R108" t="n">
-        <v>-0.07688758882839108</v>
+        <v>-0.006328035443194491</v>
       </c>
       <c r="S108" t="n">
-        <v>0.003727691778091291</v>
+        <v>-0.01289331915412382</v>
       </c>
       <c r="T108" t="n">
         <v>28.995</v>
@@ -10413,6 +10736,9 @@
       <c r="AB108" t="n">
         <v>-0.1398969209040258</v>
       </c>
+      <c r="AC108" t="n">
+        <v>3.611344073523441</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10468,13 +10794,13 @@
         <v>0.002447857918222877</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.294434161386915</v>
+        <v>4.169</v>
       </c>
       <c r="R109" t="n">
-        <v>-0.07376868045082707</v>
+        <v>-0.04006899180484025</v>
       </c>
       <c r="S109" t="n">
-        <v>0.003325214549208928</v>
+        <v>-0.02013419468071367</v>
       </c>
       <c r="T109" t="n">
         <v>29.01</v>
@@ -10505,6 +10831,9 @@
       <c r="AB109" t="n">
         <v>0.2430785711148564</v>
       </c>
+      <c r="AC109" t="n">
+        <v>2.859946810771716</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10560,13 +10889,13 @@
         <v>0.002192943138090632</v>
       </c>
       <c r="Q110" t="n">
-        <v>4.228211276665901</v>
+        <v>4.106</v>
       </c>
       <c r="R110" t="n">
-        <v>-0.07091616962933611</v>
+        <v>-0.0413426573426563</v>
       </c>
       <c r="S110" t="n">
-        <v>0.002907514964359856</v>
+        <v>0.006681932355861783</v>
       </c>
       <c r="T110" t="n">
         <v>28.98</v>
@@ -10597,6 +10926,9 @@
       <c r="AB110" t="n">
         <v>0.3784772902973303</v>
       </c>
+      <c r="AC110" t="n">
+        <v>2.04908911365771</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10652,13 +10984,13 @@
         <v>0.001858787740399326</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.14182795782078</v>
+        <v>4.101</v>
       </c>
       <c r="R111" t="n">
-        <v>-0.06763004016716101</v>
+        <v>-0.01923219814241506</v>
       </c>
       <c r="S111" t="n">
-        <v>0.00235997287669356</v>
+        <v>0.005004321979409698</v>
       </c>
       <c r="T111" t="n">
         <v>29.01</v>
@@ -10689,6 +11021,9 @@
       <c r="AB111" t="n">
         <v>0.4272160143279087</v>
       </c>
+      <c r="AC111" t="n">
+        <v>1.158583948368213</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10744,13 +11079,13 @@
         <v>0.001406724296956905</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.037708494123475</v>
+        <v>4.04</v>
       </c>
       <c r="R112" t="n">
-        <v>-0.06443277189122842</v>
+        <v>-0.03674724602203172</v>
       </c>
       <c r="S112" t="n">
-        <v>0.001619228410825142</v>
+        <v>-0.008567712689067595</v>
       </c>
       <c r="T112" t="n">
         <v>28.98</v>
@@ -10781,6 +11116,9 @@
       <c r="AB112" t="n">
         <v>0.4798105591741548</v>
       </c>
+      <c r="AC112" t="n">
+        <v>0.1853250864187432</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10836,13 +11174,13 @@
         <v>0.000880447129478692</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.912195091961094</v>
+        <v>3.971</v>
       </c>
       <c r="R113" t="n">
-        <v>-0.06220509129191787</v>
+        <v>-0.04758097165991881</v>
       </c>
       <c r="S113" t="n">
-        <v>0.000756878435445342</v>
+        <v>-0.003986266036997179</v>
       </c>
       <c r="T113" t="n">
         <v>29.01</v>
@@ -10873,6 +11211,9 @@
       <c r="AB113" t="n">
         <v>0.5197472299269156</v>
       </c>
+      <c r="AC113" t="n">
+        <v>-0.7233749756991107</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10928,13 +11269,13 @@
         <v>-0.0001080411410060017</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.647818699384286</v>
+        <v>3.642</v>
       </c>
       <c r="R114" t="n">
-        <v>-0.0622767600189591</v>
+        <v>-0.05142307692307679</v>
       </c>
       <c r="S114" t="n">
-        <v>-0.0008628438105337151</v>
+        <v>0.001965044534412978</v>
       </c>
       <c r="T114" t="n">
         <v>29.01</v>
@@ -10965,6 +11306,9 @@
       <c r="AB114" t="n">
         <v>0.5187938176432531</v>
       </c>
+      <c r="AC114" t="n">
+        <v>-1.777320557315394</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11020,13 +11364,13 @@
         <v>-0.0005551800082818237</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.543212033153671</v>
+        <v>3.572</v>
       </c>
       <c r="R115" t="n">
-        <v>-0.06425733616056928</v>
+        <v>-0.04631999999999981</v>
       </c>
       <c r="S115" t="n">
-        <v>-0.001595518938801424</v>
+        <v>-0.0002364923076923538</v>
       </c>
       <c r="T115" t="n">
         <v>29.01</v>
@@ -11057,6 +11401,9 @@
       <c r="AB115" t="n">
         <v>0.4798326520311891</v>
       </c>
+      <c r="AC115" t="n">
+        <v>-1.827902391620322</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11112,13 +11459,13 @@
         <v>-0.001262511799616995</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.376968681168996</v>
+        <v>3.44</v>
       </c>
       <c r="R116" t="n">
-        <v>-0.06977303320945527</v>
+        <v>-0.05928000000000022</v>
       </c>
       <c r="S116" t="n">
-        <v>-0.002754542340416524</v>
+        <v>-0.003660195348837152</v>
       </c>
       <c r="T116" t="n">
         <v>28.995</v>
@@ -11149,6 +11496,9 @@
       <c r="AB116" t="n">
         <v>0.3747967623575328</v>
       </c>
+      <c r="AC116" t="n">
+        <v>-1.49888559811747</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11204,13 +11554,13 @@
         <v>-0.001716623534717529</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.257040634247031</v>
+        <v>3.334</v>
       </c>
       <c r="R117" t="n">
-        <v>-0.0749731187999963</v>
+        <v>-0.06368720930232546</v>
       </c>
       <c r="S117" t="n">
-        <v>-0.003498643106672418</v>
+        <v>-0.005705195358700371</v>
       </c>
       <c r="T117" t="n">
         <v>28.98</v>
@@ -11241,6 +11591,9 @@
       <c r="AB117" t="n">
         <v>0.2977087888821338</v>
       </c>
+      <c r="AC117" t="n">
+        <v>-1.200014726026039</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11296,13 +11649,13 @@
         <v>-0.002463198348949519</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.027245369937801</v>
+        <v>3.151</v>
       </c>
       <c r="R118" t="n">
-        <v>-0.08686927210603346</v>
+        <v>-0.09513423124589948</v>
       </c>
       <c r="S118" t="n">
-        <v>-0.00472196954463445</v>
+        <v>-0.01059677734848656</v>
       </c>
       <c r="T118" t="n">
         <v>29.01</v>
@@ -11333,6 +11686,9 @@
       <c r="AB118" t="n">
         <v>0.189063643585355</v>
       </c>
+      <c r="AC118" t="n">
+        <v>-0.8100541190990447</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11388,13 +11744,13 @@
         <v>-0.003189110866347219</v>
       </c>
       <c r="Q119" t="n">
-        <v>2.752294038039425</v>
+        <v>2.778</v>
       </c>
       <c r="R119" t="n">
-        <v>-0.102437715694196</v>
+        <v>-0.1250981909152303</v>
       </c>
       <c r="S119" t="n">
-        <v>-0.005911439048897982</v>
+        <v>-0.01115875793578195</v>
       </c>
       <c r="T119" t="n">
         <v>29.01</v>
@@ -11425,6 +11781,9 @@
       <c r="AB119" t="n">
         <v>0.1160162919992433</v>
       </c>
+      <c r="AC119" t="n">
+        <v>-0.6259893618765752</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11480,13 +11839,13 @@
         <v>-0.004075977575900037</v>
       </c>
       <c r="Q120" t="n">
-        <v>2.414263131103091</v>
+        <v>2.405</v>
       </c>
       <c r="R120" t="n">
-        <v>-0.1222637205931832</v>
+        <v>-0.1619067920031776</v>
       </c>
       <c r="S120" t="n">
-        <v>-0.007364645709586715</v>
+        <v>-0.009896672088702197</v>
       </c>
       <c r="T120" t="n">
         <v>29.01</v>
@@ -11517,6 +11876,9 @@
       <c r="AB120" t="n">
         <v>0.08201579757485161</v>
       </c>
+      <c r="AC120" t="n">
+        <v>-0.6633517402212648</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11572,13 +11934,13 @@
         <v>-0.004634695647620763</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.086299653662603</v>
+        <v>1.92</v>
       </c>
       <c r="R121" t="n">
-        <v>-0.1423826153722847</v>
+        <v>-0.1820371434474639</v>
       </c>
       <c r="S121" t="n">
-        <v>-0.008280152870387792</v>
+        <v>-0.003548965325650622</v>
       </c>
       <c r="T121" t="n">
         <v>28.995</v>
@@ -11609,6 +11971,9 @@
       <c r="AB121" t="n">
         <v>0.1099057100818981</v>
       </c>
+      <c r="AC121" t="n">
+        <v>-0.9194498805502402</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11664,13 +12029,13 @@
         <v>-0.005461783123241583</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.8116881888459335</v>
+        <v>0.848</v>
       </c>
       <c r="R122" t="n">
-        <v>-0.2076251095201643</v>
+        <v>-0.1123335659346869</v>
       </c>
       <c r="S122" t="n">
-        <v>-0.009635406163354884</v>
+        <v>0.02268953580970839</v>
       </c>
       <c r="T122" t="n">
         <v>28.98</v>
@@ -11701,6 +12066,9 @@
       <c r="AB122" t="n">
         <v>0.2985811083836037</v>
       </c>
+      <c r="AC122" t="n">
+        <v>-1.998857655475034</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11756,13 +12124,13 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>5.592431734443508</v>
+        <v>5.11</v>
       </c>
       <c r="R123" t="n">
-        <v>-0.1605587730358544</v>
+        <v>0.1361702755076259</v>
       </c>
       <c r="S123" t="n">
-        <v>1.122540463638355e-07</v>
+        <v>-0.1126639443221651</v>
       </c>
       <c r="T123" t="n">
         <v>37.065</v>
@@ -11793,6 +12161,9 @@
       <c r="AB123" t="n">
         <v>0.2961312051420067</v>
       </c>
+      <c r="AC123" t="n">
+        <v>3.313023003094814</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11848,13 +12219,13 @@
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>5.488093393481237</v>
+        <v>5.179</v>
       </c>
       <c r="R124" t="n">
-        <v>-0.1604822760788234</v>
+        <v>0.07613741680006791</v>
       </c>
       <c r="S124" t="n">
-        <v>0.0002352629983568277</v>
+        <v>-0.07205254400878257</v>
       </c>
       <c r="T124" t="n">
         <v>36.98999999999999</v>
@@ -11885,6 +12256,9 @@
       <c r="AB124" t="n">
         <v>0.41725799155868</v>
       </c>
+      <c r="AC124" t="n">
+        <v>3.443499809460463</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11940,13 +12314,13 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>5.370438035918479</v>
+        <v>5.21</v>
       </c>
       <c r="R125" t="n">
-        <v>-0.1602124738456299</v>
+        <v>0.04009881422924888</v>
       </c>
       <c r="S125" t="n">
-        <v>0.0006087828617032942</v>
+        <v>0.03236949534242994</v>
       </c>
       <c r="T125" t="n">
         <v>36.98999999999999</v>
@@ -11977,6 +12351,9 @@
       <c r="AB125" t="n">
         <v>0.5631477425737303</v>
       </c>
+      <c r="AC125" t="n">
+        <v>3.011837705125814</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12032,13 +12409,13 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>5.247790136128947</v>
+        <v>5.239</v>
       </c>
       <c r="R126" t="n">
-        <v>-0.159552678782255</v>
+        <v>0.1302493673798022</v>
       </c>
       <c r="S126" t="n">
-        <v>0.001147011017144095</v>
+        <v>0.0403544816631714</v>
       </c>
       <c r="T126" t="n">
         <v>37.005</v>
@@ -12069,6 +12446,9 @@
       <c r="AB126" t="n">
         <v>0.7925378766569672</v>
       </c>
+      <c r="AC126" t="n">
+        <v>1.39686600427235</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12124,13 +12504,13 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>5.154905414913893</v>
+        <v>5.356</v>
       </c>
       <c r="R127" t="n">
-        <v>-0.1587564691919297</v>
+        <v>0.1195102550383447</v>
       </c>
       <c r="S127" t="n">
-        <v>0.001579281223228146</v>
+        <v>-0.06978356474461157</v>
       </c>
       <c r="T127" t="n">
         <v>37.035</v>
@@ -12161,6 +12541,9 @@
       <c r="AB127" t="n">
         <v>1.073416419704768</v>
       </c>
+      <c r="AC127" t="n">
+        <v>-0.720365515082811</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12216,13 +12599,13 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>5.012683444043301</v>
+        <v>5.351</v>
       </c>
       <c r="R128" t="n">
-        <v>-0.157037475115251</v>
+        <v>-0.01463094673620935</v>
       </c>
       <c r="S128" t="n">
-        <v>0.002207243150674235</v>
+        <v>-0.1159961160611575</v>
       </c>
       <c r="T128" t="n">
         <v>37.035</v>
@@ -12253,6 +12636,9 @@
       <c r="AB128" t="n">
         <v>1.695652023744553</v>
       </c>
+      <c r="AC128" t="n">
+        <v>-3.41003098346165</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12308,13 +12694,13 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>4.86448752113856</v>
+        <v>5.328</v>
       </c>
       <c r="R129" t="n">
-        <v>-0.1546425186962677</v>
+        <v>-0.09168578868460564</v>
       </c>
       <c r="S129" t="n">
-        <v>0.002830586848225569</v>
+        <v>-0.08953810553234574</v>
       </c>
       <c r="T129" t="n">
         <v>37.02</v>
@@ -12345,6 +12731,9 @@
       <c r="AB129" t="n">
         <v>2.606035115992697</v>
       </c>
+      <c r="AC129" t="n">
+        <v>-5.858698024470596</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12400,13 +12789,13 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.716330785199085</v>
+        <v>5.173</v>
       </c>
       <c r="R130" t="n">
-        <v>-0.1516017737992774</v>
+        <v>-0.1865290381125231</v>
       </c>
       <c r="S130" t="n">
-        <v>0.003526471232355888</v>
+        <v>-0.0926065853845936</v>
       </c>
       <c r="T130" t="n">
         <v>36.98999999999999</v>
@@ -12437,6 +12826,9 @@
       <c r="AB130" t="n">
         <v>3.795841063326084</v>
       </c>
+      <c r="AC130" t="n">
+        <v>-9.816038158956275</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12492,13 +12884,13 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>4.62100671610599</v>
+        <v>5.044</v>
       </c>
       <c r="R131" t="n">
-        <v>-0.1492103015868738</v>
+        <v>-0.2428947368421064</v>
       </c>
       <c r="S131" t="n">
-        <v>0.003995844243220623</v>
+        <v>-0.06489520954417326</v>
       </c>
       <c r="T131" t="n">
         <v>37.035</v>
@@ -12529,6 +12921,9 @@
       <c r="AB131" t="n">
         <v>4.451505516103177</v>
       </c>
+      <c r="AC131" t="n">
+        <v>-12.42365759698266</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12584,13 +12979,13 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>4.435303846448252</v>
+        <v>4.637</v>
       </c>
       <c r="R132" t="n">
-        <v>-0.14359198231225</v>
+        <v>-0.2640337381916322</v>
       </c>
       <c r="S132" t="n">
-        <v>0.004841484713956901</v>
+        <v>-0.07362255842034135</v>
       </c>
       <c r="T132" t="n">
         <v>36.98999999999999</v>
@@ -12621,6 +13016,9 @@
       <c r="AB132" t="n">
         <v>4.778074869011388</v>
       </c>
+      <c r="AC132" t="n">
+        <v>-14.91760204762478</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12676,13 +13074,13 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>4.307999424911104</v>
+        <v>4.436</v>
       </c>
       <c r="R133" t="n">
-        <v>-0.13897503925967</v>
+        <v>-0.3667017543859641</v>
       </c>
       <c r="S133" t="n">
-        <v>0.005472655484762945</v>
+        <v>-0.05811724264875145</v>
       </c>
       <c r="T133" t="n">
         <v>36.93</v>
@@ -12713,6 +13111,9 @@
       <c r="AB133" t="n">
         <v>4.155713318143079</v>
       </c>
+      <c r="AC133" t="n">
+        <v>-14.70625294824191</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12768,13 +13169,13 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>4.171773627877908</v>
+        <v>3.91</v>
       </c>
       <c r="R134" t="n">
-        <v>-0.133121585153047</v>
+        <v>-0.3626430738119315</v>
       </c>
       <c r="S134" t="n">
-        <v>0.006211626561850425</v>
+        <v>0.07925207654239341</v>
       </c>
       <c r="T134" t="n">
         <v>36.98999999999999</v>
@@ -12805,6 +13206,9 @@
       <c r="AB134" t="n">
         <v>2.994905744117902</v>
       </c>
+      <c r="AC134" t="n">
+        <v>-12.87511465271384</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12860,13 +13264,13 @@
         <v>0.01370049311218863</v>
       </c>
       <c r="Q135" t="n">
-        <v>4.022789125163403</v>
+        <v>3.709</v>
       </c>
       <c r="R135" t="n">
-        <v>-0.1255045315348808</v>
+        <v>-0.1720599196200223</v>
       </c>
       <c r="S135" t="n">
-        <v>0.00696191218612182</v>
+        <v>0.1324668005956939</v>
       </c>
       <c r="T135" t="n">
         <v>37.005</v>
@@ -12897,6 +13301,9 @@
       <c r="AB135" t="n">
         <v>1.855617321432888</v>
       </c>
+      <c r="AC135" t="n">
+        <v>-9.448636258436965</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12952,13 +13359,13 @@
         <v>0.02555529823895503</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.852054104506391</v>
+        <v>3.47</v>
       </c>
       <c r="R136" t="n">
-        <v>-0.1150512795494714</v>
+        <v>-0.04243889594206962</v>
       </c>
       <c r="S136" t="n">
-        <v>0.007534284372663874</v>
+        <v>0.06734969333078814</v>
       </c>
       <c r="T136" t="n">
         <v>36.96</v>
@@ -12989,6 +13396,9 @@
       <c r="AB136" t="n">
         <v>0.9038694069820155</v>
       </c>
+      <c r="AC136" t="n">
+        <v>-4.028246075253294</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13044,13 +13454,13 @@
         <v>0.01087678132715291</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.751634109924598</v>
+        <v>3.504</v>
       </c>
       <c r="R137" t="n">
-        <v>-0.1081815037588462</v>
+        <v>0.004369139904023767</v>
       </c>
       <c r="S137" t="n">
-        <v>0.007504281528254799</v>
+        <v>0.01440927302218155</v>
       </c>
       <c r="T137" t="n">
         <v>31.995</v>
@@ -13081,6 +13491,9 @@
       <c r="AB137" t="n">
         <v>0.557886275373886</v>
       </c>
+      <c r="AC137" t="n">
+        <v>-1.036977167359194</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13136,13 +13549,13 @@
         <v>-0.00710389630350909</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.604326670005563</v>
+        <v>3.434</v>
       </c>
       <c r="R138" t="n">
-        <v>-0.09771938685462644</v>
+        <v>-0.06080690627202245</v>
       </c>
       <c r="S138" t="n">
-        <v>0.007021889859726835</v>
+        <v>-0.02470380297996579</v>
       </c>
       <c r="T138" t="n">
         <v>32.01</v>
@@ -13173,6 +13586,9 @@
       <c r="AB138" t="n">
         <v>0.3103350383602442</v>
       </c>
+      <c r="AC138" t="n">
+        <v>1.092856710913152</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13228,13 +13644,13 @@
         <v>-0.00637303148429085</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.465680010216048</v>
+        <v>3.324</v>
       </c>
       <c r="R139" t="n">
-        <v>-0.08762178809163856</v>
+        <v>-0.06526190476190463</v>
       </c>
       <c r="S139" t="n">
-        <v>0.006377596591206413</v>
+        <v>0.001595388495633288</v>
       </c>
       <c r="T139" t="n">
         <v>32.01</v>
@@ -13265,6 +13681,9 @@
       <c r="AB139" t="n">
         <v>0.2377085833703645</v>
       </c>
+      <c r="AC139" t="n">
+        <v>1.256852204810589</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13320,13 +13739,13 @@
         <v>-0.005470297797812553</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.303261283191983</v>
+        <v>3.215</v>
       </c>
       <c r="R140" t="n">
-        <v>-0.07581095735576482</v>
+        <v>-0.04989676113360325</v>
       </c>
       <c r="S140" t="n">
-        <v>0.005581792466871252</v>
+        <v>0.007705590900327696</v>
       </c>
       <c r="T140" t="n">
         <v>31.98</v>
@@ -13357,6 +13776,9 @@
       <c r="AB140" t="n">
         <v>0.2407625145597302</v>
       </c>
+      <c r="AC140" t="n">
+        <v>0.5724246734257523</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13412,13 +13834,13 @@
         <v>-0.003799960777227666</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.025432170228625</v>
+        <v>3.042</v>
       </c>
       <c r="R141" t="n">
-        <v>-0.05466164945932772</v>
+        <v>-0.01628974358974355</v>
       </c>
       <c r="S141" t="n">
-        <v>0.004109308267022663</v>
+        <v>0.002903851551956846</v>
       </c>
       <c r="T141" t="n">
         <v>31.995</v>
@@ -13449,6 +13871,9 @@
       <c r="AB141" t="n">
         <v>0.3051722636592766</v>
       </c>
+      <c r="AC141" t="n">
+        <v>-0.9508965773725447</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13504,13 +13929,13 @@
         <v>-0.003042496589870878</v>
       </c>
       <c r="Q142" t="n">
-        <v>2.940388883453159</v>
+        <v>3.03</v>
       </c>
       <c r="R142" t="n">
-        <v>-0.04830722622425132</v>
+        <v>-0.01455999999999991</v>
       </c>
       <c r="S142" t="n">
-        <v>0.003441566347823866</v>
+        <v>-0.005828492307692312</v>
       </c>
       <c r="T142" t="n">
         <v>31.98</v>
@@ -13541,6 +13966,9 @@
       <c r="AB142" t="n">
         <v>0.3150057454595456</v>
       </c>
+      <c r="AC142" t="n">
+        <v>-1.173932627829475</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13596,13 +14024,13 @@
         <v>-0.001847930289874596</v>
       </c>
       <c r="Q143" t="n">
-        <v>2.829816114796388</v>
+        <v>2.966</v>
       </c>
       <c r="R143" t="n">
-        <v>-0.04109488882927403</v>
+        <v>-0.05488000000000004</v>
       </c>
       <c r="S143" t="n">
-        <v>0.002388497427756134</v>
+        <v>-0.009211589800174978</v>
       </c>
       <c r="T143" t="n">
         <v>31.98</v>
@@ -13633,6 +14061,9 @@
       <c r="AB143" t="n">
         <v>0.3042101058979073</v>
       </c>
+      <c r="AC143" t="n">
+        <v>-1.022414594764808</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13688,13 +14119,13 @@
         <v>-0.001075146602099324</v>
       </c>
       <c r="Q144" t="n">
-        <v>2.764807098562525</v>
+        <v>2.842</v>
       </c>
       <c r="R144" t="n">
-        <v>-0.03766565703883024</v>
+        <v>-0.06254774944493047</v>
       </c>
       <c r="S144" t="n">
-        <v>0.001707250615809435</v>
+        <v>-0.0001214833357782589</v>
       </c>
       <c r="T144" t="n">
         <v>32.01</v>
@@ -13725,6 +14156,9 @@
       <c r="AB144" t="n">
         <v>0.2903724799169134</v>
       </c>
+      <c r="AC144" t="n">
+        <v>-0.8086885580720576</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13780,13 +14214,13 @@
         <v>0.0001606346812521692</v>
       </c>
       <c r="Q145" t="n">
-        <v>2.666198413653078</v>
+        <v>2.723</v>
       </c>
       <c r="R145" t="n">
-        <v>-0.03454200862781115</v>
+        <v>-0.04206596642780003</v>
       </c>
       <c r="S145" t="n">
-        <v>0.0006178486617255188</v>
+        <v>0.00370098193486991</v>
       </c>
       <c r="T145" t="n">
         <v>31.995</v>
@@ -13817,6 +14251,9 @@
       <c r="AB145" t="n">
         <v>0.2704304451900449</v>
       </c>
+      <c r="AC145" t="n">
+        <v>-0.5455376838656428</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13872,13 +14309,13 @@
         <v>0.001434166412932715</v>
       </c>
       <c r="Q146" t="n">
-        <v>2.563807363985861</v>
+        <v>2.597</v>
       </c>
       <c r="R146" t="n">
-        <v>-0.03434345135035966</v>
+        <v>-0.04300293546493239</v>
       </c>
       <c r="S146" t="n">
-        <v>-0.0005048321684275239</v>
+        <v>-0.0004882235739605677</v>
       </c>
       <c r="T146" t="n">
         <v>31.98</v>
@@ -13909,6 +14346,9 @@
       <c r="AB146" t="n">
         <v>0.2577431435737859</v>
       </c>
+      <c r="AC146" t="n">
+        <v>-0.462673759667947</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13964,13 +14404,13 @@
         <v>0.002930754982840081</v>
       </c>
       <c r="Q147" t="n">
-        <v>2.458497161231485</v>
+        <v>2.463</v>
       </c>
       <c r="R147" t="n">
-        <v>-0.03753971711341153</v>
+        <v>-0.0450017653667148</v>
       </c>
       <c r="S147" t="n">
-        <v>-0.001824148567276949</v>
+        <v>-0.001241633240984915</v>
       </c>
       <c r="T147" t="n">
         <v>32.01</v>
@@ -14001,6 +14441,9 @@
       <c r="AB147" t="n">
         <v>0.2557588708921351</v>
       </c>
+      <c r="AC147" t="n">
+        <v>-0.5925120549491631</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14056,13 +14499,13 @@
         <v>0.00391744027113252</v>
       </c>
       <c r="Q148" t="n">
-        <v>2.356099883078157</v>
+        <v>2.346</v>
       </c>
       <c r="R148" t="n">
-        <v>-0.04393991643780183</v>
+        <v>-0.04948921998782908</v>
       </c>
       <c r="S148" t="n">
-        <v>-0.002693960155794071</v>
+        <v>-0.002121073335170386</v>
       </c>
       <c r="T148" t="n">
         <v>32.01</v>
@@ -14093,6 +14536,9 @@
       <c r="AB148" t="n">
         <v>0.2659772851655287</v>
       </c>
+      <c r="AC148" t="n">
+        <v>-0.9270946213544438</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14148,13 +14594,13 @@
         <v>0.005362219758256564</v>
       </c>
       <c r="Q149" t="n">
-        <v>1.925963527392448</v>
+        <v>1.876</v>
       </c>
       <c r="R149" t="n">
-        <v>-0.06925386137422668</v>
+        <v>-0.0741949905384866</v>
       </c>
       <c r="S149" t="n">
-        <v>-0.003967604301159836</v>
+        <v>-0.004380445230792118</v>
       </c>
       <c r="T149" t="n">
         <v>32.01</v>
@@ -14185,6 +14631,9 @@
       <c r="AB149" t="n">
         <v>0.3117734557549207</v>
       </c>
+      <c r="AC149" t="n">
+        <v>-2.22648472982898</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14240,13 +14689,13 @@
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>5.568555367888618</v>
+        <v>5.341</v>
       </c>
       <c r="R150" t="n">
-        <v>-0.1302594256056371</v>
+        <v>0.002202380952377681</v>
       </c>
       <c r="S150" t="n">
-        <v>0.005281409957490109</v>
+        <v>-0.006189090979920544</v>
       </c>
       <c r="T150" t="n">
         <v>37.26</v>
@@ -14277,6 +14726,9 @@
       <c r="AB150" t="n">
         <v>0.1191079425402689</v>
       </c>
+      <c r="AC150" t="n">
+        <v>0.9540753836815266</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14332,13 +14784,13 @@
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>5.46602359888036</v>
+        <v>5.342</v>
       </c>
       <c r="R151" t="n">
-        <v>-0.1260699969150112</v>
+        <v>0.0002976190476187135</v>
       </c>
       <c r="S151" t="n">
-        <v>0.005192161769074652</v>
+        <v>0.001427186218023125</v>
       </c>
       <c r="T151" t="n">
         <v>36.98999999999999</v>
@@ -14369,6 +14821,9 @@
       <c r="AB151" t="n">
         <v>0.5252207132001485</v>
       </c>
+      <c r="AC151" t="n">
+        <v>0.4722469647603376</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14424,13 +14879,13 @@
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>5.336536880326731</v>
+        <v>5.341</v>
       </c>
       <c r="R152" t="n">
-        <v>-0.1206797246373128</v>
+        <v>0.007044255583251058</v>
       </c>
       <c r="S152" t="n">
-        <v>0.005033894490633087</v>
+        <v>0.008224470502934305</v>
       </c>
       <c r="T152" t="n">
         <v>36.98999999999999</v>
@@ -14461,6 +14916,9 @@
       <c r="AB152" t="n">
         <v>1.011427118841145</v>
       </c>
+      <c r="AC152" t="n">
+        <v>-0.5401718691950494</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14516,13 +14974,13 @@
         <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>5.197254517771801</v>
+        <v>5.36</v>
       </c>
       <c r="R153" t="n">
-        <v>-0.1148559067382955</v>
+        <v>0.01917582479641311</v>
       </c>
       <c r="S153" t="n">
-        <v>0.004803262707272632</v>
+        <v>-0.1326490903472027</v>
       </c>
       <c r="T153" t="n">
         <v>37.02</v>
@@ -14553,6 +15011,9 @@
       <c r="AB153" t="n">
         <v>1.609085007840527</v>
       </c>
+      <c r="AC153" t="n">
+        <v>-1.744092462923201</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14608,13 +15069,13 @@
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>5.088475729068357</v>
+        <v>5.381</v>
       </c>
       <c r="R154" t="n">
-        <v>-0.1103061500195719</v>
+        <v>-0.2218965517241398</v>
       </c>
       <c r="S154" t="n">
-        <v>0.004606003144244745</v>
+        <v>-0.04570210440003079</v>
       </c>
       <c r="T154" t="n">
         <v>36.98999999999999</v>
@@ -14645,6 +15106,9 @@
       <c r="AB154" t="n">
         <v>2.284668667495373</v>
       </c>
+      <c r="AC154" t="n">
+        <v>-2.099023934851583</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14700,13 +15164,13 @@
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.983995961067296</v>
+        <v>4.931</v>
       </c>
       <c r="R155" t="n">
-        <v>-0.105950967326089</v>
+        <v>-0.06918157704364747</v>
       </c>
       <c r="S155" t="n">
-        <v>0.004402817657000492</v>
+        <v>0.1643195662838958</v>
       </c>
       <c r="T155" t="n">
         <v>37.005</v>
@@ -14737,6 +15201,9 @@
       <c r="AB155" t="n">
         <v>3.215184949252306</v>
       </c>
+      <c r="AC155" t="n">
+        <v>-5.268939610290632</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14792,13 +15259,13 @@
         <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.893828029242033</v>
+        <v>5.179</v>
       </c>
       <c r="R156" t="n">
-        <v>-0.1022148696958085</v>
+        <v>0.07815384615384646</v>
       </c>
       <c r="S156" t="n">
-        <v>0.004226462520941054</v>
+        <v>-0.04070561058532067</v>
       </c>
       <c r="T156" t="n">
         <v>37.035</v>
@@ -14829,6 +15296,9 @@
       <c r="AB156" t="n">
         <v>4.306374541182488</v>
       </c>
+      <c r="AC156" t="n">
+        <v>-11.30199594735004</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14884,13 +15354,13 @@
         <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.785566677835473</v>
+        <v>4.982</v>
       </c>
       <c r="R157" t="n">
-        <v>-0.09775051984832794</v>
+        <v>-0.251277678393957</v>
       </c>
       <c r="S157" t="n">
-        <v>0.004016857859617459</v>
+        <v>-0.1535860637023436</v>
       </c>
       <c r="T157" t="n">
         <v>37.02</v>
@@ -14921,6 +15391,9 @@
       <c r="AB157" t="n">
         <v>5.750789206449928</v>
       </c>
+      <c r="AC157" t="n">
+        <v>-16.4781423572674</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14976,13 +15449,13 @@
         <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.716547121242288</v>
+        <v>4.769</v>
       </c>
       <c r="R158" t="n">
-        <v>-0.09492111652909863</v>
+        <v>-0.2899930861093658</v>
       </c>
       <c r="S158" t="n">
-        <v>0.003864805099588017</v>
+        <v>-0.02904525734168401</v>
       </c>
       <c r="T158" t="n">
         <v>37.035</v>
@@ -15013,6 +15486,9 @@
       <c r="AB158" t="n">
         <v>6.320935151676336</v>
       </c>
+      <c r="AC158" t="n">
+        <v>-16.45134830242088</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15068,13 +15544,13 @@
         <v>0.0107956597074198</v>
       </c>
       <c r="Q159" t="n">
-        <v>4.658747469779701</v>
+        <v>4.594</v>
       </c>
       <c r="R159" t="n">
-        <v>-0.09258196739953251</v>
+        <v>-0.2946514308426078</v>
       </c>
       <c r="S159" t="n">
-        <v>0.003724601654162454</v>
+        <v>0.03446216173681331</v>
       </c>
       <c r="T159" t="n">
         <v>36.96</v>
@@ -15105,6 +15581,9 @@
       <c r="AB159" t="n">
         <v>5.749088823986074</v>
       </c>
+      <c r="AC159" t="n">
+        <v>-13.91352446682418</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15160,13 +15639,13 @@
         <v>0.02134946752914934</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.585872500453607</v>
+        <v>4.347</v>
       </c>
       <c r="R160" t="n">
-        <v>-0.08967349540000558</v>
+        <v>-0.2234756637168138</v>
       </c>
       <c r="S160" t="n">
-        <v>0.003551534140926266</v>
+        <v>0.1203369683688771</v>
       </c>
       <c r="T160" t="n">
         <v>37.02</v>
@@ -15197,6 +15676,9 @@
       <c r="AB160" t="n">
         <v>3.850441400322788</v>
       </c>
+      <c r="AC160" t="n">
+        <v>-8.317267676272134</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15252,13 +15734,13 @@
         <v>0.007802512902614564</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.490809690745411</v>
+        <v>4.23</v>
       </c>
       <c r="R161" t="n">
-        <v>-0.08594931119250493</v>
+        <v>-0.04709440936393117</v>
       </c>
       <c r="S161" t="n">
-        <v>0.00333617496416037</v>
+        <v>0.112937955611399</v>
       </c>
       <c r="T161" t="n">
         <v>29.01</v>
@@ -15289,6 +15771,9 @@
       <c r="AB161" t="n">
         <v>1.63961880357864</v>
       </c>
+      <c r="AC161" t="n">
+        <v>-1.18934854841909</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15344,13 +15829,13 @@
         <v>-0.003760463504501162</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.371031064913568</v>
+        <v>4.278</v>
       </c>
       <c r="R162" t="n">
-        <v>-0.08136000964781998</v>
+        <v>0.02019889840881239</v>
       </c>
       <c r="S162" t="n">
-        <v>0.003055232595542551</v>
+        <v>-0.01216435835344395</v>
       </c>
       <c r="T162" t="n">
         <v>28.995</v>
@@ -15381,6 +15866,9 @@
       <c r="AB162" t="n">
         <v>0.3167538372520005</v>
       </c>
+      <c r="AC162" t="n">
+        <v>2.839222131285208</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15436,13 +15924,13 @@
         <v>-0.00346125297583441</v>
       </c>
       <c r="Q163" t="n">
-        <v>4.283397728433791</v>
+        <v>4.289</v>
       </c>
       <c r="R163" t="n">
-        <v>-0.07812301627178186</v>
+        <v>-0.04308441558441545</v>
       </c>
       <c r="S163" t="n">
-        <v>0.002807371276816465</v>
+        <v>-0.04475767231777314</v>
       </c>
       <c r="T163" t="n">
         <v>28.995</v>
@@ -15473,6 +15961,9 @@
       <c r="AB163" t="n">
         <v>0.1810885986158573</v>
       </c>
+      <c r="AC163" t="n">
+        <v>2.618074207300888</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15528,13 +16019,13 @@
         <v>-0.003027186320082213</v>
       </c>
       <c r="Q164" t="n">
-        <v>4.17183600426774</v>
+        <v>4.122</v>
       </c>
       <c r="R164" t="n">
-        <v>-0.07427022279296658</v>
+        <v>-0.08375144708394533</v>
       </c>
       <c r="S164" t="n">
-        <v>0.002447797253171801</v>
+        <v>-0.01306044838440818</v>
       </c>
       <c r="T164" t="n">
         <v>28.995</v>
@@ -15565,6 +16056,9 @@
       <c r="AB164" t="n">
         <v>0.2501555067739906</v>
       </c>
+      <c r="AC164" t="n">
+        <v>1.465281615898401</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15620,13 +16114,13 @@
         <v>-0.002361504646655055</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.979098951820144</v>
+        <v>4.046</v>
       </c>
       <c r="R165" t="n">
-        <v>-0.06852164333929281</v>
+        <v>-0.04542750894571571</v>
       </c>
       <c r="S165" t="n">
-        <v>0.001896356974107972</v>
+        <v>0.01053506813459414</v>
       </c>
       <c r="T165" t="n">
         <v>28.995</v>
@@ -15657,6 +16151,9 @@
       <c r="AB165" t="n">
         <v>0.3586542799317901</v>
       </c>
+      <c r="AC165" t="n">
+        <v>-0.1437343420758286</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15712,13 +16209,13 @@
         <v>-0.001230388993487751</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.626293769239063</v>
+        <v>3.596</v>
       </c>
       <c r="R166" t="n">
-        <v>-0.06048772095122956</v>
+        <v>-0.02745734370734354</v>
       </c>
       <c r="S166" t="n">
-        <v>0.0009593584711666027</v>
+        <v>-0.008569105796206915</v>
       </c>
       <c r="T166" t="n">
         <v>28.995</v>
@@ -15749,6 +16246,9 @@
       <c r="AB166" t="n">
         <v>0.4961118495453845</v>
       </c>
+      <c r="AC166" t="n">
+        <v>-1.845336128953297</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15804,13 +16304,13 @@
         <v>-0.0007687188886404113</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.528000277359463</v>
+        <v>3.577</v>
       </c>
       <c r="R167" t="n">
-        <v>-0.05914425896806597</v>
+        <v>-0.04738816738816731</v>
       </c>
       <c r="S167" t="n">
-        <v>0.0005769181823391187</v>
+        <v>-0.01493323787331291</v>
       </c>
       <c r="T167" t="n">
         <v>28.98</v>
@@ -15841,6 +16341,9 @@
       <c r="AB167" t="n">
         <v>0.5077574479287422</v>
       </c>
+      <c r="AC167" t="n">
+        <v>-1.9059684657569</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15896,13 +16399,13 @@
         <v>-0.0002878484120212748</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.43986691748777</v>
+        <v>3.457</v>
       </c>
       <c r="R168" t="n">
-        <v>-0.058602474241916</v>
+        <v>-0.07367977528089908</v>
       </c>
       <c r="S168" t="n">
-        <v>0.0001785726060587051</v>
+        <v>-0.005803414230380478</v>
       </c>
       <c r="T168" t="n">
         <v>29.01</v>
@@ -15933,6 +16436,9 @@
       <c r="AB168" t="n">
         <v>0.4999218214613053</v>
       </c>
+      <c r="AC168" t="n">
+        <v>-1.708820698722495</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15988,13 +16494,13 @@
         <v>0.0001083999204683676</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.354136177248058</v>
+        <v>3.358</v>
       </c>
       <c r="R169" t="n">
-        <v>-0.05860245436134193</v>
+        <v>-0.06537789987789966</v>
       </c>
       <c r="S169" t="n">
-        <v>-0.000149673310524831</v>
+        <v>0.003710269929774715</v>
       </c>
       <c r="T169" t="n">
         <v>29.01</v>
@@ -16025,6 +16531,9 @@
       <c r="AB169" t="n">
         <v>0.4842522708684667</v>
       </c>
+      <c r="AC169" t="n">
+        <v>-1.457232128454974</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16080,13 +16589,13 @@
         <v>0.0008166001620623204</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.175436403096402</v>
+        <v>3.173</v>
       </c>
       <c r="R170" t="n">
-        <v>-0.05999552168575839</v>
+        <v>-0.06635733511424119</v>
       </c>
       <c r="S170" t="n">
-        <v>-0.0007363353059610753</v>
+        <v>0.0006501891024152592</v>
       </c>
       <c r="T170" t="n">
         <v>28.995</v>
@@ -16117,6 +16626,9 @@
       <c r="AB170" t="n">
         <v>0.4428751455358038</v>
       </c>
+      <c r="AC170" t="n">
+        <v>-1.040928247386846</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16172,13 +16684,13 @@
         <v>0.001518467427489923</v>
       </c>
       <c r="Q171" t="n">
-        <v>2.992235033403133</v>
+        <v>2.958</v>
       </c>
       <c r="R171" t="n">
-        <v>-0.0630266400465459</v>
+        <v>-0.06151960784313726</v>
       </c>
       <c r="S171" t="n">
-        <v>-0.00131775116306425</v>
+        <v>0.003819154909326017</v>
       </c>
       <c r="T171" t="n">
         <v>29.01</v>
@@ -16209,6 +16721,9 @@
       <c r="AB171" t="n">
         <v>0.3932150357978619</v>
       </c>
+      <c r="AC171" t="n">
+        <v>-0.7891848947269442</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16264,13 +16779,13 @@
         <v>0.002291792353591941</v>
       </c>
       <c r="Q172" t="n">
-        <v>2.819519212679411</v>
+        <v>2.818</v>
       </c>
       <c r="R172" t="n">
-        <v>-0.06726924374333371</v>
+        <v>-0.04610478490913283</v>
       </c>
       <c r="S172" t="n">
-        <v>-0.00195836142781991</v>
+        <v>0.001334471343549186</v>
       </c>
       <c r="T172" t="n">
         <v>28.98</v>
@@ -16301,6 +16816,9 @@
       <c r="AB172" t="n">
         <v>0.3413636070570498</v>
       </c>
+      <c r="AC172" t="n">
+        <v>-0.7072462025365256</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16356,13 +16874,13 @@
         <v>0.002879348659543106</v>
       </c>
       <c r="Q173" t="n">
-        <v>2.631055662577874</v>
+        <v>2.711</v>
       </c>
       <c r="R173" t="n">
-        <v>-0.07356115845571501</v>
+        <v>-0.05465620331956053</v>
       </c>
       <c r="S173" t="n">
-        <v>-0.002445083875279956</v>
+        <v>-0.005176699384183049</v>
       </c>
       <c r="T173" t="n">
         <v>28.98</v>
@@ -16393,6 +16911,9 @@
       <c r="AB173" t="n">
         <v>0.2797930157739653</v>
       </c>
+      <c r="AC173" t="n">
+        <v>-0.8011639035919315</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16448,13 +16969,13 @@
         <v>0.003700188554177305</v>
       </c>
       <c r="Q174" t="n">
-        <v>1.953444176187408</v>
+        <v>1.917564923015524</v>
       </c>
       <c r="R174" t="n">
-        <v>-0.09584171314190154</v>
+        <v>-0.1437025659265583</v>
       </c>
       <c r="S174" t="n">
-        <v>-0.003125054796266683</v>
+        <v>-0.0170848912675664</v>
       </c>
       <c r="T174" t="n">
         <v>28.98</v>
@@ -16485,6 +17006,9 @@
       <c r="AB174" t="n">
         <v>0.07524205713058127</v>
       </c>
+      <c r="AC174" t="n">
+        <v>-1.371002725428623</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16540,13 +17064,13 @@
         <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>5.732872388967566</v>
+        <v>5.365</v>
       </c>
       <c r="R175" t="n">
-        <v>-0.1889704791412807</v>
+        <v>-0.01342967956413554</v>
       </c>
       <c r="S175" t="n">
-        <v>0.01015684076917937</v>
+        <v>0.1115624830899768</v>
       </c>
       <c r="T175" t="n">
         <v>36.98999999999999</v>
@@ -16577,6 +17101,9 @@
       <c r="AB175" t="n">
         <v>0.005412691265803897</v>
       </c>
+      <c r="AC175" t="n">
+        <v>4.150347420779199</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16632,13 +17159,13 @@
         <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>5.525158401246508</v>
+        <v>5.387</v>
       </c>
       <c r="R176" t="n">
-        <v>-0.1775836168370564</v>
+        <v>0.05225320897589825</v>
       </c>
       <c r="S176" t="n">
-        <v>0.009937622120628334</v>
+        <v>0.00434849668655338</v>
       </c>
       <c r="T176" t="n">
         <v>36.98999999999999</v>
@@ -16669,6 +17196,9 @@
       <c r="AB176" t="n">
         <v>0.6255367644071316</v>
       </c>
+      <c r="AC176" t="n">
+        <v>2.560746014097226</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16724,13 +17254,13 @@
         <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>5.383482253426692</v>
+        <v>5.449</v>
       </c>
       <c r="R177" t="n">
-        <v>-0.1695323950433436</v>
+        <v>0.02425781688822326</v>
       </c>
       <c r="S177" t="n">
-        <v>0.009686683770619972</v>
+        <v>-0.04673169996865803</v>
       </c>
       <c r="T177" t="n">
         <v>37.005</v>
@@ -16761,6 +17291,9 @@
       <c r="AB177" t="n">
         <v>1.156045873504645</v>
       </c>
+      <c r="AC177" t="n">
+        <v>-1.448015660549672</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16816,13 +17349,13 @@
         <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>5.218784881591974</v>
+        <v>5.41</v>
       </c>
       <c r="R178" t="n">
-        <v>-0.1600562686120586</v>
+        <v>-0.03772077453908729</v>
       </c>
       <c r="S178" t="n">
-        <v>0.009296834962808163</v>
+        <v>-0.06059605818184402</v>
       </c>
       <c r="T178" t="n">
         <v>37.02</v>
@@ -16853,6 +17386,9 @@
       <c r="AB178" t="n">
         <v>1.958585501744631</v>
       </c>
+      <c r="AC178" t="n">
+        <v>-5.799856639106845</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16908,13 +17444,13 @@
         <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>5.030919876745513</v>
+        <v>5.366</v>
       </c>
       <c r="R179" t="n">
-        <v>-0.1490105205838401</v>
+        <v>-0.1093994454200278</v>
       </c>
       <c r="S179" t="n">
-        <v>0.008851884966514401</v>
+        <v>-0.06824452736122164</v>
       </c>
       <c r="T179" t="n">
         <v>36.98999999999999</v>
@@ -16945,6 +17481,9 @@
       <c r="AB179" t="n">
         <v>2.947231657412036</v>
       </c>
+      <c r="AC179" t="n">
+        <v>-6.730495407239411</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -17000,13 +17539,13 @@
         <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>4.891023058375276</v>
+        <v>5.204</v>
       </c>
       <c r="R180" t="n">
-        <v>-0.1406278983839231</v>
+        <v>-0.1825353594389245</v>
       </c>
       <c r="S180" t="n">
-        <v>0.00848261608410221</v>
+        <v>-0.04042016117383522</v>
       </c>
       <c r="T180" t="n">
         <v>36.98999999999999</v>
@@ -17037,6 +17576,9 @@
       <c r="AB180" t="n">
         <v>3.637240802282883</v>
       </c>
+      <c r="AC180" t="n">
+        <v>-9.352969870954205</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17092,13 +17634,13 @@
         <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>4.754629244342364</v>
+        <v>5.006</v>
       </c>
       <c r="R181" t="n">
-        <v>-0.1323408637347274</v>
+        <v>-0.1865027472527476</v>
       </c>
       <c r="S181" t="n">
-        <v>0.008090679247391472</v>
+        <v>-0.05232210855654934</v>
       </c>
       <c r="T181" t="n">
         <v>36.98999999999999</v>
@@ -17129,6 +17671,9 @@
       <c r="AB181" t="n">
         <v>4.202352900146515</v>
       </c>
+      <c r="AC181" t="n">
+        <v>-12.70981863197453</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17184,13 +17729,13 @@
         <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.642978045107347</v>
+        <v>4.853</v>
       </c>
       <c r="R182" t="n">
-        <v>-0.1254764264443433</v>
+        <v>-0.2681683426929604</v>
       </c>
       <c r="S182" t="n">
-        <v>0.007762549690039248</v>
+        <v>-0.1372463787340703</v>
       </c>
       <c r="T182" t="n">
         <v>37.035</v>
@@ -17221,6 +17766,9 @@
       <c r="AB182" t="n">
         <v>4.31649893106351</v>
       </c>
+      <c r="AC182" t="n">
+        <v>-13.77859206877289</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17276,13 +17824,13 @@
         <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.517448759616197</v>
+        <v>4.463</v>
       </c>
       <c r="R183" t="n">
-        <v>-0.1176497336051909</v>
+        <v>-0.4629885604079176</v>
       </c>
       <c r="S183" t="n">
-        <v>0.007379373309613885</v>
+        <v>0.1330548245626378</v>
       </c>
       <c r="T183" t="n">
         <v>36.975</v>
@@ -17313,6 +17861,9 @@
       <c r="AB183" t="n">
         <v>3.663316067014311</v>
       </c>
+      <c r="AC183" t="n">
+        <v>-11.61426348862545</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17368,13 +17919,13 @@
         <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.446307652740125</v>
+        <v>4.146</v>
       </c>
       <c r="R184" t="n">
-        <v>-0.1131708253280266</v>
+        <v>-0.2625893162602044</v>
       </c>
       <c r="S184" t="n">
-        <v>0.007131350837983122</v>
+        <v>0.319303724556464</v>
       </c>
       <c r="T184" t="n">
         <v>36.98999999999999</v>
@@ -17405,6 +17956,9 @@
       <c r="AB184" t="n">
         <v>2.836256781016594</v>
       </c>
+      <c r="AC184" t="n">
+        <v>-8.763934719054857</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -17460,13 +18014,13 @@
         <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.368830725658837</v>
+        <v>4.162</v>
       </c>
       <c r="R185" t="n">
-        <v>-0.108283562545938</v>
+        <v>-0.04358048927816371</v>
       </c>
       <c r="S185" t="n">
-        <v>0.006838185237040398</v>
+        <v>0.1339067726264078</v>
       </c>
       <c r="T185" t="n">
         <v>27.54</v>
@@ -17497,6 +18051,9 @@
       <c r="AB185" t="n">
         <v>1.795089550854996</v>
       </c>
+      <c r="AC185" t="n">
+        <v>-5.295927281779851</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17552,13 +18109,13 @@
         <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>4.29126486985254</v>
+        <v>4.079</v>
       </c>
       <c r="R186" t="n">
-        <v>-0.1033792290370099</v>
+        <v>-0.08287120906523882</v>
       </c>
       <c r="S186" t="n">
-        <v>0.006539057442742545</v>
+        <v>-0.02162104983269235</v>
       </c>
       <c r="T186" t="n">
         <v>28.995</v>
@@ -17589,6 +18146,9 @@
       <c r="AB186" t="n">
         <v>1.03864456869061</v>
       </c>
+      <c r="AC186" t="n">
+        <v>-2.886203344510287</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -17644,13 +18204,13 @@
         <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>4.179892704249451</v>
+        <v>4.038</v>
       </c>
       <c r="R187" t="n">
-        <v>-0.09633007699173546</v>
+        <v>-0.05267536219197266</v>
       </c>
       <c r="S187" t="n">
-        <v>0.006116931835647616</v>
+        <v>0.01842907930880282</v>
       </c>
       <c r="T187" t="n">
         <v>28.995</v>
@@ -17681,6 +18241,9 @@
       <c r="AB187" t="n">
         <v>0.5714869321461707</v>
       </c>
+      <c r="AC187" t="n">
+        <v>-1.457258038784022</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17736,13 +18299,13 @@
         <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>4.045170168661021</v>
+        <v>3.93</v>
       </c>
       <c r="R188" t="n">
-        <v>-0.08773564742447726</v>
+        <v>-0.04223588529461475</v>
       </c>
       <c r="S188" t="n">
-        <v>0.005580906642648598</v>
+        <v>0.006595986242658187</v>
       </c>
       <c r="T188" t="n">
         <v>28.98</v>
@@ -17773,6 +18336,9 @@
       <c r="AB188" t="n">
         <v>0.4951699747232352</v>
       </c>
+      <c r="AC188" t="n">
+        <v>-1.265738417756439</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17828,13 +18394,13 @@
         <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.945283758584152</v>
+        <v>3.91</v>
       </c>
       <c r="R189" t="n">
-        <v>-0.08139788037707119</v>
+        <v>-0.03492885270456325</v>
       </c>
       <c r="S189" t="n">
-        <v>0.005086564136433325</v>
+        <v>-0.00145165825128493</v>
       </c>
       <c r="T189" t="n">
         <v>28.995</v>
@@ -17865,6 +18431,9 @@
       <c r="AB189" t="n">
         <v>0.5026215848024155</v>
       </c>
+      <c r="AC189" t="n">
+        <v>-1.325871585602914</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -17920,13 +18489,13 @@
         <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.831377663495088</v>
+        <v>3.826</v>
       </c>
       <c r="R190" t="n">
-        <v>-0.07442712225276227</v>
+        <v>-0.05092192082111441</v>
       </c>
       <c r="S190" t="n">
-        <v>0.004411762671548086</v>
+        <v>-0.006108362231804951</v>
       </c>
       <c r="T190" t="n">
         <v>28.98</v>
@@ -17957,6 +18526,9 @@
       <c r="AB190" t="n">
         <v>0.5083124347415087</v>
       </c>
+      <c r="AC190" t="n">
+        <v>-1.393291090628012</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18012,13 +18584,13 @@
         <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.648595637603464</v>
+        <v>3.721</v>
       </c>
       <c r="R191" t="n">
-        <v>-0.06431588583730083</v>
+        <v>-0.04395754183627318</v>
       </c>
       <c r="S191" t="n">
-        <v>0.003388074231126136</v>
+        <v>0.0009205293628549282</v>
       </c>
       <c r="T191" t="n">
         <v>28.98</v>
@@ -18049,6 +18621,9 @@
       <c r="AB191" t="n">
         <v>0.5081937528597683</v>
       </c>
+      <c r="AC191" t="n">
+        <v>-1.495745290291192</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18104,13 +18679,13 @@
         <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.338917049261011</v>
+        <v>3.422</v>
       </c>
       <c r="R192" t="n">
-        <v>-0.05011772496703459</v>
+        <v>-0.05858720384093563</v>
       </c>
       <c r="S192" t="n">
-        <v>0.0016185694681621</v>
+        <v>-0.002409845609047872</v>
       </c>
       <c r="T192" t="n">
         <v>29.01</v>
@@ -18141,6 +18716,9 @@
       <c r="AB192" t="n">
         <v>0.47855134637752</v>
       </c>
+      <c r="AC192" t="n">
+        <v>-1.653052737327525</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18196,13 +18774,13 @@
         <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.262749874551532</v>
+        <v>3.328</v>
       </c>
       <c r="R193" t="n">
-        <v>-0.04798832749499038</v>
+        <v>-0.06227013972744544</v>
       </c>
       <c r="S193" t="n">
-        <v>0.0009323197603370286</v>
+        <v>-0.002281102675119218</v>
       </c>
       <c r="T193" t="n">
         <v>28.98</v>
@@ -18233,6 +18811,9 @@
       <c r="AB193" t="n">
         <v>0.4621313762975864</v>
       </c>
+      <c r="AC193" t="n">
+        <v>-1.683074665953119</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -18288,13 +18869,13 @@
         <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.189332572827509</v>
+        <v>3.228</v>
       </c>
       <c r="R194" t="n">
-        <v>-0.04719784172966035</v>
+        <v>-0.06569895173441775</v>
       </c>
       <c r="S194" t="n">
-        <v>0.000160708791953186</v>
+        <v>-0.0005008970921516163</v>
       </c>
       <c r="T194" t="n">
         <v>28.995</v>
@@ -18325,6 +18906,9 @@
       <c r="AB194" t="n">
         <v>0.4401129170107577</v>
       </c>
+      <c r="AC194" t="n">
+        <v>-1.703905076199792</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -18380,13 +18964,13 @@
         <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.12034244550554</v>
+        <v>3.13</v>
       </c>
       <c r="R195" t="n">
-        <v>-0.04744687385215529</v>
+        <v>-0.06405871905871907</v>
       </c>
       <c r="S195" t="n">
-        <v>-0.000452126974844435</v>
+        <v>0.002412451169891895</v>
       </c>
       <c r="T195" t="n">
         <v>28.995</v>
@@ -18417,6 +19001,9 @@
       <c r="AB195" t="n">
         <v>0.4148233066433576</v>
       </c>
+      <c r="AC195" t="n">
+        <v>-1.716994537241806</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -18472,13 +19059,13 @@
         <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>2.973859734392465</v>
+        <v>2.953</v>
       </c>
       <c r="R196" t="n">
-        <v>-0.05058953336990651</v>
+        <v>-0.04862236658369257</v>
       </c>
       <c r="S196" t="n">
-        <v>-0.001519770183040392</v>
+        <v>-0.001644053893141581</v>
       </c>
       <c r="T196" t="n">
         <v>28.98</v>
@@ -18509,6 +19096,9 @@
       <c r="AB196" t="n">
         <v>0.3505176057965108</v>
       </c>
+      <c r="AC196" t="n">
+        <v>-1.727173376227441</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -18564,13 +19154,13 @@
         <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>2.815271320868581</v>
+        <v>2.836</v>
       </c>
       <c r="R197" t="n">
-        <v>-0.05658408257420433</v>
+        <v>-0.0735314464133654</v>
       </c>
       <c r="S197" t="n">
-        <v>-0.002555149639045278</v>
+        <v>-0.003153424161267297</v>
       </c>
       <c r="T197" t="n">
         <v>28.995</v>
@@ -18601,6 +19191,9 @@
       <c r="AB197" t="n">
         <v>0.2733429230022186</v>
       </c>
+      <c r="AC197" t="n">
+        <v>-1.719585285772643</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -18656,13 +19249,13 @@
         <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>2.726598804550801</v>
+        <v>2.698</v>
       </c>
       <c r="R198" t="n">
-        <v>-0.0608864521354604</v>
+        <v>-0.07436563436563448</v>
       </c>
       <c r="S198" t="n">
-        <v>-0.003047017038159183</v>
+        <v>0.01272827474437706</v>
       </c>
       <c r="T198" t="n">
         <v>29.01</v>
@@ -18693,6 +19286,9 @@
       <c r="AB198" t="n">
         <v>0.2283843276209666</v>
       </c>
+      <c r="AC198" t="n">
+        <v>-1.708451505245871</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -18748,13 +19344,13 @@
         <v>0</v>
       </c>
       <c r="Q199" t="n">
-        <v>2.660908107778384</v>
+        <v>2.632</v>
       </c>
       <c r="R199" t="n">
-        <v>-0.06423868457390691</v>
+        <v>-0.05134865134865096</v>
       </c>
       <c r="S199" t="n">
-        <v>-0.00333818760650087</v>
+        <v>0.03111359766892498</v>
       </c>
       <c r="T199" t="n">
         <v>28.98</v>
@@ -18784,6 +19380,9 @@
       </c>
       <c r="AB199" t="n">
         <v>0.1954476002213318</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>-1.698722903124076</v>
       </c>
     </row>
   </sheetData>
